--- a/Interim1/Q3_Results.xlsx
+++ b/Interim1/Q3_Results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="85" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="136" uniqueCount="15">
   <si>
     <t>Theta2_deg</t>
   </si>
@@ -145,22 +145,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="0">
-        <v>-0.75244326454947297</v>
+        <v>-3.7667516454869903</v>
       </c>
       <c r="C2" s="0">
-        <v>167.47660893543079</v>
+        <v>170.77220822187019</v>
       </c>
       <c r="D2" s="0">
-        <v>168.89622909189691</v>
+        <v>169.4723934099593</v>
       </c>
       <c r="E2" s="0">
-        <v>10.726656890450464</v>
+        <v>8.5438944659426834</v>
       </c>
       <c r="F2" s="0">
-        <v>8.7156907170903253</v>
+        <v>5.977374162840988</v>
       </c>
       <c r="G2" s="0">
-        <v>175.19408373851175</v>
+        <v>176.19828591936928</v>
       </c>
     </row>
     <row r="3">
@@ -168,22 +168,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>0.60653925981621271</v>
+        <v>-1.9481856245333482</v>
       </c>
       <c r="C3" s="0">
-        <v>167.01722672726157</v>
+        <v>169.77185819219898</v>
       </c>
       <c r="D3" s="0">
-        <v>168.75693375911772</v>
+        <v>169.0697099440286</v>
       </c>
       <c r="E3" s="0">
-        <v>11.850511341278541</v>
+        <v>9.7974564783567537</v>
       </c>
       <c r="F3" s="0">
-        <v>10.015137937874044</v>
+        <v>7.6000591753311255</v>
       </c>
       <c r="G3" s="0">
-        <v>174.920214115557</v>
+        <v>175.51088273282559</v>
       </c>
     </row>
     <row r="4">
@@ -191,22 +191,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="0">
-        <v>1.8783919010673549</v>
+        <v>-0.47120918730902162</v>
       </c>
       <c r="C4" s="0">
-        <v>166.66032371894667</v>
+        <v>169.1736289248673</v>
       </c>
       <c r="D4" s="0">
-        <v>168.66696000023967</v>
+        <v>168.86299386668301</v>
       </c>
       <c r="E4" s="0">
-        <v>12.951412054174527</v>
+        <v>10.95399973522127</v>
       </c>
       <c r="F4" s="0">
-        <v>11.254403948683176</v>
+        <v>8.9821615232742147</v>
       </c>
       <c r="G4" s="0">
-        <v>174.72455857885802</v>
+        <v>175.13082240835871</v>
       </c>
     </row>
     <row r="5">
@@ -214,22 +214,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="0">
-        <v>3.0946510851092755</v>
+        <v>0.86654464830185463</v>
       </c>
       <c r="C5" s="0">
-        <v>166.36876287783466</v>
+        <v>168.73922046083732</v>
       </c>
       <c r="D5" s="0">
-        <v>168.60801327320877</v>
+        <v>168.73576799720846</v>
       </c>
       <c r="E5" s="0">
-        <v>14.038794615210083</v>
+        <v>12.072128601814722</v>
       </c>
       <c r="F5" s="0">
-        <v>12.456113013513658</v>
+        <v>10.266848184906934</v>
       </c>
       <c r="G5" s="0">
-        <v>174.57859304200829</v>
+        <v>174.87603361070089</v>
       </c>
     </row>
     <row r="6">
@@ -237,22 +237,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="0">
-        <v>4.2721419541296104</v>
+        <v>2.1254156040632157</v>
       </c>
       <c r="C6" s="0">
-        <v>166.12272901083534</v>
+        <v>168.39757981277549</v>
       </c>
       <c r="D6" s="0">
-        <v>168.57034756904787</v>
+        <v>168.65308028946393</v>
       </c>
       <c r="E6" s="0">
-        <v>15.11768051193553</v>
+        <v>13.169767785990205</v>
       </c>
       <c r="F6" s="0">
-        <v>13.632339069669257</v>
+        <v>11.4972652354069</v>
       </c>
       <c r="G6" s="0">
-        <v>174.46710139003787</v>
+        <v>174.69200145459982</v>
       </c>
     </row>
     <row r="7">
@@ -260,22 +260,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="0">
-        <v>5.4210061993431342</v>
+        <v>3.3328576569152917</v>
       </c>
       <c r="C7" s="0">
-        <v>165.91027602441818</v>
+        <v>168.11637691053136</v>
       </c>
       <c r="D7" s="0">
-        <v>168.54811501229767</v>
+        <v>168.59900481123685</v>
       </c>
       <c r="E7" s="0">
-        <v>16.19105821842281</v>
+        <v>14.255134942458778</v>
       </c>
       <c r="F7" s="0">
-        <v>14.790339735228173</v>
+        <v>12.693115144713232</v>
       </c>
       <c r="G7" s="0">
-        <v>174.38092438686996</v>
+        <v>174.55389204730355</v>
       </c>
     </row>
     <row r="8">
@@ -283,22 +283,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="0">
-        <v>6.5478652335033054</v>
+        <v>4.5039547246809235</v>
       </c>
       <c r="C8" s="0">
-        <v>165.72360242713634</v>
+        <v>167.8778467096424</v>
       </c>
       <c r="D8" s="0">
-        <v>168.53752502067479</v>
+        <v>168.5648101127465</v>
       </c>
       <c r="E8" s="0">
-        <v>17.260837747184684</v>
+        <v>15.332723826806996</v>
       </c>
       <c r="F8" s="0">
-        <v>15.934829228598232</v>
+        <v>13.865218670401589</v>
       </c>
       <c r="G8" s="0">
-        <v>174.31409628993316</v>
+        <v>174.44806649821953</v>
       </c>
     </row>
     <row r="9">
@@ -306,22 +306,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="0">
-        <v>7.6572942336158985</v>
+        <v>5.6479688009247067</v>
       </c>
       <c r="C9" s="0">
-        <v>165.55731575871772</v>
+        <v>167.67107884463613</v>
       </c>
       <c r="D9" s="0">
-        <v>168.53598332104716</v>
+        <v>168.54516219503853</v>
       </c>
       <c r="E9" s="0">
-        <v>18.328301566001912</v>
+        <v>16.405253828260374</v>
       </c>
       <c r="F9" s="0">
-        <v>17.069042349136254</v>
+        <v>15.020198231912474</v>
       </c>
       <c r="G9" s="0">
-        <v>174.26250838303619</v>
+        <v>174.36616340441242</v>
       </c>
     </row>
     <row r="10">
@@ -329,22 +329,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="0">
-        <v>8.7525915783307884</v>
+        <v>6.77102495552937</v>
       </c>
       <c r="C10" s="0">
-        <v>165.40752665944177</v>
+        <v>167.48885617747311</v>
       </c>
       <c r="D10" s="0">
-        <v>168.54164128502615</v>
+        <v>168.5365606854545</v>
       </c>
       <c r="E10" s="0">
-        <v>19.394342379383048</v>
+        <v>17.474482661094655</v>
       </c>
       <c r="F10" s="0">
-        <v>18.19529171929878</v>
+        <v>16.162409184306625</v>
       </c>
       <c r="G10" s="0">
-        <v>174.22321055014604</v>
+        <v>174.30266744455776</v>
       </c>
     </row>
     <row r="11">
@@ -352,22 +352,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="0">
-        <v>9.836215055826905</v>
+        <v>7.8773955237834636</v>
       </c>
       <c r="C11" s="0">
-        <v>165.27133529216204</v>
+        <v>167.32614277247237</v>
       </c>
       <c r="D11" s="0">
-        <v>168.55313996854625</v>
+        <v>168.53658827898914</v>
       </c>
       <c r="E11" s="0">
-        <v>20.459598856646554</v>
+        <v>18.541600110951741</v>
       </c>
       <c r="F11" s="0">
-        <v>19.315284418586145</v>
+        <v>17.294867460949405</v>
       </c>
       <c r="G11" s="0">
-        <v>174.19401501367295</v>
+        <v>174.25374474097336</v>
       </c>
     </row>
     <row r="12">
@@ -375,22 +375,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="0">
-        <v>10.910045252493834</v>
+        <v>8.9701829671965534</v>
       </c>
       <c r="C12" s="0">
-        <v>165.14652124126405</v>
+        <v>167.17927990392064</v>
       </c>
       <c r="D12" s="0">
-        <v>168.5694554155674</v>
+        <v>168.54351060591111</v>
       </c>
       <c r="E12" s="0">
-        <v>21.524537880410296</v>
+        <v>19.607439406077695</v>
       </c>
       <c r="F12" s="0">
-        <v>20.430313424897605</v>
+        <v>18.419744381198569</v>
       </c>
       <c r="G12" s="0">
-        <v>174.17325695439047</v>
+        <v>174.21662290547741</v>
       </c>
     </row>
     <row r="13">
@@ -398,22 +398,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="0">
-        <v>11.975552720115438</v>
+        <v>10.051712425807075</v>
       </c>
       <c r="C13" s="0">
-        <v>165.03134670017821</v>
+        <v>167.04552387846925</v>
       </c>
       <c r="D13" s="0">
-        <v>168.58980047356141</v>
+        <v>168.55604582819956</v>
       </c>
       <c r="E13" s="0">
-        <v>22.589506767892836</v>
+        <v>20.672599480908012</v>
       </c>
       <c r="F13" s="0">
-        <v>21.541379168387493</v>
+        <v>19.538651692541805</v>
       </c>
       <c r="G13" s="0">
-        <v>174.15964255630328</v>
+        <v>174.18923439343271</v>
       </c>
     </row>
     <row r="14">
@@ -421,22 +421,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="0">
-        <v>13.033908454720184</v>
+        <v>11.12377133948981</v>
       </c>
       <c r="C14" s="0">
-        <v>164.92442640084002</v>
+        <v>166.92276391735268</v>
       </c>
       <c r="D14" s="0">
-        <v>168.61355996145221</v>
+        <v>168.57322389177028</v>
       </c>
       <c r="E14" s="0">
-        <v>23.654767688726007</v>
+        <v>21.7375198274102</v>
       </c>
       <c r="F14" s="0">
-        <v>22.649269828211033</v>
+        <v>20.652815763691876</v>
       </c>
       <c r="G14" s="0">
-        <v>174.15214859279993</v>
+        <v>174.16999871215788</v>
       </c>
     </row>
     <row r="15">
@@ -444,22 +444,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="0">
-        <v>14.086059400968796</v>
+        <v>12.187762867138293</v>
       </c>
       <c r="C15" s="0">
-        <v>164.82463871950276</v>
+        <v>166.80934153021002</v>
       </c>
       <c r="D15" s="0">
-        <v>168.64024643957569</v>
+        <v>168.5942964261331</v>
       </c>
       <c r="E15" s="0">
-        <v>24.720521051125129</v>
+        <v>22.802528407212915</v>
       </c>
       <c r="F15" s="0">
-        <v>23.754616138776925</v>
+        <v>21.763189139144032</v>
       </c>
       <c r="G15" s="0">
-        <v>174.14995382788692</v>
+        <v>174.15768296281564</v>
       </c>
     </row>
     <row r="16">
@@ -467,22 +467,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="0">
-        <v>15.132781533450355</v>
+        <v>13.244808012241425</v>
       </c>
       <c r="C16" s="0">
-        <v>164.7310631813472</v>
+        <v>166.70393027914111</v>
       </c>
       <c r="D16" s="0">
-        <v>168.66946919660421</v>
+        <v>168.6186768311814</v>
       </c>
       <c r="E16" s="0">
-        <v>25.786921799485587</v>
+        <v>23.867873437909136</v>
       </c>
       <c r="F16" s="0">
-        <v>24.857929839432501</v>
+        <v>22.870524750399625</v>
       </c>
       <c r="G16" s="0">
-        <v>174.15239082184374</v>
+        <v>174.15130902406173</v>
       </c>
     </row>
     <row r="17">
@@ -490,22 +490,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="0">
-        <v>16.17471808666037</v>
+        <v>14.29581584068648</v>
       </c>
       <c r="C17" s="0">
-        <v>164.64293544927924</v>
+        <v>166.60545310847925</v>
       </c>
       <c r="D17" s="0">
-        <v>168.70091199091999</v>
+        <v>168.64589916280295</v>
       </c>
       <c r="E17" s="0">
-        <v>26.854091016406937</v>
+        <v>24.933745108812644</v>
       </c>
       <c r="F17" s="0">
-        <v>25.959631287918825</v>
+        <v>23.975426866758284</v>
       </c>
       <c r="G17" s="0">
-        <v>174.158911253524</v>
+        <v>174.15008976346249</v>
       </c>
     </row>
     <row r="18">
@@ -513,22 +513,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="0">
-        <v>17.212407670282548</v>
+        <v>15.341533099356631</v>
       </c>
       <c r="C18" s="0">
-        <v>164.55961422034386</v>
+        <v>166.51302392600201</v>
       </c>
       <c r="D18" s="0">
-        <v>168.73431675127799</v>
+        <v>168.67558916110698</v>
       </c>
       <c r="E18" s="0">
-        <v>27.922124333070546</v>
+        <v>26.000290783440605</v>
       </c>
       <c r="F18" s="0">
-        <v>27.06006969598846</v>
+        <v>25.078387018473791</v>
       </c>
       <c r="G18" s="0">
-        <v>174.16906044846746</v>
+        <v>174.15338399453822</v>
       </c>
     </row>
     <row r="19">
@@ -536,22 +536,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="0">
-        <v>18.246305326884425</v>
+        <v>16.38258011045264</v>
       </c>
       <c r="C19" s="0">
-        <v>164.48055643057168</v>
+        <v>166.42590534142118</v>
       </c>
       <c r="D19" s="0">
-        <v>168.76947143109527</v>
+        <v>168.70744336828304</v>
       </c>
       <c r="E19" s="0">
-        <v>28.991098121794458</v>
+        <v>27.067625863745729</v>
       </c>
       <c r="F19" s="0">
-        <v>28.159538221755298</v>
+        <v>26.179809906184886</v>
       </c>
       <c r="G19" s="0">
-        <v>174.1824583294692</v>
+        <v>174.1606639248875</v>
       </c>
     </row>
     <row r="20">
@@ -559,22 +559,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="0">
-        <v>19.276798559543647</v>
+        <v>17.419477270794324</v>
       </c>
       <c r="C20" s="0">
-        <v>164.40529838125804</v>
+        <v>166.34347746519975</v>
       </c>
       <c r="D20" s="0">
-        <v>168.80620081824574</v>
+        <v>168.7412137807892</v>
       </c>
       <c r="E20" s="0">
-        <v>30.061074117797109</v>
+        <v>28.135841691728487</v>
       </c>
       <c r="F20" s="0">
-        <v>29.258285401836417</v>
+        <v>27.280032458370243</v>
       </c>
       <c r="G20" s="0">
-        <v>174.1987849431579</v>
+        <v>174.17149115497077</v>
       </c>
     </row>
     <row r="21">
@@ -582,22 +582,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="0">
-        <v>20.304219706601785</v>
+        <v>18.45266496636383</v>
       </c>
       <c r="C21" s="0">
-        <v>164.3334411653141</v>
+        <v>166.26521445913747</v>
       </c>
       <c r="D21" s="0">
-        <v>168.84435948647041</v>
+        <v>168.77669637579118</v>
       </c>
       <c r="E21" s="0">
-        <v>31.132102909842768</v>
+        <v>29.205011384049758</v>
       </c>
       <c r="F21" s="0">
-        <v>30.356523931002698</v>
+        <v>28.379338091322609</v>
       </c>
       <c r="G21" s="0">
-        <v>174.21776930818268</v>
+        <v>174.18549866878342</v>
       </c>
     </row>
     <row r="22">
@@ -605,22 +605,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="0">
-        <v>21.328855619019883</v>
+        <v>19.482518775280404</v>
       </c>
       <c r="C22" s="0">
-        <v>164.26463926882775</v>
+        <v>166.19066663341997</v>
       </c>
       <c r="D22" s="0">
-        <v>168.88382632393839</v>
+        <v>168.81372240487283</v>
       </c>
       <c r="E22" s="0">
-        <v>32.204226604480482</v>
+        <v>30.275194197543051</v>
       </c>
       <c r="F22" s="0">
-        <v>31.454437488447411</v>
+        <v>29.477967541950534</v>
       </c>
       <c r="G22" s="0">
-        <v>174.23918071469146</v>
+        <v>174.20237711044837</v>
       </c>
     </row>
     <row r="23">
@@ -628,22 +628,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="0">
-        <v>22.350955315863821</v>
+        <v>20.509361237231889</v>
       </c>
       <c r="C23" s="0">
-        <v>164.19859155255335</v>
+        <v>166.11944658552685</v>
       </c>
       <c r="D23" s="0">
-        <v>168.92450024018697</v>
+        <v>168.85215169976416</v>
       </c>
       <c r="E23" s="0">
-        <v>33.277480878766362</v>
+        <v>31.346438833598558</v>
       </c>
       <c r="F23" s="0">
-        <v>32.552186104735057</v>
+        <v>30.576127208582932</v>
       </c>
       <c r="G23" s="0">
-        <v>174.26282185983033</v>
+        <v>174.22186418263428</v>
       </c>
     </row>
     <row r="24">
@@ -651,22 +651,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="0">
-        <v>23.370736103689985</v>
+        <v>21.533471079540192</v>
       </c>
       <c r="C24" s="0">
-        <v>164.1350340414462</v>
+        <v>166.05121833301146</v>
       </c>
       <c r="D24" s="0">
-        <v>168.96629676503204</v>
+        <v>168.89186746426077</v>
       </c>
       <c r="E24" s="0">
-        <v>34.351896575384316</v>
+        <v>32.418785965196008</v>
       </c>
       <c r="F24" s="0">
-        <v>33.649910424426736</v>
+        <v>31.673995651069106</v>
       </c>
       <c r="G24" s="0">
-        <v>174.28852337691117</v>
+        <v>174.24373635596714</v>
       </c>
     </row>
     <row r="25">
@@ -674,22 +674,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="0">
-        <v>24.388388514536121</v>
+        <v>22.555090531452628</v>
       </c>
       <c r="C25" s="0">
-        <v>164.07373410465888</v>
+        <v>165.98568869659593</v>
       </c>
       <c r="D25" s="0">
-        <v>169.00914533065785</v>
+        <v>168.93277217957623</v>
       </c>
       <c r="E25" s="0">
-        <v>35.427500951943024</v>
+        <v>33.492270187365492</v>
       </c>
       <c r="F25" s="0">
-        <v>34.74773512328963</v>
+        <v>32.771728712047462</v>
       </c>
       <c r="G25" s="0">
-        <v>174.31613943535413</v>
+        <v>174.26780231419642</v>
       </c>
     </row>
     <row r="26">
@@ -697,22 +697,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="0">
-        <v>25.40408032514312</v>
+        <v>23.574431182284187</v>
       </c>
       <c r="C26" s="0">
-        <v>164.01448571681553</v>
+        <v>165.92260039718826</v>
       </c>
       <c r="D26" s="0">
-        <v>169.05298708261952</v>
+        <v>168.97478435457077</v>
       </c>
       <c r="E26" s="0">
-        <v>36.504318666646022</v>
+        <v>34.566921535297411</v>
       </c>
       <c r="F26" s="0">
-        <v>35.845771671492656</v>
+        <v>33.869463592275537</v>
       </c>
       <c r="G26" s="0">
-        <v>174.34554417244124</v>
+        <v>174.29389772023958</v>
       </c>
     </row>
     <row r="27">
@@ -720,22 +720,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="0">
-        <v>26.41795985433615</v>
+        <v>24.591678717063957</v>
       </c>
       <c r="C27" s="0">
-        <v>163.95710556872325</v>
+        <v>165.8617264740204</v>
       </c>
       <c r="D27" s="0">
-        <v>169.09777310437352</v>
+        <v>169.01783592453307</v>
       </c>
       <c r="E27" s="0">
-        <v>37.582372561462535</v>
+        <v>35.642766675115162</v>
       </c>
       <c r="F27" s="0">
-        <v>36.944120586034927</v>
+        <v>34.967322123499088</v>
       </c>
       <c r="G27" s="0">
-        <v>174.37662877780724</v>
+        <v>174.32188099939796</v>
       </c>
     </row>
     <row r="28">
@@ -743,22 +743,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="0">
-        <v>27.430158687953814</v>
+        <v>25.606996777376534</v>
       </c>
       <c r="C28" s="0">
-        <v>163.90142985164317</v>
+        <v>165.80286573230677</v>
       </c>
       <c r="D28" s="0">
-        <v>169.14346296806383</v>
+        <v>169.06187015308831</v>
       </c>
       <c r="E28" s="0">
-        <v>38.661684288729042</v>
+        <v>36.71982984471304</v>
       </c>
       <c r="F28" s="0">
-        <v>38.042873280835494</v>
+        <v>36.065413419310033</v>
       </c>
       <c r="G28" s="0">
-        <v>174.40929909492104</v>
+        <v>174.35162991439674</v>
       </c>
     </row>
     <row r="29">
@@ -766,22 +766,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="0">
-        <v>28.440793945863827</v>
+        <v>26.620530133571599</v>
       </c>
       <c r="C29" s="0">
-        <v>163.84731158027091</v>
+        <v>165.74583900124244</v>
       </c>
       <c r="D29" s="0">
-        <v>169.19002354488202</v>
+        <v>169.10683992821103</v>
       </c>
       <c r="E29" s="0">
-        <v>39.742274816013875</v>
+        <v>37.79813360234332</v>
       </c>
       <c r="F29" s="0">
-        <v>39.142113597402215</v>
+        <v>37.163836039363417</v>
       </c>
       <c r="G29" s="0">
-        <v>174.44347363557816</v>
+        <v>174.38303876297499</v>
       </c>
     </row>
     <row r="30">
@@ -789,22 +789,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="0">
-        <v>29.449970179752405</v>
+        <v>27.632407309885487</v>
       </c>
       <c r="C30" s="0">
-        <v>163.79461835000706</v>
+        <v>165.69048603569996</v>
       </c>
       <c r="D30" s="0">
-        <v>169.23742802356736</v>
+        <v>169.15270636970686</v>
       </c>
       <c r="E30" s="0">
-        <v>40.82416483589234</v>
+        <v>38.877699426382556</v>
       </c>
       <c r="F30" s="0">
-        <v>40.241919080108545</v>
+        <v>38.262679769635554</v>
       </c>
       <c r="G30" s="0">
-        <v>174.47908192697645</v>
+        <v>174.41601606943354</v>
       </c>
     </row>
     <row r="31">
@@ -812,22 +812,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="0">
-        <v>30.45778097098377</v>
+        <v>28.642742771217041</v>
       </c>
       <c r="C31" s="0">
-        <v>163.74323044692432</v>
+        <v>165.63666293359665</v>
       </c>
       <c r="D31" s="0">
-        <v>169.28565509703407</v>
+        <v>169.19943768490239</v>
       </c>
       <c r="E31" s="0">
-        <v>41.90737510118035</v>
+        <v>39.958548199266687</v>
       </c>
       <c r="F31" s="0">
-        <v>41.34236204595166</v>
+        <v>39.362027097403569</v>
       </c>
       <c r="G31" s="0">
-        <v>174.51606312861367</v>
+        <v>174.45048267143997</v>
       </c>
     </row>
     <row r="32">
@@ -835,22 +835,22 @@
         <v>30</v>
       </c>
       <c r="B32" s="0">
-        <v>31.464310283134669</v>
+        <v>29.651638755916039</v>
       </c>
       <c r="C32" s="0">
-        <v>163.69303924613291</v>
+        <v>165.58423996960966</v>
       </c>
       <c r="D32" s="0">
-        <v>169.334688285749</v>
+        <v>169.24700822366077</v>
       </c>
       <c r="E32" s="0">
-        <v>42.991926701590124</v>
+        <v>41.04070060088003</v>
       </c>
       <c r="F32" s="0">
-        <v>42.443510487970315</v>
+        <v>40.461954441813702</v>
       </c>
       <c r="G32" s="0">
-        <v>174.55436486962287</v>
+        <v>174.48637012560798</v>
       </c>
     </row>
     <row r="33">
@@ -858,22 +858,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="0">
-        <v>32.469633612570618</v>
+        <v>30.65918682061206</v>
       </c>
       <c r="C33" s="0">
-        <v>163.64394584747222</v>
+        <v>165.53309976749262</v>
       </c>
       <c r="D33" s="0">
-        <v>169.38451537307409</v>
+        <v>169.29539769463293</v>
       </c>
       <c r="E33" s="0">
-        <v>44.077841294297336</v>
+        <v>42.124177430921115</v>
       </c>
       <c r="F33" s="0">
-        <v>43.545428843332474</v>
+        <v>41.562533187530676</v>
       </c>
       <c r="G33" s="0">
-        <v>174.59394226739318</v>
+        <v>174.52361937206661</v>
       </c>
     </row>
     <row r="34">
@@ -881,22 +881,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="0">
-        <v>33.473818971758433</v>
+        <v>31.665469149197822</v>
       </c>
       <c r="C34" s="0">
-        <v>163.59585990766607</v>
+        <v>165.48313574962711</v>
       </c>
       <c r="D34" s="0">
-        <v>169.43512793286106</v>
+        <v>169.3445905128292</v>
       </c>
       <c r="E34" s="0">
-        <v>45.165141298260089</v>
+        <v>43.208999875436504</v>
       </c>
       <c r="F34" s="0">
-        <v>44.648178650824008</v>
+        <v>42.663830558832729</v>
       </c>
       <c r="G34" s="0">
-        <v>174.63475709621216</v>
+        <v>174.56217961090297</v>
       </c>
     </row>
     <row r="35">
@@ -904,22 +904,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="0">
-        <v>34.476927733262201</v>
+        <v>32.670559667417351</v>
       </c>
       <c r="C35" s="0">
-        <v>163.54869863601923</v>
+        <v>165.4342508149935</v>
       </c>
       <c r="D35" s="0">
-        <v>169.48652093352556</v>
+        <v>169.39457525484917</v>
       </c>
       <c r="E35" s="0">
-        <v>46.253850060088077</v>
+        <v>44.295189729424514</v>
       </c>
       <c r="F35" s="0">
-        <v>45.751819117592561</v>
+        <v>43.76591036377522</v>
       </c>
       <c r="G35" s="0">
-        <v>174.67677708080504</v>
+        <v>174.60200735306998</v>
       </c>
     </row>
     <row r="36">
@@ -927,22 +927,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="0">
-        <v>35.479015357079554</v>
+        <v>33.674524996267259</v>
       </c>
       <c r="C36" s="0">
-        <v>163.5023859269599</v>
+        <v>165.38635620644709</v>
       </c>
       <c r="D36" s="0">
-        <v>169.53869240590458</v>
+        <v>169.44534420292462</v>
       </c>
       <c r="E36" s="0">
-        <v>47.343991997690985</v>
+        <v>45.382769584896011</v>
       </c>
       <c r="F36" s="0">
-        <v>46.856407611202087</v>
+        <v>44.86883363207707</v>
       </c>
       <c r="G36" s="0">
-        <v>174.71997529445284</v>
+        <v>174.64306561584707</v>
       </c>
     </row>
     <row r="37">
@@ -950,22 +950,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="0">
-        <v>36.480132019795924</v>
+        <v>34.677425270996054</v>
       </c>
       <c r="C37" s="0">
-        <v>163.45685160765015</v>
+        <v>165.33937053574559</v>
       </c>
       <c r="D37" s="0">
-        <v>169.59164316462787</v>
+        <v>169.49689296267999</v>
       </c>
       <c r="E37" s="0">
-        <v>48.435592726706133</v>
+        <v>46.47176299184521</v>
       </c>
       <c r="F37" s="0">
-        <v>47.962000090053834</v>
+        <v>45.972659165748439</v>
       </c>
       <c r="G37" s="0">
-        <v>174.76432964517107</v>
+        <v>174.68532323878662</v>
       </c>
     </row>
     <row r="38">
@@ -973,22 +973,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="0">
-        <v>37.480323160713532</v>
+        <v>35.679314847443059</v>
       </c>
       <c r="C38" s="0">
-        <v>163.41203078279418</v>
+        <v>165.29321894070941</v>
       </c>
       <c r="D38" s="0">
-        <v>169.64537657465445</v>
+        <v>169.54922014244639</v>
       </c>
       <c r="E38" s="0">
-        <v>49.52867917375459</v>
+        <v>47.56219459808753</v>
       </c>
       <c r="F38" s="0">
-        <v>49.06865148287153</v>
+        <v>47.077444017857829</v>
       </c>
       <c r="G38" s="0">
-        <v>174.80982243644488</v>
+        <v>174.72875430065889</v>
       </c>
     </row>
     <row r="39">
@@ -996,22 +996,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="0">
-        <v>38.479629957451493</v>
+        <v>36.68024291346871</v>
       </c>
       <c r="C39" s="0">
-        <v>163.3678632619042</v>
+        <v>165.24783235359095</v>
       </c>
       <c r="D39" s="0">
-        <v>169.6998983561613</v>
+        <v>169.60232708427969</v>
       </c>
       <c r="E39" s="0">
-        <v>50.623279679823405</v>
+        <v>48.654090272755923</v>
       </c>
       <c r="F39" s="0">
-        <v>50.176416026058035</v>
+        <v>48.183243911976632</v>
       </c>
       <c r="G39" s="0">
-        <v>174.85643999143412</v>
+        <v>174.77333762153731</v>
       </c>
     </row>
     <row r="40">
@@ -1019,22 +1019,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="0">
-        <v>39.478089741373822</v>
+        <v>37.68025402005317</v>
       </c>
       <c r="C40" s="0">
-        <v>163.32429305680086</v>
+        <v>165.20314686346546</v>
       </c>
       <c r="D40" s="0">
-        <v>169.75521642220281</v>
+        <v>169.65621763866932</v>
       </c>
       <c r="E40" s="0">
-        <v>51.71942409648463</v>
+        <v>49.747477217339132</v>
       </c>
       <c r="F40" s="0">
-        <v>51.285347566230513</v>
+        <v>49.290113612587021</v>
       </c>
       <c r="G40" s="0">
-        <v>174.90417233150484</v>
+        <v>174.81905633704631</v>
       </c>
     </row>
     <row r="41">
@@ -1042,22 +1042,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="0">
-        <v>40.47573636146813</v>
+        <v>38.679388544094231</v>
       </c>
       <c r="C41" s="0">
-        <v>163.28126793916266</v>
+        <v>165.15910315845008</v>
       </c>
       <c r="D41" s="0">
-        <v>169.8113407445542</v>
+        <v>169.71089797639269</v>
       </c>
       <c r="E41" s="0">
-        <v>52.817143877199676</v>
+        <v>50.842384067430622</v>
       </c>
       <c r="F41" s="0">
-        <v>52.395499834032307</v>
+        <v>50.39810725493183</v>
       </c>
       <c r="G41" s="0">
-        <v>174.9530129015159</v>
+        <v>174.8658975341084</v>
       </c>
     </row>
     <row r="42">
@@ -1065,22 +1065,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="0">
-        <v>41.47260050388698</v>
+        <v>39.677683092884991</v>
       </c>
       <c r="C42" s="0">
-        <v>163.2387390495997</v>
+        <v>165.11564603597094</v>
       </c>
       <c r="D42" s="0">
-        <v>169.86828324396305</v>
+        <v>169.76637643214997</v>
       </c>
       <c r="E42" s="0">
-        <v>53.916472165591564</v>
+        <v>51.938840987798173</v>
       </c>
       <c r="F42" s="0">
-        <v>53.50692669434342</v>
+        <v>51.507278641352201</v>
       </c>
       <c r="G42" s="0">
-        <v>175.00295833557558</v>
+        <v>174.91385193938686</v>
       </c>
     </row>
     <row r="43">
@@ -1088,22 +1088,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="0">
-        <v>42.468709973208171</v>
+        <v>40.67517085858843</v>
       </c>
       <c r="C43" s="0">
-        <v>163.19666055108306</v>
+        <v>165.072723971252</v>
       </c>
       <c r="D43" s="0">
-        <v>169.9260577016924</v>
+        <v>169.82266337556831</v>
       </c>
       <c r="E43" s="0">
-        <v>55.017443882282258</v>
+        <v>53.03687976294102</v>
       </c>
       <c r="F43" s="0">
-        <v>54.619682377226226</v>
+        <v>52.617681509996444</v>
       </c>
       <c r="G43" s="0">
-        <v>175.05400825803071</v>
+        <v>174.96291365313297</v>
       </c>
     </row>
     <row r="44">
@@ -1111,22 +1111,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="0">
-        <v>43.464089940521227</v>
+        <v>41.671881929670974</v>
       </c>
       <c r="C44" s="0">
-        <v>163.15498932067638</v>
+        <v>165.03028873579484</v>
       </c>
       <c r="D44" s="0">
-        <v>169.98467968978457</v>
+        <v>169.87977110594201</v>
       </c>
       <c r="E44" s="0">
-        <v>56.120095811666545</v>
+        <v>54.136533884955611</v>
       </c>
       <c r="F44" s="0">
-        <v>55.733821693302062</v>
+        <v>53.729369780853233</v>
       </c>
       <c r="G44" s="0">
-        <v>175.10616511531876</v>
+        <v>175.01307992237813</v>
       </c>
     </row>
     <row r="45">
@@ -1134,22 +1134,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="0">
-        <v>44.458763162661846</v>
+        <v>42.66784356514686</v>
       </c>
       <c r="C45" s="0">
-        <v>163.11368467443867</v>
+        <v>164.98829505892033</v>
       </c>
       <c r="D45" s="0">
-        <v>170.0441665179257</v>
+        <v>169.9377137677096</v>
       </c>
       <c r="E45" s="0">
-        <v>57.224466689819828</v>
+        <v>55.23783864025647</v>
       </c>
       <c r="F45" s="0">
-        <v>56.84940023673883</v>
+        <v>54.842397783305742</v>
       </c>
       <c r="G45" s="0">
-        <v>175.15943403503024</v>
+        <v>175.06435094841981</v>
       </c>
     </row>
     <row r="46">
@@ -1157,22 +1157,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="0">
-        <v>45.452750176265134</v>
+        <v>43.66308043657105</v>
       </c>
       <c r="C46" s="0">
-        <v>163.07270812112961</v>
+        <v>164.94670032651874</v>
       </c>
       <c r="D46" s="0">
-        <v>170.1045371951638</v>
+        <v>169.99650728419473</v>
       </c>
       <c r="E46" s="0">
-        <v>58.330597294602867</v>
+        <v>56.340831196486171</v>
       </c>
       <c r="F46" s="0">
-        <v>57.966474578607077</v>
+        <v>55.956820468791321</v>
       </c>
       <c r="G46" s="0">
-        <v>175.21382270912633</v>
+        <v>175.11672972438754</v>
       </c>
     </row>
     <row r="47">
@@ -1180,22 +1180,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="0">
-        <v>46.446069469765035</v>
+        <v>44.657614841962484</v>
       </c>
       <c r="C47" s="0">
-        <v>163.03202314098573</v>
+        <v>164.90546431204047</v>
       </c>
       <c r="D47" s="0">
-        <v>170.16581240505155</v>
+        <v>170.05616930757009</v>
       </c>
       <c r="E47" s="0">
-        <v>59.438530538924376</v>
+        <v>57.445550690781062</v>
       </c>
       <c r="F47" s="0">
-        <v>59.085102453021733</v>
+        <v>57.072693611653648</v>
       </c>
       <c r="G47" s="0">
-        <v>175.26934129875912</v>
+        <v>175.17022189936347</v>
       </c>
     </row>
     <row r="48">
@@ -1203,22 +1203,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="0">
-        <v>47.438737636013144</v>
+        <v>45.651466895212153</v>
       </c>
       <c r="C48" s="0">
-        <v>162.99159498636686</v>
+        <v>164.86454893549561</v>
       </c>
       <c r="D48" s="0">
-        <v>170.22801449304814</v>
+        <v>170.11671918336569</v>
       </c>
       <c r="E48" s="0">
-        <v>60.548311568048362</v>
+        <v>58.552038320433446</v>
       </c>
       <c r="F48" s="0">
-        <v>60.2053429382117</v>
+        <v>58.190074000872315</v>
       </c>
       <c r="G48" s="0">
-        <v>175.32600235856367</v>
+        <v>175.2248356661101</v>
       </c>
     </row>
     <row r="49">
@@ -1226,22 +1226,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="0">
-        <v>48.430769507808073</v>
+        <v>46.644654694005645</v>
       </c>
       <c r="C49" s="0">
-        <v>162.95139050151846</v>
+        <v>164.8239180468448</v>
       </c>
       <c r="D49" s="0">
-        <v>170.29116746524295</v>
+        <v>170.17817792814893</v>
       </c>
       <c r="E49" s="0">
-        <v>61.659987861783307</v>
+        <v>59.660337436894082</v>
       </c>
       <c r="F49" s="0">
-        <v>61.327256634437958</v>
+        <v>59.309019625026892</v>
       </c>
       <c r="G49" s="0">
-        <v>175.38382077865219</v>
+        <v>175.28058166994273</v>
       </c>
     </row>
     <row r="50">
@@ -1249,22 +1249,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="0">
-        <v>49.422178278303996</v>
+        <v>47.637194468852002</v>
       </c>
       <c r="C50" s="0">
-        <v>162.91137795907025</v>
+        <v>164.78353723067639</v>
       </c>
       <c r="D50" s="0">
-        <v>170.35529699765962</v>
+        <v>170.24056821925896</v>
       </c>
       <c r="E50" s="0">
-        <v>62.77360934235476</v>
+        <v>60.770493643990392</v>
       </c>
       <c r="F50" s="0">
-        <v>62.45090584050557</v>
+        <v>60.429589852588279</v>
       </c>
       <c r="G50" s="0">
-        <v>175.44281374284702</v>
+        <v>175.33747293669342</v>
       </c>
     </row>
     <row r="51">
@@ -1272,22 +1272,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="0">
-        <v>50.412975607994532</v>
+        <v>48.629100715440664</v>
       </c>
       <c r="C51" s="0">
-        <v>162.87152691120949</v>
+        <v>164.74337362949527</v>
       </c>
       <c r="D51" s="0">
-        <v>170.42043045556693</v>
+        <v>170.30391439570028</v>
       </c>
       <c r="E51" s="0">
-        <v>63.889228488753851</v>
+        <v>61.882554901188357</v>
       </c>
       <c r="F51" s="0">
-        <v>63.576354730480077</v>
+        <v>61.551845609421235</v>
       </c>
       <c r="G51" s="0">
-        <v>175.50300070195473</v>
+        <v>175.39552481806081</v>
       </c>
     </row>
     <row r="52">
@@ -1295,22 +1295,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="0">
-        <v>51.403171719735575</v>
+        <v>49.620386312237507</v>
       </c>
       <c r="C52" s="0">
-        <v>162.83180805373436</v>
+        <v>164.70339578331243</v>
       </c>
       <c r="D52" s="0">
-        <v>170.48659692237453</v>
+        <v>170.36824246948876</v>
       </c>
       <c r="E52" s="0">
-        <v>65.006900458347772</v>
+        <v>62.996571632697922</v>
       </c>
       <c r="F52" s="0">
-        <v>64.703669532110382</v>
+        <v>62.675849555212253</v>
       </c>
       <c r="G52" s="0">
-        <v>175.56440336111567</v>
+        <v>175.45475495293917</v>
       </c>
     </row>
     <row r="53">
@@ -1318,22 +1318,22 @@
         <v>51</v>
       </c>
       <c r="B53" s="0">
-        <v>52.392775483073145</v>
+        <v>50.61106262496606</v>
       </c>
       <c r="C53" s="0">
-        <v>162.7921931014225</v>
+        <v>164.66357348352966</v>
       </c>
       <c r="D53" s="0">
-        <v>170.55382723782421</v>
+        <v>170.43358014690881</v>
       </c>
       <c r="E53" s="0">
-        <v>66.126683216556913</v>
+        <v>64.112596843210042</v>
       </c>
       <c r="F53" s="0">
-        <v>65.832918708391816</v>
+        <v>63.801666260409078</v>
       </c>
       <c r="G53" s="0">
-        <v>175.62704568046587</v>
+        <v>175.51518324357809</v>
       </c>
     </row>
     <row r="54">
@@ -1341,22 +1341,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="0">
-        <v>53.381794488972609</v>
+        <v>51.601139599395985</v>
       </c>
       <c r="C54" s="0">
-        <v>162.75265467334185</v>
+        <v>164.62387763937488</v>
       </c>
       <c r="D54" s="0">
-        <v>170.62215404530693</v>
+        <v>170.49995685928755</v>
       </c>
       <c r="E54" s="0">
-        <v>67.248637675426792</v>
+        <v>65.230686241056105</v>
       </c>
       <c r="F54" s="0">
-        <v>66.964173143647642</v>
+        <v>64.929362385160388</v>
       </c>
       <c r="G54" s="0">
-        <v>175.6909538885289</v>
+        <v>175.57683184564948</v>
       </c>
     </row>
     <row r="55">
@@ -1364,22 +1364,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="0">
-        <v>54.370235115899959</v>
+        <v>52.590625843668398</v>
       </c>
       <c r="C55" s="0">
-        <v>162.71316618689838</v>
+        <v>164.58428015536293</v>
       </c>
       <c r="D55" s="0">
-        <v>170.69161184824935</v>
+        <v>170.56740380302091</v>
       </c>
       <c r="E55" s="0">
-        <v>68.372827841961382</v>
+        <v>66.350898369595939</v>
       </c>
       <c r="F55" s="0">
-        <v>68.097506335483317</v>
+        <v>66.059006861671691</v>
       </c>
       <c r="G55" s="0">
-        <v>175.75615650791943</v>
+        <v>175.63972517149654</v>
       </c>
     </row>
     <row r="56">
@@ -1387,22 +1387,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="0">
-        <v>55.358102588080008</v>
+        <v>53.579528701223787</v>
       </c>
       <c r="C56" s="0">
-        <v>162.67370175955577</v>
+        <v>164.5447538184454</v>
       </c>
       <c r="D56" s="0">
-        <v>170.76223707561513</v>
+        <v>170.63595398870558</v>
       </c>
       <c r="E56" s="0">
-        <v>69.499320977135355</v>
+        <v>67.473294747672043</v>
       </c>
       <c r="F56" s="0">
-        <v>69.232994593961635</v>
+        <v>67.190671081354907</v>
       </c>
       <c r="G56" s="0">
-        <v>175.82268439308908</v>
+        <v>175.70388990601629</v>
       </c>
     </row>
     <row r="57">
@@ -1410,22 +1410,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="0">
-        <v>56.345401026647842</v>
+        <v>54.567854315256334</v>
       </c>
       <c r="C57" s="0">
-        <v>162.63423611728356</v>
+        <v>164.50527219367416</v>
       </c>
       <c r="D57" s="0">
-        <v>170.83406815666774</v>
+        <v>170.70564229934195</v>
       </c>
       <c r="E57" s="0">
-        <v>70.628187766562704</v>
+        <v>68.597940020002966</v>
       </c>
       <c r="F57" s="0">
-        <v>70.370717249359515</v>
+        <v>68.324429088117938</v>
       </c>
       <c r="G57" s="0">
-        <v>175.8905707799824</v>
+        <v>175.76935503478913</v>
       </c>
     </row>
     <row r="58">
@@ -1433,22 +1433,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="0">
-        <v>57.332133494314661</v>
+        <v>55.555607685496717</v>
       </c>
       <c r="C58" s="0">
-        <v>162.59474450889439</v>
+        <v>164.4658095273382</v>
       </c>
       <c r="D58" s="0">
-        <v>170.90714560523611</v>
+        <v>170.77650555767258</v>
       </c>
       <c r="E58" s="0">
-        <v>71.759502503874302</v>
+        <v>69.724902118446821</v>
       </c>
       <c r="F58" s="0">
-        <v>71.510756869900291</v>
+        <v>69.460357779147046</v>
       </c>
       <c r="G58" s="0">
-        <v>175.95985134760321</v>
+        <v>175.83615188421226</v>
       </c>
     </row>
     <row r="59">
@@ -1456,22 +1456,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="0">
-        <v>58.318302034087004</v>
+        <v>56.542792718019541</v>
       </c>
       <c r="C59" s="0">
-        <v>162.55520262551957</v>
+        <v>164.42634065665405</v>
       </c>
       <c r="D59" s="0">
-        <v>170.9815121138225</v>
+        <v>170.84858260282329</v>
       </c>
       <c r="E59" s="0">
-        <v>72.893343287941789</v>
+        <v>70.854252435124678</v>
       </c>
       <c r="F59" s="0">
-        <v>72.653199490905621</v>
+        <v>70.598537114545621</v>
       </c>
       <c r="G59" s="0">
-        <v>176.03056429161771</v>
+        <v>175.9043141735344</v>
       </c>
     </row>
     <row r="60">
@@ -1479,22 +1479,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="0">
-        <v>59.303907702505519</v>
+        <v>57.529412268679202</v>
       </c>
       <c r="C60" s="0">
-        <v>162.51558652454924</v>
+        <v>164.38684092518784</v>
       </c>
       <c r="D60" s="0">
-        <v>171.05721265798508</v>
+        <v>170.9219143765072</v>
       </c>
       <c r="E60" s="0">
-        <v>74.029792235186534</v>
+        <v>71.986066008473372</v>
       </c>
       <c r="F60" s="0">
-        <v>73.798134856880751</v>
+        <v>71.739050337232953</v>
       </c>
       <c r="G60" s="0">
-        <v>176.10275041023974</v>
+        <v>175.97387807881484</v>
       </c>
     </row>
     <row r="61">
@@ -1502,22 +1502,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="0">
-        <v>60.288950597805467</v>
+        <v>58.515468180697894</v>
       </c>
       <c r="C61" s="0">
-        <v>162.47587255742874</v>
+        <v>164.34728610327568</v>
       </c>
       <c r="D61" s="0">
-        <v>171.13429461153046</v>
+        <v>170.99654401914944</v>
       </c>
       <c r="E61" s="0">
-        <v>75.168935708325051</v>
+        <v>73.120421723384069</v>
       </c>
       <c r="F61" s="0">
-        <v>74.945656678134114</v>
+        <v>72.881984204559217</v>
       </c>
       <c r="G61" s="0">
-        <v>176.17645320277219</v>
+        <v>176.04488230895947</v>
       </c>
     </row>
     <row r="62">
@@ -1525,22 +1525,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="0">
-        <v>61.273429883345081</v>
+        <v>59.500961316858366</v>
       </c>
       <c r="C62" s="0">
-        <v>162.43603730075867</v>
+        <v>164.30765231278173</v>
       </c>
       <c r="D62" s="0">
-        <v>171.21280787315138</v>
+        <v>171.0725169763862</v>
       </c>
       <c r="E62" s="0">
-        <v>76.310864563034201</v>
+        <v>74.257402526686349</v>
       </c>
       <c r="F62" s="0">
-        <v>76.095862903641148</v>
+        <v>74.027429233166217</v>
       </c>
       <c r="G62" s="0">
-        <v>176.25171898129685</v>
+        <v>176.11736819410407</v>
       </c>
     </row>
     <row r="63">
@@ -1548,22 +1548,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="0">
-        <v>62.257343806596602</v>
+        <v>60.485891586692205</v>
       </c>
       <c r="C63" s="0">
-        <v>162.39605749019398</v>
+        <v>164.2679159555978</v>
       </c>
       <c r="D63" s="0">
-        <v>171.29280500525599</v>
+        <v>171.14988111649151</v>
       </c>
       <c r="E63" s="0">
-        <v>77.45567441416604</v>
+        <v>75.39709565935442</v>
       </c>
       <c r="F63" s="0">
-        <v>77.248856011989702</v>
+        <v>75.175479958715343</v>
       </c>
       <c r="G63" s="0">
-        <v>176.3285969961367</v>
+        <v>176.19137978674098</v>
       </c>
     </row>
     <row r="64">
@@ -1571,22 +1571,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="0">
-        <v>63.240689713950431</v>
+        <v>61.470257968998467</v>
       </c>
       <c r="C64" s="0">
-        <v>162.35590995667934</v>
+        <v>164.22805364534221</v>
       </c>
       <c r="D64" s="0">
-        <v>171.37434138585036</v>
+        <v>171.22868685939034</v>
       </c>
       <c r="E64" s="0">
-        <v>78.603465923311362</v>
+        <v>76.539592906946893</v>
       </c>
       <c r="F64" s="0">
-        <v>78.404743322398318</v>
+        <v>76.326235212216304</v>
       </c>
       <c r="G64" s="0">
-        <v>176.40713957584586</v>
+        <v>176.26696397611019</v>
       </c>
     </row>
     <row r="65">
@@ -1594,22 +1594,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="0">
-        <v>64.223464061541264</v>
+        <v>62.45405852997871</v>
       </c>
       <c r="C65" s="0">
-        <v>162.31557156459024</v>
+        <v>164.18804214176214</v>
       </c>
       <c r="D65" s="0">
-        <v>171.45747537446323</v>
+        <v>171.30898731802557</v>
       </c>
       <c r="E65" s="0">
-        <v>79.754345109699244</v>
+        <v>77.684990869941686</v>
       </c>
       <c r="F65" s="0">
-        <v>79.56363732797081</v>
+        <v>77.479798414822525</v>
       </c>
       <c r="G65" s="0">
-        <v>176.4874022826256</v>
+        <v>176.34417061650191</v>
       </c>
     </row>
     <row r="66">
@@ -1617,22 +1617,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="0">
-        <v>65.205662422268731</v>
+        <v>63.437290437230182</v>
       </c>
       <c r="C66" s="0">
-        <v>162.27501915138077</v>
+        <v>164.14785828738317</v>
       </c>
       <c r="D66" s="0">
-        <v>171.54226849323834</v>
+        <v>171.39083845296565</v>
       </c>
       <c r="E66" s="0">
-        <v>80.908423686636638</v>
+        <v>78.833391255801189</v>
       </c>
       <c r="F66" s="0">
-        <v>80.725656053560101</v>
+        <v>78.636277893117224</v>
       </c>
       <c r="G66" s="0">
-        <v>176.56944408421566</v>
+        <v>176.4230526702554</v>
       </c>
     </row>
     <row r="67">
@@ -1640,22 +1640,22 @@
         <v>65</v>
       </c>
       <c r="B67" s="0">
-        <v>66.187279489150001</v>
+        <v>64.419949969798068</v>
       </c>
       <c r="C67" s="0">
-        <v>162.23422946836058</v>
+        <v>164.10747894598345</v>
       </c>
       <c r="D67" s="0">
-        <v>171.62878562447364</v>
+        <v>171.47429924126794</v>
       </c>
       <c r="E67" s="0">
-        <v>82.065819425933341</v>
+        <v>79.98490119479618</v>
       </c>
       <c r="F67" s="0">
-        <v>81.890923440842045</v>
+        <v>79.795787217093405</v>
       </c>
       <c r="G67" s="0">
-        <v>176.65332754347671</v>
+        <v>176.50366636638063</v>
       </c>
     </row>
     <row r="68">
@@ -1663,22 +1663,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="0">
-        <v>67.168309075111083</v>
+        <v>65.402032524452551</v>
       </c>
       <c r="C68" s="0">
-        <v>162.19317912224449</v>
+        <v>164.06688094249614</v>
       </c>
       <c r="D68" s="0">
-        <v>171.71709522605155</v>
+        <v>171.55943186075336</v>
       </c>
       <c r="E68" s="0">
-        <v>83.22665655303534</v>
+        <v>81.139633581838595</v>
       </c>
       <c r="F68" s="0">
-        <v>83.059569763475764</v>
+        <v>80.958445563242904</v>
       </c>
       <c r="G68" s="0">
-        <v>176.73911902705743</v>
+        <v>176.58607137588572</v>
       </c>
     </row>
     <row r="69">
@@ -1686,22 +1686,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="0">
-        <v>68.148744109293858</v>
+        <v>66.383532618321738</v>
       </c>
       <c r="C69" s="0">
-        <v>162.15184451713256</v>
+        <v>164.02604100396937</v>
       </c>
       <c r="D69" s="0">
-        <v>171.80726956639504</v>
+        <v>171.64630189100231</v>
       </c>
       <c r="E69" s="0">
-        <v>84.391066175900463</v>
+        <v>82.297707446820809</v>
       </c>
       <c r="F69" s="0">
-        <v>84.231732075528441</v>
+        <v>82.12437810540888</v>
       </c>
       <c r="G69" s="0">
-        <v>176.82688893474202</v>
+        <v>176.67033100505793</v>
       </c>
     </row>
     <row r="70">
@@ -1709,22 +1709,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="0">
-        <v>69.128576629927323</v>
+        <v>67.364443887980727</v>
       </c>
       <c r="C70" s="0">
-        <v>162.11020179659056</v>
+        <v>163.98493570122867</v>
       </c>
       <c r="D70" s="0">
-        <v>171.89938498079169</v>
+        <v>171.73497853255296</v>
       </c>
       <c r="E70" s="0">
-        <v>85.559186751005925</v>
+        <v>83.459248356244245</v>
       </c>
       <c r="F70" s="0">
-        <v>85.407554696699407</v>
+        <v>83.293716436333924</v>
       </c>
       <c r="G70" s="0">
-        <v>176.91671195129405</v>
+        <v>176.75651240813298</v>
       </c>
     </row>
     <row r="71">
@@ -1732,22 +1732,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="0">
-        <v>70.107797773785848</v>
+        <v>68.344759085068446</v>
       </c>
       <c r="C71" s="0">
-        <v>162.06822678550876</v>
+        <v>163.94354139090336</v>
       </c>
       <c r="D71" s="0">
-        <v>171.99352215116554</v>
+        <v>171.82553484597651</v>
       </c>
       <c r="E71" s="0">
-        <v>86.731164590281026</v>
+        <v>84.624388849237548</v>
       </c>
       <c r="F71" s="0">
-        <v>86.58718973827753</v>
+        <v>84.466599023149442</v>
       </c>
       <c r="G71" s="0">
-        <v>177.00866732286016</v>
+        <v>176.84468682098901</v>
       </c>
     </row>
     <row r="72">
@@ -1755,22 +1755,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="0">
-        <v>71.086397762230831</v>
+        <v>69.324470068475478</v>
       </c>
       <c r="C72" s="0">
-        <v>162.02589493142062</v>
+        <v>163.90183415748811</v>
       </c>
       <c r="D72" s="0">
-        <v>172.08976641164253</v>
+        <v>171.91804801271633</v>
       </c>
       <c r="E72" s="0">
-        <v>87.907154413218777</v>
+        <v>85.793268911432591</v>
       </c>
       <c r="F72" s="0">
-        <v>87.770797674230977</v>
+        <v>85.643171700418478</v>
       </c>
       <c r="G72" s="0">
-        <v>177.10283916027456</v>
+        <v>176.93492981772874</v>
       </c>
     </row>
     <row r="73">
@@ -1778,22 +1778,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="0">
-        <v>72.064365883806474</v>
+        <v>70.303567793119939</v>
       </c>
       <c r="C73" s="0">
-        <v>161.98318124496706</v>
+        <v>163.85978975511912</v>
       </c>
       <c r="D73" s="0">
-        <v>172.18820808255998</v>
+        <v>172.01259961982154</v>
       </c>
       <c r="E73" s="0">
-        <v>89.087319948943687</v>
+        <v>86.966036490576258</v>
       </c>
       <c r="F73" s="0">
-        <v>88.958547962351531</v>
+        <v>86.823588204751388</v>
       </c>
       <c r="G73" s="0">
-        <v>177.1993167719242</v>
+        <v>177.02732159226633</v>
       </c>
     </row>
     <row r="74">
@@ -1801,22 +1801,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="0">
-        <v>73.04169047333653</v>
+        <v>71.282042295303157</v>
       </c>
       <c r="C74" s="0">
-        <v>161.94006023918695</v>
+        <v>163.81738354874719</v>
       </c>
       <c r="D74" s="0">
-        <v>172.28894283591251</v>
+        <v>172.1092759709791</v>
       </c>
       <c r="E74" s="0">
-        <v>90.271834593616362</v>
+        <v>88.142848058233014</v>
       </c>
       <c r="F74" s="0">
-        <v>90.150619720987663</v>
+        <v>88.008010755494254</v>
       </c>
       <c r="G74" s="0">
-        <v>177.29819502918591</v>
+        <v>177.12194726732076</v>
       </c>
     </row>
     <row r="75">
@@ -1824,22 +1824,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="0">
-        <v>74.018358887442261</v>
+        <v>72.259882674610751</v>
       </c>
       <c r="C75" s="0">
-        <v>161.89650586731378</v>
+        <v>163.7745904543927</v>
       </c>
       <c r="D75" s="0">
-        <v>172.39207209562403</v>
+        <v>172.20816842655918</v>
       </c>
       <c r="E75" s="0">
-        <v>91.460882129241512</v>
+        <v>89.323869222469582</v>
       </c>
       <c r="F75" s="0">
-        <v>91.347202467590577</v>
+        <v>89.196610686528118</v>
       </c>
       <c r="G75" s="0">
-        <v>177.39957476785756</v>
+        <v>177.21889723354244</v>
       </c>
     </row>
     <row r="76">
@@ -1847,22 +1847,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="0">
-        <v>74.99435747637709</v>
+        <v>73.237077072300693</v>
       </c>
       <c r="C76" s="0">
-        <v>161.85249145874781</v>
+        <v>163.73138487816326</v>
       </c>
       <c r="D76" s="0">
-        <v>172.49770347648339</v>
+        <v>172.30937377574156</v>
       </c>
       <c r="E76" s="0">
-        <v>92.654657510739256</v>
+        <v>90.509275397030379</v>
       </c>
       <c r="F76" s="0">
-        <v>92.548496926104917</v>
+        <v>90.389569134841878</v>
       </c>
       <c r="G76" s="0">
-        <v>177.50356322946996</v>
+        <v>177.31826752186058</v>
       </c>
     </row>
     <row r="77">
@@ -1870,22 +1870,22 @@
         <v>75</v>
       </c>
       <c r="B77" s="0">
-        <v>75.969671552047302</v>
+        <v>74.213612646093878</v>
       </c>
       <c r="C77" s="0">
-        <v>161.80798965286425</v>
+        <v>163.68774065371221</v>
       </c>
       <c r="D77" s="0">
-        <v>172.60595126610195</v>
+        <v>172.41299464419782</v>
       </c>
       <c r="E77" s="0">
-        <v>93.853367729049964</v>
+        <v>91.699252533222491</v>
       </c>
       <c r="F77" s="0">
-        <v>93.75471591115533</v>
+        <v>91.587077792257517</v>
       </c>
       <c r="G77" s="0">
-        <v>177.61027454689767</v>
+        <v>177.42016021256444</v>
       </c>
     </row>
     <row r="78">
@@ -1893,22 +1893,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="0">
-        <v>76.94428535205995</v>
+        <v>75.18947554125738</v>
       </c>
       <c r="C78" s="0">
-        <v>161.76297233030408</v>
+        <v>163.6436309778056</v>
       </c>
       <c r="D78" s="0">
-        <v>172.71693695484808</v>
+        <v>172.51913994126497</v>
       </c>
       <c r="E78" s="0">
-        <v>95.057232759095939</v>
+        <v>92.893997921540631</v>
       </c>
       <c r="F78" s="0">
-        <v>94.966085298052519</v>
+        <v>92.789339727511873</v>
       </c>
       <c r="G78" s="0">
-        <v>177.71983027930582</v>
+        <v>177.52468388510275</v>
       </c>
     </row>
     <row r="79">
@@ -1916,22 +1916,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="0">
-        <v>77.918181999611505</v>
+        <v>76.164650857844023</v>
       </c>
       <c r="C79" s="0">
-        <v>161.71741054137556</v>
+        <v>163.59902834365553</v>
       </c>
       <c r="D79" s="0">
-        <v>172.83078981940346</v>
+        <v>172.62792535108113</v>
       </c>
       <c r="E79" s="0">
-        <v>96.266486602641464</v>
+        <v>94.093721071000786</v>
       </c>
       <c r="F79" s="0">
-        <v>96.182845088878992</v>
+        <v>93.996570286847899</v>
       </c>
       <c r="G79" s="0">
-        <v>177.83236000217423</v>
+        <v>177.63195411313765</v>
       </c>
     </row>
     <row r="80">
@@ -1939,22 +1939,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="0">
-        <v>78.891343458999557</v>
+        <v>77.139122613924329</v>
       </c>
       <c r="C80" s="0">
-        <v>161.6712744311771</v>
+        <v>163.55390447166332</v>
       </c>
       <c r="D80" s="0">
-        <v>172.94764756638873</v>
+        <v>172.73947387276888</v>
       </c>
       <c r="E80" s="0">
-        <v>97.481378437506393</v>
+        <v>95.298644675236133</v>
       </c>
       <c r="F80" s="0">
-        <v>97.405250586354427</v>
+        <v>95.208998082373185</v>
       </c>
       <c r="G80" s="0">
-        <v>177.94800195896823</v>
+        <v>177.74209401002253</v>
       </c>
     </row>
     <row r="81">
@@ -1962,22 +1962,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="0">
-        <v>79.863750486508778</v>
+        <v>78.112873704618295</v>
       </c>
       <c r="C81" s="0">
-        <v>161.62453316102432</v>
+        <v>163.50823023719769</v>
       </c>
       <c r="D81" s="0">
-        <v>173.06765704343624</v>
+        <v>172.85391641546207</v>
       </c>
       <c r="E81" s="0">
-        <v>98.702173886238356</v>
+        <v>96.509005675662351</v>
       </c>
       <c r="F81" s="0">
-        <v>98.633573688858277</v>
+        <v>96.426866078715676</v>
       </c>
       <c r="G81" s="0">
-        <v>178.06690378197942</v>
+        <v>177.85523483060237</v>
       </c>
     </row>
     <row r="82">
@@ -1985,22 +1985,22 @@
         <v>80</v>
       </c>
       <c r="B82" s="0">
-        <v>80.835382576385797</v>
+        <v>79.085885856702959</v>
       </c>
       <c r="C82" s="0">
-        <v>161.57715482573852</v>
+        <v>163.46197559501212</v>
       </c>
       <c r="D82" s="0">
-        <v>173.19097502617416</v>
+        <v>172.97139245479795</v>
       </c>
       <c r="E82" s="0">
-        <v>99.92915641926669</v>
+        <v>97.72505643347732</v>
       </c>
       <c r="F82" s="0">
-        <v>99.868104321943093</v>
+        <v>97.650432789991811</v>
       </c>
       <c r="G82" s="0">
-        <v>178.18922329097353</v>
+        <v>177.97151663608258</v>
       </c>
     </row>
     <row r="83">
@@ -2008,22 +2008,22 @@
         <v>81</v>
       </c>
       <c r="B83" s="0">
-        <v>81.806217901582301</v>
+        <v>80.058139578539809</v>
       </c>
       <c r="C83" s="0">
-        <v>161.52910636632075</v>
+        <v>163.41510949988083</v>
       </c>
       <c r="D83" s="0">
-        <v>173.31776909086074</v>
+        <v>173.09205075845745</v>
       </c>
       <c r="E83" s="0">
-        <v>101.16262890981966</v>
+        <v>98.947066023960431</v>
       </c>
       <c r="F83" s="0">
-        <v>101.1091520239729</v>
+        <v>98.879973600832088</v>
       </c>
       <c r="G83" s="0">
-        <v>178.31512937959389</v>
+        <v>178.09108902970172</v>
       </c>
     </row>
     <row r="84">
@@ -2031,22 +2031,22 @@
         <v>82</v>
       </c>
       <c r="B84" s="0">
-        <v>82.776233248902642</v>
+        <v>81.029614105030674</v>
       </c>
       <c r="C84" s="0">
-        <v>161.48035347749695</v>
+        <v>163.36759982300373</v>
       </c>
       <c r="D84" s="0">
-        <v>173.4482185838975</v>
+        <v>173.21605018945599</v>
       </c>
       <c r="E84" s="0">
-        <v>102.40291536052921</v>
+        <v>100.17532166851873</v>
       </c>
       <c r="F84" s="0">
-        <v>102.35704770621543</v>
+        <v>100.11578222722933</v>
       </c>
       <c r="G84" s="0">
-        <v>178.44480300099568</v>
+        <v>178.21411197208928</v>
       </c>
     </row>
     <row r="85">
@@ -2054,22 +2054,22 @@
         <v>83</v>
       </c>
       <c r="B85" s="0">
-        <v>83.745403948149345</v>
+        <v>82.000287337271828</v>
       </c>
       <c r="C85" s="0">
-        <v>161.4308605095795</v>
+        <v>163.31941326369673</v>
       </c>
       <c r="D85" s="0">
-        <v>173.58251570121439</v>
+        <v>173.34356059720272</v>
       </c>
       <c r="E85" s="0">
-        <v>103.65036282477183</v>
+        <v>101.41013032225469</v>
       </c>
       <c r="F85" s="0">
-        <v>103.61214561090326</v>
+        <v>101.3581723353465</v>
       </c>
       <c r="G85" s="0">
-        <v>178.57843826599824</v>
+        <v>178.34075668654361</v>
       </c>
     </row>
     <row r="86">
@@ -2077,22 +2077,22 @@
         <v>84</v>
       </c>
       <c r="B86" s="0">
-        <v>84.713703794809305</v>
+        <v>82.970135776535486</v>
       </c>
       <c r="C86" s="0">
-        <v>161.38059036403985</v>
+        <v>163.27051525584639</v>
       </c>
       <c r="D86" s="0">
-        <v>173.72086669259971</v>
+        <v>173.47476380788726</v>
       </c>
       <c r="E86" s="0">
-        <v>104.90534354948711</v>
+        <v>102.65182043756531</v>
       </c>
       <c r="F86" s="0">
-        <v>104.87482549455025</v>
+        <v>102.60747933921004</v>
       </c>
       <c r="G86" s="0">
-        <v>178.71624366917894</v>
+        <v>178.47120666604303</v>
       </c>
     </row>
     <row r="87">
@@ -2100,22 +2100,22 @@
         <v>85</v>
       </c>
       <c r="B87" s="0">
-        <v>85.681104965770857</v>
+        <v>83.939134452161341</v>
       </c>
       <c r="C87" s="0">
-        <v>161.32950438213368</v>
+        <v>163.22086986856354</v>
       </c>
       <c r="D87" s="0">
-        <v>173.86349320851912</v>
+        <v>173.60985472757505</v>
       </c>
       <c r="E87" s="0">
-        <v>106.16825737060447</v>
+        <v>103.90074392750937</v>
       </c>
       <c r="F87" s="0">
-        <v>106.14549506828575</v>
+        <v>103.86406240150767</v>
       </c>
       <c r="G87" s="0">
-        <v>178.85844346086879</v>
+        <v>178.60565879567855</v>
       </c>
     </row>
     <row r="88">
@@ -2123,22 +2123,22 @@
         <v>86</v>
       </c>
       <c r="B88" s="0">
-        <v>86.647577927500109</v>
+        <v>84.907256842891996</v>
       </c>
       <c r="C88" s="0">
-        <v>161.27756222585708</v>
+        <v>163.17043970042104</v>
       </c>
       <c r="D88" s="0">
-        <v>174.0106338099134</v>
+        <v>173.74904257354439</v>
       </c>
       <c r="E88" s="0">
-        <v>107.43953439743882</v>
+        <v>105.15727835650345</v>
       </c>
       <c r="F88" s="0">
-        <v>107.42459273231312</v>
+        <v>105.1283066656091</v>
       </c>
       <c r="G88" s="0">
-        <v>179.00527918603586</v>
+        <v>178.74432460640136</v>
       </c>
     </row>
     <row r="89">
@@ -2146,22 +2146,22 @@
         <v>87</v>
       </c>
       <c r="B89" s="0">
-        <v>87.613091336040625</v>
+        <v>85.874474791129174</v>
       </c>
       <c r="C89" s="0">
-        <v>161.22472175044291</v>
+        <v>163.119185766605</v>
       </c>
       <c r="D89" s="0">
-        <v>174.16254566498944</v>
+        <v>173.89255225195862</v>
       </c>
       <c r="E89" s="0">
-        <v>108.71963802868245</v>
+        <v>106.42182939044847</v>
       </c>
       <c r="F89" s="0">
-        <v>108.71259064799843</v>
+        <v>106.40062575156838</v>
       </c>
       <c r="G89" s="0">
-        <v>179.15701141466528</v>
+        <v>178.88743167861074</v>
       </c>
     </row>
     <row r="90">
@@ -2169,22 +2169,22 @@
         <v>88</v>
       </c>
       <c r="B90" s="0">
-        <v>88.577611928124227</v>
+        <v>86.840758409528277</v>
       </c>
       <c r="C90" s="0">
-        <v>161.17093886752596</v>
+        <v>163.06706737824476</v>
       </c>
       <c r="D90" s="0">
-        <v>174.31950646124963</v>
+        <v>174.0406259030174</v>
       </c>
       <c r="E90" s="0">
-        <v>110.00906835015179</v>
+        <v>107.69483354381427</v>
       </c>
       <c r="F90" s="0">
-        <v>110.00999819879283</v>
+        <v>107.68146455440267</v>
       </c>
       <c r="G90" s="0">
-        <v>179.31392169259161</v>
+        <v>179.03522521724096</v>
       </c>
     </row>
     <row r="91">
@@ -2192,22 +2192,22 @@
         <v>89</v>
       </c>
       <c r="B91" s="0">
-        <v>89.541104402598933</v>
+        <v>87.806075979279527</v>
       </c>
       <c r="C91" s="0">
-        <v>161.11616739801679</v>
+        <v>163.01404201311516</v>
       </c>
       <c r="D91" s="0">
-        <v>174.48181656611834</v>
+        <v>174.19352463838516</v>
       </c>
       <c r="E91" s="0">
-        <v>111.3083659735435</v>
+        <v>108.97676126770311</v>
       </c>
       <c r="F91" s="0">
-        <v>111.31736590048682</v>
+        <v>108.97130238957941</v>
       </c>
       <c r="G91" s="0">
-        <v>179.4763147469985</v>
+        <v>179.18796982376026</v>
       </c>
     </row>
     <row r="92">
@@ -2215,22 +2215,22 @@
         <v>90</v>
       </c>
       <c r="B92" s="0">
-        <v>90.503531291287686</v>
+        <v>88.7703938393485</v>
       </c>
       <c r="C92" s="0">
-        <v>161.06035891362259</v>
+        <v>162.96006517682358</v>
       </c>
       <c r="D92" s="0">
-        <v>174.64980147571987</v>
+        <v>174.35153050009069</v>
       </c>
       <c r="E92" s="0">
-        <v>112.61811638650018</v>
+        <v>110.26812043073434</v>
       </c>
       <c r="F92" s="0">
-        <v>112.63528983259167</v>
+        <v>110.27065653863363</v>
       </c>
       <c r="G92" s="0">
-        <v>179.64452098717408</v>
+        <v>179.34595149501405</v>
       </c>
     </row>
     <row r="93">
@@ -2238,22 +2238,22 @@
         <v>91</v>
       </c>
       <c r="B93" s="0">
-        <v>91.464852818286133</v>
+        <v>89.733676265864503</v>
       </c>
       <c r="C93" s="0">
-        <v>161.00346256583774</v>
+        <v>162.90509025350147</v>
       </c>
       <c r="D93" s="0">
-        <v>174.8238145989136</v>
+        <v>174.51494867539935</v>
       </c>
       <c r="E93" s="0">
-        <v>113.93895489774461</v>
+        <v>111.56946025404744</v>
       </c>
       <c r="F93" s="0">
-        <v>113.96441667640853</v>
+        <v>111.5800862575046</v>
       </c>
       <c r="G93" s="0">
-        <v>179.81889934887923</v>
+        <v>179.50947988430184</v>
       </c>
     </row>
     <row r="94">
@@ -2261,22 +2261,22 @@
         <v>92</v>
       </c>
       <c r="B94" s="0">
-        <v>92.425026746591413</v>
+        <v>90.695885340749896</v>
       </c>
       <c r="C94" s="0">
-        <v>160.94542490109714</v>
+        <v>162.84906834491733</v>
       </c>
       <c r="D94" s="0">
-        <v>175.00424043294331</v>
+        <v>174.68411000860473</v>
       </c>
       <c r="E94" s="0">
-        <v>115.27157227755697</v>
+        <v>112.88137577319952</v>
       </c>
       <c r="F94" s="0">
-        <v>115.3054494622445</v>
+        <v>112.90019732191786</v>
       </c>
       <c r="G94" s="0">
-        <v>179.99984054021527</v>
+        <v>179.67889086670948</v>
       </c>
     </row>
     <row r="95">
@@ -2284,22 +2284,22 @@
         <v>93</v>
       </c>
       <c r="B95" s="0">
-        <v>93.384008210821207</v>
+        <v>91.65698080857662</v>
       </c>
       <c r="C95" s="0">
-        <v>160.88618966063856</v>
+        <v>162.79194809680874</v>
       </c>
       <c r="D95" s="0">
-        <v>175.19149819845404</v>
+        <v>174.85937385854749</v>
       </c>
       <c r="E95" s="0">
-        <v>116.61672121421933</v>
+        <v>114.2045129137567</v>
       </c>
       <c r="F95" s="0">
-        <v>116.65915414906668</v>
+        <v>114.23164719848323</v>
       </c>
       <c r="G95" s="0">
-        <v>180.18777075861269</v>
+        <v>179.85454945880642</v>
       </c>
     </row>
     <row r="96">
@@ -2307,22 +2307,22 @@
         <v>94</v>
       </c>
       <c r="B96" s="0">
-        <v>94.341749534633038</v>
+        <v>92.616919920516978</v>
       </c>
       <c r="C96" s="0">
-        <v>160.82569756345109</v>
+        <v>162.73367551109891</v>
       </c>
       <c r="D96" s="0">
-        <v>175.38604601574698</v>
+        <v>175.04113136030958</v>
       </c>
       <c r="E96" s="0">
-        <v>117.97522373229535</v>
+        <v>115.53957428458459</v>
       </c>
       <c r="F96" s="0">
-        <v>118.02636718573335</v>
+        <v>115.57515094778779</v>
       </c>
       <c r="G96" s="0">
-        <v>180.3831559631146</v>
+        <v>180.03685315274612</v>
       </c>
     </row>
     <row r="97">
@@ -2330,22 +2330,22 @@
         <v>95</v>
       </c>
       <c r="B97" s="0">
-        <v>95.298200031284011</v>
+        <v>93.575657264119002</v>
       </c>
       <c r="C97" s="0">
-        <v>160.76388607049759</v>
+        <v>162.6741937425119</v>
       </c>
       <c r="D97" s="0">
-        <v>175.58838572174312</v>
+        <v>175.22980916142197</v>
       </c>
       <c r="E97" s="0">
-        <v>119.34797975011136</v>
+        <v>116.88732581408291</v>
       </c>
       <c r="F97" s="0">
-        <v>119.40800423520874</v>
+        <v>116.93148798750462</v>
       </c>
       <c r="G97" s="0">
-        <v>180.58650680427962</v>
+        <v>180.22623573705801</v>
       </c>
     </row>
     <row r="98">
@@ -2353,22 +2353,22 @@
         <v>96</v>
       </c>
       <c r="B98" s="0">
-        <v>96.253305785579187</v>
+        <v>94.533144577484336</v>
       </c>
       <c r="C98" s="0">
-        <v>160.70068912818206</v>
+        <v>162.61344287792713</v>
       </c>
       <c r="D98" s="0">
-        <v>175.79906844921419</v>
+        <v>175.42587371766783</v>
       </c>
       <c r="E98" s="0">
-        <v>120.73597699337464</v>
+        <v>118.2486043809791</v>
       </c>
       <c r="F98" s="0">
-        <v>120.80507028372189</v>
+        <v>118.3015098705435</v>
       </c>
       <c r="G98" s="0">
-        <v>180.79838433681641</v>
+        <v>180.42317169161265</v>
       </c>
     </row>
     <row r="99">
@@ -2376,22 +2376,22 @@
         <v>97</v>
       </c>
       <c r="B99" s="0">
-        <v>97.207009415237721</v>
+        <v>95.489330546252575</v>
       </c>
       <c r="C99" s="0">
-        <v>160.63603688878459</v>
+        <v>162.55135969662098</v>
       </c>
       <c r="D99" s="0">
-        <v>176.01870111774591</v>
+        <v>175.62983625197657</v>
       </c>
       <c r="E99" s="0">
-        <v>122.14030253191775</v>
+        <v>119.62432662424945</v>
       </c>
       <c r="F99" s="0">
-        <v>122.21867140814665</v>
+        <v>119.6861492670287</v>
       </c>
       <c r="G99" s="0">
-        <v>181.01940666887964</v>
+        <v>180.62818126323759</v>
       </c>
     </row>
     <row r="100">
@@ -2399,22 +2399,22 @@
         <v>98</v>
       </c>
       <c r="B100" s="0">
-        <v>98.159249809455943</v>
+        <v>96.444160581598439</v>
       </c>
       <c r="C100" s="0">
-        <v>160.56985540530493</v>
+        <v>162.48787740931798</v>
       </c>
       <c r="D100" s="0">
-        <v>176.24795402142871</v>
+        <v>175.84225850302963</v>
       </c>
       <c r="E100" s="0">
-        <v>123.56215627036066</v>
+        <v>121.01549915818337</v>
       </c>
       <c r="F100" s="0">
-        <v>123.65002854032866</v>
+        <v>121.08643038137384</v>
       </c>
       <c r="G100" s="0">
-        <v>181.25025673866278</v>
+        <v>180.84183635232279</v>
       </c>
     </row>
     <row r="101">
@@ -2422,22 +2422,22 @@
         <v>99</v>
       </c>
       <c r="B101" s="0">
-        <v>99.109961842161795</v>
+        <v>97.397576577223205</v>
       </c>
       <c r="C101" s="0">
-        <v>160.50206629783179</v>
+        <v>162.42292537372208</v>
       </c>
       <c r="D101" s="0">
-        <v>176.48756974386387</v>
+        <v>176.06375941947354</v>
       </c>
       <c r="E101" s="0">
-        <v>125.00286680544964</v>
+        <v>122.42323047111971</v>
       </c>
       <c r="F101" s="0">
-        <v>125.1004936512023</v>
+        <v>122.50348108956386</v>
       </c>
       <c r="G101" s="0">
-        <v>181.49169145606302</v>
+        <v>181.0647673709847</v>
       </c>
     </row>
     <row r="102">
@@ -2445,22 +2445,22 @@
         <v>100</v>
       </c>
       <c r="B102" s="0">
-        <v>100.05907605712781</v>
+        <v>98.349516643066707</v>
       </c>
       <c r="C102" s="0">
-        <v>160.43258638818375</v>
+        <v>162.35642878390723</v>
       </c>
       <c r="D102" s="0">
-        <v>176.73837369007654</v>
+        <v>176.29502299295714</v>
       </c>
       <c r="E102" s="0">
-        <v>126.46391016905957</v>
+        <v>123.84874485341872</v>
       </c>
       <c r="F102" s="0">
-        <v>126.57156888661618</v>
+        <v>123.93854715052859</v>
       </c>
       <c r="G102" s="0">
-        <v>181.74455250824514</v>
+        <v>181.29767127192534</v>
       </c>
     </row>
     <row r="103">
@@ -2468,22 +2468,22 @@
         <v>101</v>
       </c>
       <c r="B103" s="0">
-        <v>101.00651832173456</v>
+        <v>99.299914813171213</v>
       </c>
       <c r="C103" s="0">
-        <v>160.36132729914186</v>
+        <v>162.28830833061406</v>
       </c>
       <c r="D103" s="0">
-        <v>177.00128660199479</v>
+        <v>176.53680747118006</v>
       </c>
       <c r="E103" s="0">
-        <v>127.94693211477228</v>
+        <v>125.29339878650389</v>
       </c>
       <c r="F103" s="0">
-        <v>128.06492932950775</v>
+        <v>125.393008934031</v>
       </c>
       <c r="G103" s="0">
-        <v>182.00977920773008</v>
+        <v>181.54132099672282</v>
       </c>
     </row>
     <row r="104">
@@ -2491,22 +2491,22 @@
         <v>102</v>
       </c>
       <c r="B104" s="0">
-        <v>101.95220944574491</v>
+        <v>100.24870072479412</v>
       </c>
       <c r="C104" s="0">
-        <v>160.28819501410189</v>
+        <v>162.21847982911817</v>
       </c>
       <c r="D104" s="0">
-        <v>177.27733952580201</v>
+        <v>176.789956254337</v>
       </c>
       <c r="E104" s="0">
-        <v>129.45377478945369</v>
+        <v>126.75870033680476</v>
       </c>
       <c r="F104" s="0">
-        <v>129.58245025170251</v>
+        <v>126.86840122250756</v>
       </c>
       <c r="G104" s="0">
-        <v>182.28842386698432</v>
+        <v>181.79657665665812</v>
       </c>
     </row>
     <row r="105">
@@ -2514,22 +2514,22 @@
         <v>103</v>
       </c>
       <c r="B105" s="0">
-        <v>102.89606476095122</v>
+        <v>101.19579926547954</v>
       </c>
       <c r="C105" s="0">
-        <v>160.21308939240913</v>
+        <v>162.14685381089728</v>
       </c>
       <c r="D105" s="0">
-        <v>177.56769183497801</v>
+        <v>177.055410859728</v>
       </c>
       <c r="E105" s="0">
-        <v>130.98650887625163</v>
+        <v>128.24633224519562</v>
       </c>
       <c r="F105" s="0">
-        <v>131.12623997060729</v>
+        <v>128.36643679508748</v>
       </c>
       <c r="G105" s="0">
-        <v>182.58167032404268</v>
+        <v>182.06439884346844</v>
       </c>
     </row>
     <row r="106">
@@ -2537,22 +2537,22 @@
         <v>104</v>
       </c>
       <c r="B106" s="0">
-        <v>103.83799365698171</v>
+        <v>102.14113018435557</v>
       </c>
       <c r="C106" s="0">
-        <v>160.13590363498096</v>
+        <v>162.07333507481917</v>
       </c>
       <c r="D106" s="0">
-        <v>177.87365309557453</v>
+        <v>177.33422644687906</v>
       </c>
       <c r="E106" s="0">
-        <v>132.54747262633222</v>
+        <v>129.75817959677824</v>
       </c>
       <c r="F106" s="0">
-        <v>132.69867976662809</v>
+        <v>129.88903470171974</v>
       </c>
       <c r="G106" s="0">
-        <v>182.89085643342591</v>
+        <v>182.34586457892388</v>
       </c>
     </row>
     <row r="107">
@@ -2560,22 +2560,22 @@
         <v>105</v>
       </c>
       <c r="B107" s="0">
-        <v>104.77789906788453</v>
+        <v>103.08460766341028</v>
       </c>
       <c r="C107" s="0">
-        <v>160.05652369406272</v>
+        <v>161.99782219298749</v>
       </c>
       <c r="D107" s="0">
-        <v>178.1967098097816</v>
+        <v>177.62759053923296</v>
       </c>
       <c r="E107" s="0">
-        <v>134.13931964923432</v>
+        <v>131.2963632157863</v>
       </c>
       <c r="F107" s="0">
-        <v>134.30247278324086</v>
+        <v>131.43835440272116</v>
       </c>
       <c r="G107" s="0">
-        <v>183.21750159593597</v>
+        <v>182.64218656122961</v>
       </c>
     </row>
     <row r="108">
@@ -2583,22 +2583,22 @@
         <v>106</v>
       </c>
       <c r="B108" s="0">
-        <v>105.71567690333258</v>
+        <v>104.02613984390729</v>
       </c>
       <c r="C108" s="0">
-        <v>159.97482762007908</v>
+        <v>161.92020696571024</v>
       </c>
       <c r="D108" s="0">
-        <v>178.53855841920796</v>
+        <v>177.93684577275326</v>
       </c>
       <c r="E108" s="0">
-        <v>135.76507795920634</v>
+        <v>132.86328028230841</v>
       </c>
       <c r="F108" s="0">
-        <v>135.94070447836896</v>
+        <v>133.01683731130447</v>
       </c>
       <c r="G108" s="0">
-        <v>183.56334076024976</v>
+        <v>182.95473656800937</v>
       </c>
     </row>
     <row r="109">
@@ -2606,22 +2606,22 @@
         <v>107</v>
       </c>
       <c r="B109" s="0">
-        <v>106.65121541738709</v>
+        <v>104.96562830241361</v>
       </c>
       <c r="C109" s="0">
-        <v>159.89068483751052</v>
+        <v>161.84037381926854</v>
       </c>
       <c r="D109" s="0">
-        <v>178.90114643452063</v>
+        <v>178.26351776775053</v>
       </c>
       <c r="E109" s="0">
-        <v>137.42822365802789</v>
+        <v>134.46165415010219</v>
       </c>
       <c r="F109" s="0">
-        <v>137.61691810664988</v>
+        <v>134.62725777372683</v>
       </c>
       <c r="G109" s="0">
-        <v>183.93036683466755</v>
+        <v>183.28507415211746</v>
       </c>
     </row>
     <row r="110">
@@ -2629,22 +2629,22 @@
         <v>108</v>
       </c>
       <c r="B110" s="0">
-        <v>107.58439450670242</v>
+        <v>105.90296747011234</v>
       </c>
       <c r="C110" s="0">
-        <v>159.80395534052147</v>
+        <v>161.75819913925412</v>
       </c>
       <c r="D110" s="0">
-        <v>179.28672425106942</v>
+        <v>178.60934958945424</v>
       </c>
       <c r="E110" s="0">
-        <v>139.13277389838566</v>
+        <v>136.09459601581727</v>
       </c>
       <c r="F110" s="0">
-        <v>139.33521001657869</v>
+        <v>136.27278621342589</v>
       </c>
       <c r="G110" s="0">
-        <v>184.32088417011252</v>
+        <v>183.63498215075862</v>
       </c>
     </row>
     <row r="111">
@@ -2652,22 +2652,22 @@
         <v>109</v>
       </c>
       <c r="B111" s="0">
-        <v>108.5150849288151</v>
+        <v>106.8380439881411</v>
       </c>
       <c r="C111" s="0">
-        <v>159.71448879765308</v>
+        <v>161.67355053118041</v>
       </c>
       <c r="D111" s="0">
-        <v>179.69791121787483</v>
+        <v>178.97634478321811</v>
       </c>
       <c r="E111" s="0">
-        <v>140.88340561285648</v>
+        <v>137.76568203737722</v>
       </c>
       <c r="F111" s="0">
-        <v>141.10035144870881</v>
+        <v>137.95706814291</v>
       </c>
       <c r="G111" s="0">
-        <v>184.73757682790895</v>
+        <v>184.00651107056518</v>
       </c>
     </row>
     <row r="112">
@@ -2675,22 +2675,22 @@
         <v>110</v>
       </c>
       <c r="B112" s="0">
-        <v>109.44314742970599</v>
+        <v>107.77073599060496</v>
       </c>
       <c r="C112" s="0">
-        <v>159.62212355323413</v>
+        <v>161.58628599882744</v>
       </c>
       <c r="D112" s="0">
-        <v>180.13778102259036</v>
+        <v>179.3668217159908</v>
       </c>
       <c r="E112" s="0">
-        <v>142.68560923039351</v>
+        <v>139.47905085956273</v>
       </c>
       <c r="F112" s="0">
-        <v>142.91794635164644</v>
+        <v>139.68432415167794</v>
       </c>
       <c r="G112" s="0">
-        <v>185.18359690963362</v>
+        <v>184.4020351892579</v>
       </c>
     </row>
     <row r="113">
@@ -2698,22 +2698,22 @@
         <v>111</v>
       </c>
       <c r="B113" s="0">
-        <v>110.36843176810721</v>
+        <v>108.70091230563638</v>
       </c>
       <c r="C113" s="0">
-        <v>159.5266855112059</v>
+        <v>161.49625302932429</v>
       </c>
       <c r="D113" s="0">
-        <v>180.60997372388795</v>
+        <v>179.78348304436176</v>
       </c>
       <c r="E113" s="0">
-        <v>144.54589076336532</v>
+        <v>141.23952849441233</v>
       </c>
       <c r="F113" s="0">
-        <v>144.79463904066765</v>
+        <v>141.45947803454501</v>
       </c>
       <c r="G113" s="0">
-        <v>185.66268060283338</v>
+        <v>184.82432435177228</v>
       </c>
     </row>
     <row r="114">
@@ -2721,22 +2721,22 @@
         <v>112</v>
       </c>
       <c r="B114" s="0">
-        <v>111.29077562199606</v>
+        <v>109.62843156336821</v>
       </c>
       <c r="C114" s="0">
-        <v>159.4279868847386</v>
+        <v>161.40328757225566</v>
       </c>
       <c r="D114" s="0">
-        <v>181.11884529327443</v>
+        <v>180.22950575172067</v>
       </c>
       <c r="E114" s="0">
-        <v>146.47204213677534</v>
+        <v>143.05279047453081</v>
       </c>
       <c r="F114" s="0">
-        <v>146.73839224907272</v>
+        <v>143.28832329755346</v>
       </c>
       <c r="G114" s="0">
-        <v>186.17930330072414</v>
+        <v>185.27663713582487</v>
       </c>
     </row>
     <row r="115">
@@ -2744,22 +2744,22 @@
         <v>113</v>
       </c>
       <c r="B115" s="0">
-        <v>112.21000336031004</v>
+        <v>110.55314119791397</v>
       </c>
       <c r="C115" s="0">
-        <v>159.32582479227108</v>
+        <v>161.30721289805558</v>
       </c>
       <c r="D115" s="0">
-        <v>181.66967118136566</v>
+        <v>180.70865967046376</v>
       </c>
       <c r="E115" s="0">
-        <v>148.47351004259448</v>
+        <v>144.92557573556806</v>
       </c>
       <c r="F115" s="0">
-        <v>148.75886692668829</v>
+        <v>145.1777429781057</v>
       </c>
       <c r="G115" s="0">
-        <v>186.73889109606091</v>
+        <v>185.76284365350432</v>
       </c>
     </row>
     <row r="116">
@@ -2767,22 +2767,22 @@
         <v>114</v>
       </c>
       <c r="B116" s="0">
-        <v>113.12592466004703</v>
+        <v>111.47487632834799</v>
       </c>
       <c r="C116" s="0">
-        <v>159.21997967732796</v>
+        <v>161.20783831855525</v>
       </c>
       <c r="D116" s="0">
-        <v>182.26892977508854</v>
+        <v>181.22546627497243</v>
       </c>
       <c r="E116" s="0">
-        <v>150.56191086232539</v>
+        <v>146.86597379913709</v>
       </c>
       <c r="F116" s="0">
-        <v>150.86795307561073</v>
+        <v>147.13600509225071</v>
       </c>
       <c r="G116" s="0">
-        <v>187.34811579865524</v>
+        <v>186.28759031714816</v>
       </c>
     </row>
     <row r="117">
@@ -2790,22 +2790,22 @@
         <v>115</v>
       </c>
       <c r="B117" s="0">
-        <v>114.0383329454867</v>
+        <v>112.39345850118509</v>
       </c>
       <c r="C117" s="0">
-        <v>159.11021352555551</v>
+        <v>161.10495774970463</v>
       </c>
       <c r="D117" s="0">
-        <v>182.9247076748658</v>
+        <v>181.78541576562785</v>
       </c>
       <c r="E117" s="0">
-        <v>152.75176891390666</v>
+        <v>148.88381831468428</v>
       </c>
       <c r="F117" s="0">
-        <v>153.08053183450315</v>
+        <v>149.17316794598969</v>
       </c>
       <c r="G117" s="0">
-        <v>188.01531758090204</v>
+        <v>186.85652545362649</v>
       </c>
     </row>
     <row r="118">
@@ -2813,22 +2813,22 @@
         <v>116</v>
       </c>
       <c r="B118" s="0">
-        <v>114.94700362215593</v>
+        <v>113.30869427388701</v>
       </c>
       <c r="C118" s="0">
-        <v>158.99626784772104</v>
+        <v>160.99834809309607</v>
       </c>
       <c r="D118" s="0">
-        <v>183.64729754982437</v>
+        <v>182.39527085089173</v>
       </c>
       <c r="E118" s="0">
-        <v>155.06160872881685</v>
+        <v>150.99123919836379</v>
       </c>
       <c r="F118" s="0">
-        <v>155.41560473642125</v>
+        <v>151.30164948324193</v>
       </c>
       <c r="G118" s="0">
-        <v>188.75112986014705</v>
+        <v>187.47661559549991</v>
       </c>
     </row>
     <row r="119">
@@ -2836,22 +2836,22 @@
         <v>117</v>
       </c>
       <c r="B119" s="0">
-        <v>115.85169207320543</v>
+        <v>114.22037361536836</v>
       </c>
       <c r="C119" s="0">
-        <v>158.87786139176313</v>
+        <v>160.88776740885945</v>
       </c>
       <c r="D119" s="0">
-        <v>184.45011383376874</v>
+        <v>183.06350362288657</v>
       </c>
       <c r="E119" s="0">
-        <v>157.51563335293881</v>
+        <v>153.20345889736177</v>
       </c>
       <c r="F119" s="0">
-        <v>157.89803183437977</v>
+        <v>153.53704949800658</v>
       </c>
       <c r="G119" s="0">
-        <v>189.56943885537379</v>
+        <v>188.15660127404922</v>
       </c>
     </row>
     <row r="120">
@@ -2859,22 +2859,22 @@
         <v>118</v>
       </c>
       <c r="B120" s="0">
-        <v>116.75213137987312</v>
+        <v>115.12826809520605</v>
       </c>
       <c r="C120" s="0">
-        <v>158.75468754013511</v>
+        <v>160.77295284762502</v>
       </c>
       <c r="D120" s="0">
-        <v>185.35116123838796</v>
+        <v>183.80094452160355</v>
       </c>
       <c r="E120" s="0">
-        <v>160.14642503190765</v>
+        <v>155.53997877665805</v>
       </c>
       <c r="F120" s="0">
-        <v>160.56133423387485</v>
+        <v>155.89937658982478</v>
       </c>
       <c r="G120" s="0">
-        <v>190.48892701499688</v>
+        <v>188.90767565135192</v>
       </c>
     </row>
     <row r="121">
@@ -2882,22 +2882,22 @@
         <v>119</v>
       </c>
       <c r="B121" s="0">
-        <v>117.64802972043061</v>
+        <v>116.03212882811197</v>
       </c>
       <c r="C121" s="0">
-        <v>158.62641134037344</v>
+        <v>160.65361830337537</v>
       </c>
       <c r="D121" s="0">
-        <v>186.37552963085665</v>
+        <v>184.62178473459272</v>
       </c>
       <c r="E121" s="0">
-        <v>162.99955010994069</v>
+        <v>158.02641754965416</v>
       </c>
       <c r="F121" s="0">
-        <v>163.45248378297185</v>
+        <v>158.41495284220554</v>
       </c>
       <c r="G121" s="0">
-        <v>191.53570428450041</v>
+        <v>189.74453552112925</v>
       </c>
     </row>
     <row r="122">
@@ -2905,22 +2905,22 @@
         <v>120</v>
       </c>
       <c r="B122" s="0">
-        <v>118.53906739312775</v>
+        <v>116.93168413400004</v>
       </c>
       <c r="C122" s="0">
-        <v>158.49266610667453</v>
+        <v>160.5294517418956</v>
       </c>
       <c r="D122" s="0">
-        <v>187.55996091887258</v>
+        <v>185.54520067347099</v>
       </c>
       <c r="E122" s="0">
-        <v>166.14202085667907</v>
+        <v>160.69750090310529</v>
       </c>
       <c r="F122" s="0">
-        <v>166.64072884992643</v>
+        <v>161.11951754370057</v>
       </c>
       <c r="G122" s="0">
-        <v>192.74814458065512</v>
+        <v>190.68708976602409</v>
       </c>
     </row>
   </sheetData>
@@ -2936,8 +2936,8 @@
     <col min="2" max="2" width="12.7109375" customWidth="true"/>
     <col min="3" max="3" width="14.42578125" customWidth="true"/>
     <col min="4" max="4" width="15.42578125" customWidth="true"/>
-    <col min="5" max="5" width="11.7109375" customWidth="true"/>
-    <col min="6" max="6" width="11.7109375" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="12.7109375" customWidth="true"/>
     <col min="7" max="7" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -2969,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="0">
-        <v>1.4205396685462923</v>
+        <v>1.1053961852920269</v>
       </c>
       <c r="C2" s="0">
-        <v>-0.5318085172656335</v>
+        <v>-0.73108400410158392</v>
       </c>
       <c r="D2" s="0">
-        <v>-0.17438587552389936</v>
+        <v>-0.3137048344601952</v>
       </c>
       <c r="E2" s="0">
-        <v>1.1406920947711829</v>
+        <v>0.68240353024800893</v>
       </c>
       <c r="F2" s="0">
-        <v>1.3424187817582605</v>
+        <v>0.94905985786607616</v>
       </c>
       <c r="G2" s="0">
-        <v>-0.32923937500993555</v>
+        <v>-0.5197496606107338</v>
       </c>
     </row>
     <row r="3">
@@ -2992,22 +2992,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>1.3081946784264154</v>
+        <v>0.7935165335391956</v>
       </c>
       <c r="C3" s="0">
-        <v>-0.39963720244609591</v>
+        <v>-0.36388291029674058</v>
       </c>
       <c r="D3" s="0">
-        <v>-0.1104449415544156</v>
+        <v>-0.1349121788165229</v>
       </c>
       <c r="E3" s="0">
-        <v>1.1102194209087912</v>
+        <v>0.59381463281292957</v>
       </c>
       <c r="F3" s="0">
-        <v>1.2641792716387241</v>
+        <v>0.7297979088558646</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.22823119356760257</v>
+        <v>-0.23958665312977981</v>
       </c>
     </row>
     <row r="4">
@@ -3015,22 +3015,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="0">
-        <v>1.2404322147107618</v>
+        <v>0.69620869080210712</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.31996448415597761</v>
+        <v>-0.2493586392617122</v>
       </c>
       <c r="D4" s="0">
-        <v>-0.072358599425942666</v>
+        <v>-0.079161498775354278</v>
       </c>
       <c r="E4" s="0">
-        <v>1.0930567138919551</v>
+        <v>0.56645930882123297</v>
       </c>
       <c r="F4" s="0">
-        <v>1.2178857110805383</v>
+        <v>0.66136456769145213</v>
       </c>
       <c r="G4" s="0">
-        <v>-0.16753234052385843</v>
+        <v>-0.15196517434275597</v>
       </c>
     </row>
     <row r="5">
@@ -3038,22 +3038,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="0">
-        <v>1.1947777137945586</v>
+        <v>0.64605819962556077</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.26632711029698181</v>
+        <v>-0.19036416178350249</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.047093850667002356</v>
+        <v>-0.050680960330107029</v>
       </c>
       <c r="E5" s="0">
-        <v>1.0825117349035931</v>
+        <v>0.55301508552164902</v>
       </c>
       <c r="F5" s="0">
-        <v>1.1874641346020323</v>
+        <v>0.62655384804689795</v>
       </c>
       <c r="G5" s="0">
-        <v>-0.12683294375888538</v>
+        <v>-0.10690324339658205</v>
       </c>
     </row>
     <row r="6">
@@ -3061,22 +3061,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="0">
-        <v>1.1618472646798021</v>
+        <v>0.61496909770875641</v>
       </c>
       <c r="C6" s="0">
-        <v>-0.22767625046095688</v>
+        <v>-0.15381582733898355</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.029184799724117985</v>
+        <v>-0.033257925898228707</v>
       </c>
       <c r="E6" s="0">
-        <v>1.0757438885594486</v>
+        <v>0.5452702647267722</v>
       </c>
       <c r="F6" s="0">
-        <v>1.1661637353514114</v>
+        <v>0.60541146610359076</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.097634296612806357</v>
+        <v>-0.079079782501584206</v>
       </c>
     </row>
     <row r="7">
@@ -3084,22 +3084,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="0">
-        <v>1.1369621502619649</v>
+        <v>0.59368332184386308</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.19850330921574649</v>
+        <v>-0.1288125937336137</v>
       </c>
       <c r="D7" s="0">
-        <v>-0.015898841618254153</v>
+        <v>-0.021518099933649705</v>
       </c>
       <c r="E7" s="0">
-        <v>1.0713229146350709</v>
+        <v>0.5404574197686981</v>
       </c>
       <c r="F7" s="0">
-        <v>1.1506069397735723</v>
+        <v>0.59130676451422037</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.075693463084124543</v>
+        <v>-0.060124034412439173</v>
       </c>
     </row>
     <row r="8">
@@ -3107,22 +3107,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="0">
-        <v>1.1175063876176812</v>
+        <v>0.57816545453802604</v>
       </c>
       <c r="C8" s="0">
-        <v>-0.17572842948919218</v>
+        <v>-0.1106031092431268</v>
       </c>
       <c r="D8" s="0">
-        <v>-0.0057064534249419256</v>
+        <v>-0.01310936651977958</v>
       </c>
       <c r="E8" s="0">
-        <v>1.0684461538652157</v>
+        <v>0.53735196790426332</v>
       </c>
       <c r="F8" s="0">
-        <v>1.1389024410152437</v>
+        <v>0.58133413733486095</v>
       </c>
       <c r="G8" s="0">
-        <v>-0.058636567685930605</v>
+        <v>-0.04638006701304935</v>
       </c>
     </row>
     <row r="9">
@@ -3130,22 +3130,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="0">
-        <v>1.1018944134567792</v>
+        <v>0.56634913324832614</v>
       </c>
       <c r="C9" s="0">
-        <v>-0.15748497608692591</v>
+        <v>-0.09675451468361522</v>
       </c>
       <c r="D9" s="0">
-        <v>0.002319016529956198</v>
+        <v>-0.0068244525056657046</v>
       </c>
       <c r="E9" s="0">
-        <v>1.0666281093502899</v>
+        <v>0.53532146350692911</v>
       </c>
       <c r="F9" s="0">
-        <v>1.1299042056438071</v>
+        <v>0.57400120544750721</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.045024636886110671</v>
+        <v>-0.035973646101496365</v>
       </c>
     </row>
     <row r="10">
@@ -3153,22 +3153,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="0">
-        <v>1.0891056842270139</v>
+        <v>0.55705768122253863</v>
       </c>
       <c r="C10" s="0">
-        <v>-0.14257155658449577</v>
+        <v>-0.085881493502974485</v>
       </c>
       <c r="D10" s="0">
-        <v>0.0087729015608279375</v>
+        <v>-0.0019753522316198419</v>
       </c>
       <c r="E10" s="0">
-        <v>1.0655586426561336</v>
+        <v>0.53400485373691109</v>
       </c>
       <c r="F10" s="0">
-        <v>1.1228759776979742</v>
+        <v>0.56845718286231983</v>
       </c>
       <c r="G10" s="0">
-        <v>-0.033931820025353568</v>
+        <v>-0.027836929102199013</v>
       </c>
     </row>
     <row r="11">
@@ -3176,22 +3176,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="0">
-        <v>1.0784520031738904</v>
+        <v>0.54956830109721022</v>
       </c>
       <c r="C11" s="0">
-        <v>-0.13017807001557566</v>
+        <v>-0.07713312676493489</v>
       </c>
       <c r="D11" s="0">
-        <v>0.014055391281732438</v>
+        <v>0.0018602493089741956</v>
       </c>
       <c r="E11" s="0">
-        <v>1.0650312823839132</v>
+        <v>0.53318105765109991</v>
       </c>
       <c r="F11" s="0">
-        <v>1.1173229546772976</v>
+        <v>0.56417976756373189</v>
       </c>
       <c r="G11" s="0">
-        <v>-0.024734269612143367</v>
+        <v>-0.021313967882925972</v>
       </c>
     </row>
     <row r="12">
@@ -3199,22 +3199,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="0">
-        <v>1.069451689440841</v>
+        <v>0.54341098002385979</v>
       </c>
       <c r="C12" s="0">
-        <v>-0.11973755562366493</v>
+        <v>-0.069956117730738093</v>
       </c>
       <c r="D12" s="0">
-        <v>0.018445362637663054</v>
+        <v>0.0049563880430597007</v>
       </c>
       <c r="E12" s="0">
-        <v>1.0649040929078344</v>
+        <v>0.53270754733047943</v>
       </c>
       <c r="F12" s="0">
-        <v>1.1129004933547939</v>
+        <v>0.56083006606233976</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.016995855574658957</v>
+        <v>-0.015978414188021626</v>
       </c>
     </row>
     <row r="13">
@@ -3222,22 +3222,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="0">
-        <v>1.0617571817755134</v>
+        <v>0.53826619213786364</v>
       </c>
       <c r="C13" s="0">
-        <v>-0.11084095639647405</v>
+        <v>-0.063974346323558418</v>
       </c>
       <c r="D13" s="0">
-        <v>0.022142943636934177</v>
+        <v>0.0074987245340991165</v>
       </c>
       <c r="E13" s="0">
-        <v>1.0650769961521587</v>
+        <v>0.53248876458036765</v>
       </c>
       <c r="F13" s="0">
-        <v>1.1093614640370804</v>
+        <v>0.55817854112707621</v>
       </c>
       <c r="G13" s="0">
-        <v>-0.0104023608548041</v>
+        <v>-0.011540678589397148</v>
       </c>
     </row>
     <row r="14">
@@ -3245,22 +3245,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="0">
-        <v>1.0551112440993096</v>
+        <v>0.53390882215974356</v>
       </c>
       <c r="C14" s="0">
-        <v>-0.10318555828267803</v>
+        <v>-0.058922845969028401</v>
       </c>
       <c r="D14" s="0">
-        <v>0.02529529891963584</v>
+        <v>0.0096174613210811243</v>
       </c>
       <c r="E14" s="0">
-        <v>1.0654779807121022</v>
+        <v>0.53245865397722703</v>
       </c>
       <c r="F14" s="0">
-        <v>1.1065243497590351</v>
+        <v>0.55606430611459101</v>
       </c>
       <c r="G14" s="0">
-        <v>-0.0047216512657987314</v>
+        <v>-0.0077969905539925482</v>
       </c>
     </row>
     <row r="15">
@@ -3268,22 +3268,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="0">
-        <v>1.049319351179989</v>
+        <v>0.53017555010098594</v>
       </c>
       <c r="C15" s="0">
-        <v>-0.096542479449260296</v>
+        <v>-0.054609403820691536</v>
       </c>
       <c r="D15" s="0">
-        <v>0.028012903345590093</v>
+        <v>0.011406524780865637</v>
       </c>
       <c r="E15" s="0">
-        <v>1.0660543782326986</v>
+        <v>0.53257043369274404</v>
       </c>
       <c r="F15" s="0">
-        <v>1.1042531089637611</v>
+        <v>0.55437139836383253</v>
       </c>
       <c r="G15" s="0">
-        <v>0.00022144957244730803</v>
+        <v>-0.0045997489712738112</v>
       </c>
     </row>
     <row r="16">
@@ -3291,22 +3291,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="0">
-        <v>1.044231657980659</v>
+        <v>0.52694494484271603</v>
       </c>
       <c r="C16" s="0">
-        <v>-0.090735442935057892</v>
+        <v>-0.050891124292198275</v>
       </c>
       <c r="D16" s="0">
-        <v>0.030380171274155619</v>
+        <v>0.012935288400640756</v>
       </c>
       <c r="E16" s="0">
-        <v>1.0667671609911584</v>
+        <v>0.53279032190789088</v>
       </c>
       <c r="F16" s="0">
-        <v>1.1024440198546688</v>
+        <v>0.55301427502530276</v>
       </c>
       <c r="G16" s="0">
-        <v>0.0045615696082964554</v>
+        <v>-0.0018394159258020343</v>
       </c>
     </row>
     <row r="17">
@@ -3314,22 +3314,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="0">
-        <v>1.039730870443228</v>
+        <v>0.52412481835356528</v>
       </c>
       <c r="C17" s="0">
-        <v>-0.085626497289597606</v>
+        <v>-0.047659541052771114</v>
       </c>
       <c r="D17" s="0">
-        <v>0.032462605143100204</v>
+        <v>0.014256025984186588</v>
       </c>
       <c r="E17" s="0">
-        <v>1.0675871096680409</v>
+        <v>0.53309354033185097</v>
       </c>
       <c r="F17" s="0">
-        <v>1.1010168309646795</v>
+        <v>0.55192858990185567</v>
       </c>
       <c r="G17" s="0">
-        <v>0.0084038278994380197</v>
+        <v>0.00056698986735732372</v>
       </c>
     </row>
     <row r="18">
@@ -3337,22 +3337,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="0">
-        <v>1.0357238732945517</v>
+        <v>0.52164391624259454</v>
       </c>
       <c r="C18" s="0">
-        <v>-0.081106160439336425</v>
+        <v>-0.044830834416015167</v>
       </c>
       <c r="D18" s="0">
-        <v>0.034311725758947781</v>
+        <v>0.015408810155094724</v>
       </c>
       <c r="E18" s="0">
-        <v>1.0684921763689588</v>
+        <v>0.53346168631083191</v>
       </c>
       <c r="F18" s="0">
-        <v>1.0999086566608121</v>
+        <v>0.5510651304215024</v>
       </c>
       <c r="G18" s="0">
-        <v>0.011831454102326725</v>
+        <v>0.0026834555710630514</v>
       </c>
     </row>
     <row r="19">
@@ -3360,22 +3360,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="0">
-        <v>1.0321358197306174</v>
+        <v>0.51944629746616977</v>
       </c>
       <c r="C19" s="0">
-        <v>-0.07708646194313297</v>
+        <v>-0.042339214764028313</v>
       </c>
       <c r="D19" s="0">
-        <v>0.035968548018943405</v>
+        <v>0.01642482439221888</v>
       </c>
       <c r="E19" s="0">
-        <v>1.0694656328128669</v>
+        <v>0.53388095789734291</v>
       </c>
       <c r="F19" s="0">
-        <v>1.0990696729401823</v>
+        <v>0.55038571741405629</v>
       </c>
       <c r="G19" s="0">
-        <v>0.014911166179627145</v>
+        <v>0.0045600895886411356</v>
       </c>
     </row>
     <row r="20">
@@ -3383,22 +3383,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="0">
-        <v>1.0289058755961169</v>
+        <v>0.51748743649811802</v>
       </c>
       <c r="C20" s="0">
-        <v>-0.073495933077941569</v>
+        <v>-0.04013233386116262</v>
       </c>
       <c r="D20" s="0">
-        <v>0.037466078833765612</v>
+        <v>0.017328657887537832</v>
       </c>
       <c r="E20" s="0">
-        <v>1.0704947467497272</v>
+        <v>0.53434092723444637</v>
       </c>
       <c r="F20" s="0">
-        <v>1.0984600237304787</v>
+        <v>0.54986036360703294</v>
       </c>
       <c r="G20" s="0">
-        <v>0.017697041214467631</v>
+        <v>0.006236668839181227</v>
       </c>
     </row>
     <row r="21">
@@ -3406,22 +3406,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="0">
-        <v>1.0259841005563679</v>
+        <v>0.51573146020454153</v>
       </c>
       <c r="C21" s="0">
-        <v>-0.070275935488633007</v>
+        <v>-0.038168032061883253</v>
       </c>
       <c r="D21" s="0">
-        <v>0.038831143192801593</v>
+        <v>0.018139929920578463</v>
       </c>
       <c r="E21" s="0">
-        <v>1.0715698212470319</v>
+        <v>0.53483367594973452</v>
       </c>
       <c r="F21" s="0">
-        <v>1.0980475591805652</v>
+        <v>0.54946526200506762</v>
       </c>
       <c r="G21" s="0">
-        <v>0.020233350568683861</v>
+        <v>0.0077451527206522626</v>
       </c>
     </row>
     <row r="22">
@@ -3429,22 +3429,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="0">
-        <v>1.0233291262972837</v>
+        <v>0.51414915087159974</v>
       </c>
       <c r="C22" s="0">
-        <v>-0.067377928160509512</v>
+        <v>-0.036411987505430406</v>
       </c>
       <c r="D22" s="0">
-        <v>0.04008573952920929</v>
+        <v>0.018874461438164229</v>
       </c>
       <c r="E22" s="0">
-        <v>1.0726834878804379</v>
+        <v>0.53535317516810754</v>
       </c>
       <c r="F22" s="0">
-        <v>1.0978061570313491</v>
+        <v>0.54918133485439513</v>
       </c>
       <c r="G22" s="0">
-        <v>0.022556669065275283</v>
+        <v>0.0091114992511372589</v>
       </c>
     </row>
     <row r="23">
@@ -3452,22 +3452,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="0">
-        <v>1.0209064034652742</v>
+        <v>0.51271647793634179</v>
       </c>
       <c r="C23" s="0">
-        <v>-0.064761403953191451</v>
+        <v>-0.034835987743720695</v>
       </c>
       <c r="D23" s="0">
-        <v>0.041248059541197306</v>
+        <v>0.019545134244630173</v>
       </c>
       <c r="E23" s="0">
-        <v>1.0738301805094464</v>
+        <v>0.53589483421688178</v>
       </c>
       <c r="F23" s="0">
-        <v>1.0977144597988937</v>
+        <v>0.54899316947684318</v>
       </c>
       <c r="G23" s="0">
-        <v>0.024697466205693443</v>
+        <v>0.01035699962612404</v>
       </c>
     </row>
     <row r="24">
@@ -3475,22 +3475,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="0">
-        <v>1.0186868610015023</v>
+        <v>0.51141350171498734</v>
       </c>
       <c r="C24" s="0">
-        <v>-0.062392311633973283</v>
+        <v>-0.033416639312756603</v>
       </c>
       <c r="D24" s="0">
-        <v>0.042333265059052286</v>
+        <v>0.020162530538258089</v>
       </c>
       <c r="E24" s="0">
-        <v>1.0750057393766435</v>
+        <v>0.53645516777161939</v>
       </c>
       <c r="F24" s="0">
-        <v>1.0977549131616122</v>
+        <v>0.54888822621958866</v>
       </c>
       <c r="G24" s="0">
-        <v>0.026681321910176213</v>
+        <v>0.011499273946921611</v>
       </c>
     </row>
     <row r="25">
@@ -3498,22 +3498,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="0">
-        <v>1.0166458688753375</v>
+        <v>0.5102235434668142</v>
       </c>
       <c r="C25" s="0">
-        <v>-0.060241835094820471</v>
+        <v>-0.032134390853209419</v>
       </c>
       <c r="D25" s="0">
-        <v>0.043354086504647393</v>
+        <v>0.020735415355356071</v>
       </c>
       <c r="E25" s="0">
-        <v>1.0762071104962965</v>
+        <v>0.53703154749790583</v>
       </c>
       <c r="F25" s="0">
-        <v>1.0979130256398342</v>
+        <v>0.54885624109269848</v>
       </c>
       <c r="G25" s="0">
-        <v>0.02852986612908966</v>
+        <v>0.012553024401345952</v>
       </c>
     </row>
     <row r="26">
@@ -3521,22 +3521,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="0">
-        <v>1.0147624269965811</v>
+        <v>0.5091325491618508</v>
       </c>
       <c r="C26" s="0">
-        <v>-0.058285438845486315</v>
+        <v>-0.030972784272700522</v>
       </c>
       <c r="D26" s="0">
-        <v>0.044321288658355378</v>
+        <v>0.021271104936162019</v>
       </c>
       <c r="E26" s="0">
-        <v>1.0774321155429867</v>
+        <v>0.53762201483826555</v>
       </c>
       <c r="F26" s="0">
-        <v>1.0981767929593975</v>
+        <v>0.54888876984916235</v>
       </c>
       <c r="G26" s="0">
-        <v>0.030261512715225265</v>
+        <v>0.013530612093043673</v>
       </c>
     </row>
     <row r="27">
@@ -3544,22 +3544,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="0">
-        <v>1.0130185247876562</v>
+        <v>0.50812859614778627</v>
       </c>
       <c r="C27" s="0">
-        <v>-0.05650211442424468</v>
+        <v>-0.02991787413963173</v>
       </c>
       <c r="D27" s="0">
-        <v>0.045244036579976797</v>
+        <v>0.021775751097755827</v>
       </c>
       <c r="E27" s="0">
-        <v>1.0786792744610112</v>
+        <v>0.53822513861679488</v>
       </c>
       <c r="F27" s="0">
-        <v>1.0985362464178101</v>
+        <v>0.54897883625912503</v>
       </c>
       <c r="G27" s="0">
-        <v>0.03189203816415908</v>
+        <v>0.014442503828211146</v>
       </c>
     </row>
     <row r="28">
@@ -3567,22 +3567,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="0">
-        <v>1.0113986309589651</v>
+        <v>0.50720150661239671</v>
       </c>
       <c r="C28" s="0">
-        <v>-0.054873780099931331</v>
+        <v>-0.028957772805692689</v>
       </c>
       <c r="D28" s="0">
-        <v>0.046130185596715195</v>
+        <v>0.022254562985374857</v>
       </c>
       <c r="E28" s="0">
-        <v>1.0799476678854603</v>
+        <v>0.53883990587607367</v>
       </c>
       <c r="F28" s="0">
-        <v>1.0989830956306659</v>
+        <v>0.54912065811333577</v>
       </c>
       <c r="G28" s="0">
-        <v>0.03343504209699931</v>
+        <v>0.015297621769924009</v>
       </c>
     </row>
     <row r="29">
@@ -3590,22 +3590,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="0">
-        <v>1.0098892836397586</v>
+        <v>0.5063425418118126</v>
       </c>
       <c r="C29" s="0">
-        <v>-0.053384798728766419</v>
+        <v>-0.028082290614177746</v>
       </c>
       <c r="D29" s="0">
-        <v>0.046986512978564009</v>
+        <v>0.022711981599562184</v>
       </c>
       <c r="E29" s="0">
-        <v>1.0812368298970598</v>
+        <v>0.53946563761587274</v>
       </c>
       <c r="F29" s="0">
-        <v>1.099510443827995</v>
+        <v>0.54930943188488868</v>
       </c>
       <c r="G29" s="0">
-        <v>0.034902316685585508</v>
+        <v>0.016103619686689923</v>
       </c>
     </row>
     <row r="30">
@@ -3613,22 +3613,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="0">
-        <v>1.008478758591431</v>
+        <v>0.50554415804814834</v>
       </c>
       <c r="C30" s="0">
-        <v>-0.052021587546714119</v>
+        <v>-0.027282648807706794</v>
       </c>
       <c r="D30" s="0">
-        <v>0.047818904429769764</v>
+        <v>0.023151818336827453</v>
       </c>
       <c r="E30" s="0">
-        <v>1.0825466640810169</v>
+        <v>0.54010192337107044</v>
       </c>
       <c r="F30" s="0">
-        <v>1.1001125594336474</v>
+        <v>0.54954116212816995</v>
       </c>
       <c r="G30" s="0">
-        <v>0.036304145312771881</v>
+        <v>0.01686710312728399</v>
       </c>
     </row>
     <row r="31">
@@ -3636,22 +3636,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="0">
-        <v>1.0071567987063414</v>
+        <v>0.50479981033372889</v>
       </c>
       <c r="C31" s="0">
-        <v>-0.050772300124994285</v>
+        <v>-0.026551248580795845</v>
       </c>
       <c r="D31" s="0">
-        <v>0.048632505279231943</v>
+        <v>0.0235773658433024</v>
       </c>
       <c r="E31" s="0">
-        <v>1.0838773776274904</v>
+        <v>0.54074857016825162</v>
       </c>
       <c r="F31" s="0">
-        <v>1.1007846916825983</v>
+        <v>0.54981252533229308</v>
       </c>
       <c r="G31" s="0">
-        <v>0.037649545766411441</v>
+        <v>0.017593806336683789</v>
       </c>
     </row>
     <row r="32">
@@ -3659,22 +3659,22 @@
         <v>30</v>
       </c>
       <c r="B32" s="0">
-        <v>1.0059143920004901</v>
+        <v>0.50410379322508303</v>
       </c>
       <c r="C32" s="0">
-        <v>-0.049626565431542313</v>
+        <v>-0.025881483897209439</v>
       </c>
       <c r="D32" s="0">
-        <v>0.049431843880541122</v>
+        <v>0.023991487378355114</v>
       </c>
       <c r="E32" s="0">
-        <v>1.0852294295010117</v>
+        <v>0.54140556254622496</v>
       </c>
       <c r="F32" s="0">
-        <v>1.1015229209713706</v>
+        <v>0.55012076055072701</v>
       </c>
       <c r="G32" s="0">
-        <v>0.038946469613528316</v>
+        <v>0.018288735494278726</v>
       </c>
     </row>
     <row r="33">
@@ -3682,22 +3682,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="0">
-        <v>1.0047435882694582</v>
+        <v>0.50345111087960692</v>
       </c>
       <c r="C33" s="0">
-        <v>-0.04857527242715224</v>
+        <v>-0.025267588717264557</v>
       </c>
       <c r="D33" s="0">
-        <v>0.050220932980393707</v>
+        <v>0.024396689362170119</v>
       </c>
       <c r="E33" s="0">
-        <v>1.0866034896566947</v>
+        <v>0.54207303115476946</v>
       </c>
       <c r="F33" s="0">
-        <v>1.1023240368095335</v>
+        <v>0.55046358101595894</v>
       </c>
       <c r="G33" s="0">
-        <v>0.040201966701352197</v>
+        <v>0.018956285512085749</v>
       </c>
     </row>
     <row r="34">
@@ -3705,22 +3705,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="0">
-        <v>1.0036373467882247</v>
+        <v>0.50283737027143083</v>
       </c>
       <c r="C34" s="0">
-        <v>-0.047610391228186076</v>
+        <v>-0.024704511497762927</v>
       </c>
       <c r="D34" s="0">
-        <v>0.051003353507602545</v>
+        <v>0.024795180665916954</v>
       </c>
       <c r="E34" s="0">
-        <v>1.0880004069880815</v>
+        <v>0.54275122805209164</v>
       </c>
       <c r="F34" s="0">
-        <v>1.1031854378613974</v>
+        <v>0.55083910233075184</v>
       </c>
       <c r="G34" s="0">
-        <v>0.041422321716468397</v>
+        <v>0.01960033591312756</v>
       </c>
     </row>
     <row r="35">
@@ -3728,22 +3728,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="0">
-        <v>1.0025894091021896</v>
+        <v>0.50225869289849856</v>
       </c>
       <c r="C35" s="0">
-        <v>-0.04672482382992324</v>
+        <v>-0.02418781147006379</v>
       </c>
       <c r="D35" s="0">
-        <v>0.051782324251585563</v>
+        <v>0.025188921377674339</v>
       </c>
       <c r="E35" s="0">
-        <v>1.0894211842219839</v>
+        <v>0.54344050726911031</v>
       </c>
       <c r="F35" s="0">
-        <v>1.1041050497880371</v>
+        <v>0.55124578385131551</v>
       </c>
       <c r="G35" s="0">
-        <v>0.042613168214515162</v>
+        <v>0.020224330037907905</v>
       </c>
     </row>
     <row r="36">
@@ -3751,22 +3751,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="0">
-        <v>1.0015941922241343</v>
+        <v>0.50171164135692792</v>
       </c>
       <c r="C36" s="0">
-        <v>-0.045912278876684968</v>
+        <v>-0.023713572430926623</v>
       </c>
       <c r="D36" s="0">
-        <v>0.052560760153051799</v>
+        <v>0.025579663160545038</v>
       </c>
       <c r="E36" s="0">
-        <v>1.0908669583768493</v>
+        <v>0.54414130954224238</v>
       </c>
       <c r="F36" s="0">
-        <v>1.1050812575271283</v>
+        <v>0.55168238064311292</v>
       </c>
       <c r="G36" s="0">
-        <v>0.043779584378637312</v>
+        <v>0.020831340875289615</v>
       </c>
     </row>
     <row r="37">
@@ -3774,22 +3774,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="0">
-        <v>1.0006466985234765</v>
+        <v>0.50119315794712727</v>
       </c>
       <c r="C37" s="0">
-        <v>-0.04516716610879648</v>
+        <v>-0.023278330708933419</v>
       </c>
       <c r="D37" s="0">
-        <v>0.053341321358719045</v>
+        <v>0.025968982854445634</v>
       </c>
       <c r="E37" s="0">
-        <v>1.0923389857069679</v>
+        <v>0.54485415036702634</v>
       </c>
       <c r="F37" s="0">
-        <v>1.1061128493583288</v>
+        <v>0.55214790396742963</v>
       </c>
       <c r="G37" s="0">
-        <v>0.044926173880341785</v>
+        <v>0.021424126095731064</v>
       </c>
     </row>
     <row r="38">
@@ -3797,22 +3797,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="0">
-        <v>0.99974243934487817</v>
+        <v>0.50070051307664343</v>
       </c>
       <c r="C38" s="0">
-        <v>-0.044484507000260465</v>
+        <v>-0.022879014676246975</v>
       </c>
       <c r="D38" s="0">
-        <v>0.054126454752095231</v>
+        <v>0.026358310619643884</v>
       </c>
       <c r="E38" s="0">
-        <v>1.0938386302895113</v>
+        <v>0.54557961071478967</v>
       </c>
       <c r="F38" s="0">
-        <v>1.1071989706498537</v>
+        <v>0.55264158869614155</v>
       </c>
       <c r="G38" s="0">
-        <v>0.046057134533700847</v>
+        <v>0.022005174318010769</v>
       </c>
     </row>
     <row r="39">
@@ -3820,22 +3820,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="0">
-        <v>0.99887736997747434</v>
+        <v>0.50023126168584231</v>
       </c>
       <c r="C39" s="0">
-        <v>-0.043859858788884043</v>
+        <v>-0.022512893718364249</v>
       </c>
       <c r="D39" s="0">
-        <v>0.05491842933102313</v>
+        <v>0.026748953649327164</v>
       </c>
       <c r="E39" s="0">
-        <v>1.0953673555928503</v>
+        <v>0.54631832989951867</v>
       </c>
       <c r="F39" s="0">
-        <v>1.1083390856079507</v>
+        <v>0.55316286638911571</v>
       </c>
       <c r="G39" s="0">
-        <v>0.047176316902783837</v>
+        <v>0.022576744220804808</v>
       </c>
     </row>
     <row r="40">
@@ -3843,22 +3843,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="0">
-        <v>0.99804783405374498</v>
+        <v>0.4997832062792984</v>
       </c>
       <c r="C40" s="0">
-        <v>-0.043289249639575138</v>
+        <v>-0.022177534994560162</v>
       </c>
       <c r="D40" s="0">
-        <v>0.055719366536257212</v>
+        <v>0.027142116269576869</v>
       </c>
       <c r="E40" s="0">
-        <v>1.0969267185057261</v>
+        <v>0.54707100019345778</v>
       </c>
       <c r="F40" s="0">
-        <v>1.1095329456842808</v>
+        <v>0.55371134302899972</v>
       </c>
       <c r="G40" s="0">
-        <v>0.048287274606776773</v>
+        <v>0.023140897786096345</v>
       </c>
     </row>
     <row r="41">
@@ -3866,22 +3866,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="0">
-        <v>0.9972505158180619</v>
+        <v>0.49935436542381662</v>
       </c>
       <c r="C41" s="0">
-        <v>-0.042769123106656967</v>
+        <v>-0.021870766649109436</v>
       </c>
       <c r="D41" s="0">
-        <v>0.056531266426015504</v>
+        <v>0.027538917082790042</v>
       </c>
       <c r="E41" s="0">
-        <v>1.098518365417462</v>
+        <v>0.54783836287619969</v>
       </c>
       <c r="F41" s="0">
-        <v>1.1107805635589143</v>
+        <v>0.55428678061089054</v>
       </c>
       <c r="G41" s="0">
-        <v>0.049393307739950175</v>
+        <v>0.023699528708682346</v>
       </c>
     </row>
     <row r="42">
@@ -3889,22 +3889,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="0">
-        <v>0.99648239899140678</v>
+        <v>0.49894294679217638</v>
       </c>
       <c r="C42" s="0">
-        <v>-0.042296290398411714</v>
+        <v>-0.021590646390244845</v>
       </c>
       <c r="D42" s="0">
-        <v>0.057356030426145073</v>
+        <v>0.027940403683690919</v>
       </c>
       <c r="E42" s="0">
-        <v>1.1001440300266083</v>
+        <v>0.54862120546923143</v>
       </c>
       <c r="F42" s="0">
-        <v>1.1120821918250199</v>
+        <v>0.55488908194320275</v>
       </c>
       <c r="G42" s="0">
-        <v>0.050497500564403636</v>
+        <v>0.024254386808115744</v>
       </c>
     </row>
     <row r="43">
@@ -3912,22 +3912,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="0">
-        <v>0.99574073118735573</v>
+        <v>0.49854732400393265</v>
       </c>
       <c r="C43" s="0">
-        <v>-0.041867889216341499</v>
+        <v>-0.021335434556662935</v>
       </c>
       <c r="D43" s="0">
-        <v>0.058195481254355759</v>
+        <v>0.028347565377302208</v>
       </c>
       <c r="E43" s="0">
-        <v>1.1018055326246676</v>
+        <v>0.54942035996055971</v>
       </c>
       <c r="F43" s="0">
-        <v>1.1134383056675512</v>
+        <v>0.55551827814136101</v>
       </c>
       <c r="G43" s="0">
-        <v>0.051602754427128202</v>
+        <v>0.024807099123289385</v>
       </c>
     </row>
     <row r="44">
@@ -3935,22 +3935,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="0">
-        <v>0.9950229930178881</v>
+        <v>0.49816601665147248</v>
       </c>
       <c r="C44" s="0">
-        <v>-0.041481348157780519</v>
+        <v>-0.021103570952568662</v>
       </c>
       <c r="D44" s="0">
-        <v>0.059051380512361841</v>
+        <v>0.028761344249341191</v>
       </c>
       <c r="E44" s="0">
-        <v>1.1035047806569651</v>
+        <v>0.55023670186570117</v>
       </c>
       <c r="F44" s="0">
-        <v>1.1148495889618593</v>
+        <v>0.55617451839550347</v>
       </c>
       <c r="G44" s="0">
-        <v>0.052711816687687999</v>
+        <v>0.025359188246087704</v>
       </c>
     </row>
     <row r="45">
@@ -3958,22 +3958,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="0">
-        <v>0.99432687117555041</v>
+        <v>0.49779767300885064</v>
       </c>
       <c r="C45" s="0">
-        <v>-0.041134355844885492</v>
+        <v>-0.020893654861035421</v>
       </c>
       <c r="D45" s="0">
-        <v>0.059925444356062126</v>
+        <v>0.029182644876846776</v>
       </c>
       <c r="E45" s="0">
-        <v>1.1052437704074154</v>
+        <v>0.55107115000439566</v>
       </c>
       <c r="F45" s="0">
-        <v>1.1163169233261421</v>
+        <v>0.55685806167289098</v>
       </c>
       <c r="G45" s="0">
-        <v>0.053827306310079551</v>
+        <v>0.025912088351860565</v>
       </c>
     </row>
     <row r="46">
@@ -3981,22 +3981,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="0">
-        <v>0.99365023489847348</v>
+        <v>0.49744105500876679</v>
       </c>
       <c r="C46" s="0">
-        <v>-0.040824834084464315</v>
+        <v>-0.020704427748951055</v>
       </c>
       <c r="D46" s="0">
-        <v>0.060819357586665526</v>
+        <v>0.029612342916832516</v>
       </c>
       <c r="E46" s="0">
-        <v>1.1070245896903037</v>
+        <v>0.55192466689892306</v>
       </c>
       <c r="F46" s="0">
-        <v>1.1178413797495828</v>
+        <v>0.55756927007970003</v>
       </c>
       <c r="G46" s="0">
-        <v>0.054951736665115922</v>
+        <v>0.026467159305423822</v>
       </c>
     </row>
     <row r="47">
@@ -4004,22 +4004,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="0">
-        <v>0.99299111532243678</v>
+        <v>0.49709502514396625</v>
       </c>
       <c r="C47" s="0">
-        <v>-0.040550914478343518</v>
+        <v>-0.020534758260406034</v>
       </c>
       <c r="D47" s="0">
-        <v>0.061734786451555106</v>
+        <v>0.030051292770704619</v>
       </c>
       <c r="E47" s="0">
-        <v>1.1088494214621223</v>
+        <v>0.552798259721345</v>
       </c>
       <c r="F47" s="0">
-        <v>1.1194242124901066</v>
+        <v>0.55830860365869117</v>
       </c>
       <c r="G47" s="0">
-        <v>0.056087536002941273</v>
+        <v>0.027025699157703271</v>
       </c>
     </row>
     <row r="48">
@@ -4027,22 +4027,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="0">
-        <v>0.99234768730409939</v>
+        <v>0.49675853500689071</v>
       </c>
       <c r="C48" s="0">
-        <v>-0.040310917998322454</v>
+        <v>-0.020383629163226957</v>
       </c>
       <c r="D48" s="0">
-        <v>0.062673390400047893</v>
+        <v>0.030500334490015116</v>
       </c>
       <c r="E48" s="0">
-        <v>1.1107205482913889</v>
+        <v>0.55369298173444892</v>
       </c>
       <c r="F48" s="0">
-        <v>1.1210668549952909</v>
+        <v>0.55907661644144524</v>
       </c>
       <c r="G48" s="0">
-        <v>0.057237065984791898</v>
+        <v>0.027588955296792693</v>
       </c>
     </row>
     <row r="49">
@@ -4050,22 +4050,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="0">
-        <v>0.99171825336518504</v>
+        <v>0.49643061522831899</v>
       </c>
       <c r="C49" s="0">
-        <v>-0.04010333711733504</v>
+        <v>-0.020250125968707906</v>
       </c>
       <c r="D49" s="0">
-        <v>0.063636833004038884</v>
+        <v>0.030960300063193166</v>
       </c>
       <c r="E49" s="0">
-        <v>1.1126403576454203</v>
+        <v>0.55460993418558391</v>
       </c>
       <c r="F49" s="0">
-        <v>1.1227709176496043</v>
+        <v>0.55987395360855796</v>
       </c>
       <c r="G49" s="0">
-        <v>0.05840263860579549</v>
+        <v>0.028158134475573467</v>
       </c>
     </row>
     <row r="50">
@@ -4073,22 +4073,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="0">
-        <v>0.99110122946155643</v>
+        <v>0.49611036661414426</v>
       </c>
       <c r="C50" s="0">
-        <v>-0.039926820152489551</v>
+        <v>-0.020133426989929367</v>
       </c>
       <c r="D50" s="0">
-        <v>0.06462679222516711</v>
+        <v>0.031432019202013509</v>
       </c>
       <c r="E50" s="0">
-        <v>1.1146113479710766</v>
+        <v>0.55555026862460277</v>
       </c>
       <c r="F50" s="0">
-        <v>1.1245381871929856</v>
+        <v>0.56070134963988161</v>
       </c>
       <c r="G50" s="0">
-        <v>0.059586531793952707</v>
+        <v>0.02873441190424169</v>
       </c>
     </row>
     <row r="51">
@@ -4096,22 +4096,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="0">
-        <v>0.99049513232597042</v>
+        <v>0.49579695231101972</v>
       </c>
       <c r="C51" s="0">
-        <v>-0.039780157528790522</v>
+        <v>-0.020032794641378218</v>
       </c>
       <c r="D51" s="0">
-        <v>0.065644970187427418</v>
+        <v>0.031916324729704085</v>
       </c>
       <c r="E51" s="0">
-        <v>1.1166361355623042</v>
+        <v>0.55651518962729474</v>
       </c>
       <c r="F51" s="0">
-        <v>1.1263706276913461</v>
+        <v>0.56155962736086718</v>
       </c>
       <c r="G51" s="0">
-        <v>0.060791003932417313</v>
+        <v>0.029318939568589719</v>
       </c>
     </row>
     <row r="52">
@@ -4119,22 +4119,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="0">
-        <v>0.98989856817055055</v>
+        <v>0.49548959085766681</v>
       </c>
       <c r="C52" s="0">
-        <v>-0.039662269716551068</v>
+        <v>-0.019947567813418863</v>
       </c>
       <c r="D52" s="0">
-        <v>0.066693102596002404</v>
+        <v>0.032414057659039923</v>
       </c>
       <c r="E52" s="0">
-        <v>1.1187174622214669</v>
+        <v>0.55750595791448876</v>
       </c>
       <c r="F52" s="0">
-        <v>1.1282703829703238</v>
+        <v>0.56244969781129994</v>
       </c>
       <c r="G52" s="0">
-        <v>0.062018307521339008</v>
+        <v>0.029912853912479866</v>
       </c>
     </row>
     <row r="53">
@@ -4142,22 +4142,22 @@
         <v>51</v>
       </c>
       <c r="B53" s="0">
-        <v>0.98931022256608781</v>
+        <v>0.49518755000024473</v>
       </c>
       <c r="C53" s="0">
-        <v>-0.039572196632475541</v>
+        <v>-0.019877155180763807</v>
       </c>
       <c r="D53" s="0">
-        <v>0.067772967928833472</v>
+        <v>0.032926072037890469</v>
       </c>
       <c r="E53" s="0">
-        <v>1.1208582037344137</v>
+        <v>0.55852389386471069</v>
       </c>
       <c r="F53" s="0">
-        <v>1.1302397804504416</v>
+        <v>0.56337256087997212</v>
       </c>
       <c r="G53" s="0">
-        <v>0.063270702170643706</v>
+        <v>0.030517283004724134</v>
       </c>
     </row>
     <row r="54">
@@ -4165,22 +4165,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="0">
-        <v>0.98872885134124411</v>
+        <v>0.49489014116813668</v>
       </c>
       <c r="C54" s="0">
-        <v>-0.039509088325391815</v>
+        <v>-0.019821029325410963</v>
       </c>
       <c r="D54" s="0">
-        <v>0.068886396516402576</v>
+        <v>0.033453239631051575</v>
       </c>
       <c r="E54" s="0">
-        <v>1.1230613791914497</v>
+        <v>0.55957038142522242</v>
       </c>
       <c r="F54" s="0">
-        <v>1.1322813363457878</v>
+        <v>0.56432930666376602</v>
       </c>
       <c r="G54" s="0">
-        <v>0.06455046709507388</v>
+        <v>0.031133353295809123</v>
       </c>
     </row>
     <row r="55">
@@ -4188,22 +4188,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="0">
-        <v>0.98815327236653217</v>
+        <v>0.49459671452149018</v>
       </c>
       <c r="C55" s="0">
-        <v>-0.039472196793735863</v>
+        <v>-0.019778721572362198</v>
       </c>
       <c r="D55" s="0">
-        <v>0.07003527961692213</v>
+        <v>0.033996454500379053</v>
       </c>
       <c r="E55" s="0">
-        <v>1.125330161198171</v>
+        <v>0.56064687243267131</v>
       </c>
       <c r="F55" s="0">
-        <v>1.1343977622100629</v>
+        <v>0.56532111752274383</v>
       </c>
       <c r="G55" s="0">
-        <v>0.065859913267031917</v>
+        <v>0.031762196057927405</v>
       </c>
     </row>
     <row r="56">
@@ -4211,22 +4211,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="0">
-        <v>0.98758235810625816</v>
+        <v>0.49430665449438638</v>
       </c>
       <c r="C56" s="0">
-        <v>-0.039460868803969762</v>
+        <v>-0.019749817451399761</v>
       </c>
       <c r="D56" s="0">
-        <v>0.071221578588270745</v>
+        <v>0.03455663754004689</v>
       </c>
       <c r="E56" s="0">
-        <v>1.1276678870318091</v>
+        <v>0.56175489136061463</v>
       </c>
       <c r="F56" s="0">
-        <v>1.1365919728339362</v>
+        <v>0.56634927081453856</v>
       </c>
       <c r="G56" s="0">
-        <v>0.067201395370538722</v>
+        <v>0.032404953592283924</v>
       </c>
     </row>
     <row r="57">
@@ -4234,22 +4234,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="0">
-        <v>0.98701502883705139</v>
+        <v>0.49401937576803273</v>
       </c>
       <c r="C57" s="0">
-        <v>-0.039474539597844437</v>
+        <v>-0.019733952710833561</v>
       </c>
       <c r="D57" s="0">
-        <v>0.072447334254274215</v>
+        <v>0.035134741019834437</v>
       </c>
       <c r="E57" s="0">
-        <v>1.1300780708105915</v>
+        <v>0.56289604051707687</v>
       </c>
       <c r="F57" s="0">
-        <v>1.138867095516749</v>
+        <v>0.56741514230203838</v>
       </c>
       <c r="G57" s="0">
-        <v>0.068577323690496281</v>
+        <v>0.033062785280060035</v>
       </c>
     </row>
     <row r="58">
@@ -4257,22 +4257,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="0">
-        <v>0.98645024644465029</v>
+        <v>0.4937343196172227</v>
       </c>
       <c r="C58" s="0">
-        <v>-0.039512727392391908</v>
+        <v>-0.019730809819803515</v>
       </c>
       <c r="D58" s="0">
-        <v>0.073714676561119214</v>
+        <v>0.0357317531866699</v>
       </c>
       <c r="E58" s="0">
-        <v>1.1325644167559461</v>
+        <v>0.56407200572112759</v>
       </c>
       <c r="F58" s="0">
-        <v>1.1412264807541048</v>
+        <v>0.5685202102382797</v>
       </c>
       <c r="G58" s="0">
-        <v>0.069990176065058793</v>
+        <v>0.033736873547678591</v>
       </c>
     </row>
     <row r="59">
@@ -4280,22 +4280,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="0">
-        <v>0.98588700872163737</v>
+        <v>0.49345095058077115</v>
       </c>
       <c r="C59" s="0">
-        <v>-0.039575028590183116</v>
+        <v>-0.019740114904795492</v>
       </c>
       <c r="D59" s="0">
-        <v>0.07502583461966307</v>
+        <v>0.036348702972963588</v>
       </c>
       <c r="E59" s="0">
-        <v>1.1351308336403938</v>
+        <v>0.5652845624934536</v>
       </c>
       <c r="F59" s="0">
-        <v>1.1436737144012088</v>
+        <v>0.56966606014193455</v>
       </c>
       <c r="G59" s="0">
-        <v>0.071442510025058928</v>
+        <v>0.034428429812711513</v>
       </c>
     </row>
     <row r="60">
@@ -4303,22 +4303,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="0">
-        <v>0.98532434409815339</v>
+        <v>0.49316875341293159</v>
       </c>
       <c r="C60" s="0">
-        <v>-0.039661113629120948</v>
+        <v>-0.01976163507376132</v>
       </c>
       <c r="D60" s="0">
-        <v>0.076383147231083568</v>
+        <v>0.036986664859560037</v>
       </c>
       <c r="E60" s="0">
-        <v>1.1377814505279684</v>
+        <v>0.56653558280209593</v>
       </c>
       <c r="F60" s="0">
-        <v>1.1462126313904737</v>
+        <v>0.57085439028598561</v>
       </c>
       <c r="G60" s="0">
-        <v>0.072936975242800906</v>
+        <v>0.03513870047385776</v>
       </c>
     </row>
     <row r="61">
@@ -4326,22 +4326,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="0">
-        <v>0.98476130674553253</v>
+        <v>0.49288723027814646</v>
       </c>
       <c r="C61" s="0">
-        <v>-0.039770723411158393</v>
+        <v>-0.019795176087858291</v>
       </c>
       <c r="D61" s="0">
-        <v>0.077789073996661059</v>
+        <v>0.037646763941286639</v>
       </c>
       <c r="E61" s="0">
-        <v>1.1405206339292235</v>
+        <v>0.56782704241114712</v>
       </c>
       <c r="F61" s="0">
-        <v>1.1488473311011325</v>
+        <v>0.57208701793138816</v>
       </c>
       <c r="G61" s="0">
-        <v>0.074476326413130053</v>
+        <v>0.035868973006702491</v>
       </c>
     </row>
     <row r="62">
@@ -4349,22 +4349,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="0">
-        <v>0.98419697199950273</v>
+        <v>0.49260589815598221</v>
       </c>
       <c r="C62" s="0">
-        <v>-0.039903666258115693</v>
+        <v>-0.019840580346513325</v>
       </c>
       <c r="D62" s="0">
-        <v>0.07924620711748985</v>
+        <v>0.03833018124409332</v>
       </c>
       <c r="E62" s="0">
-        <v>1.1433530065097017</v>
+        <v>0.56916102888727482</v>
       </c>
       <c r="F62" s="0">
-        <v>1.1515821944989617</v>
+        <v>0.57336588634684016</v>
       </c>
       <c r="G62" s="0">
-        <v>0.076063436692346886</v>
+        <v>0.036620582226399252</v>
       </c>
     </row>
     <row r="63">
@@ -4372,22 +4372,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="0">
-        <v>0.98363043205525591</v>
+        <v>0.49232428642694093</v>
       </c>
       <c r="C63" s="0">
-        <v>-0.040059815350424355</v>
+        <v>-0.019897725156434829</v>
       </c>
       <c r="D63" s="0">
-        <v>0.080757283996666138</v>
+        <v>0.039038159344607373</v>
       </c>
       <c r="E63" s="0">
-        <v>1.1462834675093561</v>
+        <v>0.57053975032673943</v>
       </c>
       <c r="F63" s="0">
-        <v>1.1544219031859802</v>
+        <v>0.57469307266554437</v>
       </c>
       <c r="G63" s="0">
-        <v>0.077701311825297104</v>
+        <v>0.037394916778905336</v>
       </c>
     </row>
     <row r="64">
@@ -4395,22 +4395,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="0">
-        <v>0.98306079189148587</v>
+        <v>0.49204193461307083</v>
       </c>
       <c r="C64" s="0">
-        <v>-0.040239106611324953</v>
+        <v>-0.019966521259466793</v>
       </c>
       <c r="D64" s="0">
-        <v>0.082325200765072479</v>
+        <v>0.039772008345614007</v>
       </c>
       <c r="E64" s="0">
-        <v>1.149317215051294</v>
+        <v>0.57196554487409978</v>
       </c>
       <c r="F64" s="0">
-        <v>1.157371460523654</v>
+        <v>0.57607079664010319</v>
       </c>
       <c r="G64" s="0">
-        <v>0.079393105097929795</v>
+        <v>0.03819342592394899</v>
       </c>
     </row>
     <row r="65">
@@ -4418,22 +4418,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="0">
-        <v>0.98248716538451042</v>
+        <v>0.49175839025004736</v>
       </c>
       <c r="C65" s="0">
-        <v>-0.040441537004993124</v>
+        <v>-0.020046911597906003</v>
       </c>
       <c r="D65" s="0">
-        <v>0.083953026862376753</v>
+        <v>0.040533112264509758</v>
       </c>
       <c r="E65" s="0">
-        <v>1.1524597705417341</v>
+        <v>0.57344089111337315</v>
       </c>
       <c r="F65" s="0">
-        <v>1.1604362150191996</v>
+        <v>0.57750143036778734</v>
       </c>
       <c r="G65" s="0">
-        <v>0.081142133261706787</v>
+        <v>0.03901762667549899</v>
       </c>
     </row>
     <row r="66">
@@ -4441,22 +4441,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="0">
-        <v>0.98190867157695105</v>
+        <v>0.49147320686969548</v>
       </c>
       <c r="C66" s="0">
-        <v>-0.040667163222305978</v>
+        <v>-0.020138870299165074</v>
       </c>
       <c r="D66" s="0">
-        <v>0.085644020817582586</v>
+        <v>0.041322935896264935</v>
       </c>
       <c r="E66" s="0">
-        <v>1.1557170053896506</v>
+        <v>0.57496841942304566</v>
       </c>
       <c r="F66" s="0">
-        <v>1.1636218861934977</v>
+        <v>0.57898750907041607</v>
       </c>
       <c r="G66" s="0">
-        <v>0.082951893587928233</v>
+        <v>0.039869111369204395</v>
       </c>
     </row>
     <row r="67">
@@ -4464,22 +4464,22 @@
         <v>65</v>
       </c>
       <c r="B67" s="0">
-        <v>0.98132443106823553</v>
+        <v>0.49118594207388006</v>
       </c>
       <c r="C67" s="0">
-        <v>-0.040916100732711208</v>
+        <v>-0.020242401864572469</v>
       </c>
       <c r="D67" s="0">
-        <v>0.087401647388502327</v>
+        <v>0.042143032217882029</v>
       </c>
       <c r="E67" s="0">
-        <v>1.1590951703048396</v>
+        <v>0.57655092439842548</v>
       </c>
       <c r="F67" s="0">
-        <v>1.1669345931815074</v>
+        <v>0.58053174302644195</v>
       </c>
       <c r="G67" s="0">
-        <v>0.084826082224143021</v>
+        <v>0.040749555731064806</v>
       </c>
     </row>
     <row r="68">
@@ -4487,22 +4487,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="0">
-        <v>0.98073356249645727</v>
+        <v>0.49089615568229833</v>
       </c>
       <c r="C68" s="0">
-        <v>-0.041188523184924802</v>
+        <v>-0.020357540549656928</v>
       </c>
       <c r="D68" s="0">
-        <v>0.089229596237325168</v>
+        <v>0.042995050407923618</v>
       </c>
       <c r="E68" s="0">
-        <v>1.162600927467677</v>
+        <v>0.57819137845844337</v>
       </c>
       <c r="F68" s="0">
-        <v>1.1703808863526937</v>
+        <v>0.58213703076757195</v>
       </c>
       <c r="G68" s="0">
-        <v>0.086768614042037201</v>
+        <v>0.041660727527655685</v>
       </c>
     </row>
     <row r="69">
@@ -4510,22 +4510,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="0">
-        <v>0.98013517908293968</v>
+        <v>0.49060340793805174</v>
       </c>
       <c r="C69" s="0">
-        <v>-0.041484662143075751</v>
+        <v>-0.020484349925589642</v>
       </c>
       <c r="D69" s="0">
-        <v>0.091131802340301549</v>
+        <v>0.043880744562462028</v>
       </c>
       <c r="E69" s="0">
-        <v>1.166241385903324</v>
+        <v>0.57989294676952352</v>
       </c>
       <c r="F69" s="0">
-        <v>1.1739677822803956</v>
+        <v>0.58380647366884486</v>
       </c>
       <c r="G69" s="0">
-        <v>0.088783644186534574</v>
+        <v>0.0426044958856115</v>
       </c>
     </row>
     <row r="70">
@@ -4533,22 +4533,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="0">
-        <v>0.97952838521227614</v>
+        <v>0.49030725775596706</v>
       </c>
       <c r="C70" s="0">
-        <v>-0.04180480714857078</v>
+        <v>-0.020622922613552454</v>
       </c>
       <c r="D70" s="0">
-        <v>0.093112468353910488</v>
+        <v>0.04480198319799323</v>
       </c>
       <c r="E70" s="0">
-        <v>1.1700241404386163</v>
+        <v>0.58165900363691825</v>
       </c>
       <c r="F70" s="0">
-        <v>1.1777028024364924</v>
+        <v>0.58554339207987005</v>
       </c>
       <c r="G70" s="0">
-        <v>0.0908755915600125</v>
+        <v>0.04358284137694228</v>
       </c>
     </row>
     <row r="71">
@@ -4556,22 +4556,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="0">
-        <v>0.97891227302164352</v>
+        <v>0.4900072609994976</v>
       </c>
       <c r="C71" s="0">
-        <v>-0.042149306101298689</v>
+        <v>-0.020773380185719361</v>
       </c>
       <c r="D71" s="0">
-        <v>0.095176089188365162</v>
+        <v>0.045760759642603205</v>
       </c>
       <c r="E71" s="0">
-        <v>1.1739573146721329</v>
+        <v>0.5834931505341685</v>
       </c>
       <c r="F71" s="0">
-        <v>1.1815940160419289</v>
+        <v>0.58735134316617743</v>
       </c>
       <c r="G71" s="0">
-        <v>0.093049164503930901</v>
+        <v>0.044597866977312509</v>
       </c>
     </row>
     <row r="72">
@@ -4579,22 +4579,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="0">
-        <v>0.97828591897387607</v>
+        <v>0.48970296877270347</v>
       </c>
       <c r="C72" s="0">
-        <v>-0.042518565957036944</v>
+        <v>-0.020935873228321234</v>
       </c>
       <c r="D72" s="0">
-        <v>0.097327479072492701</v>
+        <v>0.046759203429262666</v>
       </c>
       <c r="E72" s="0">
-        <v>1.1780496084484538</v>
+        <v>0.58539923596473875</v>
       </c>
       <c r="F72" s="0">
-        <v>1.185650087566162</v>
+        <v>0.58923414065397217</v>
       </c>
       <c r="G72" s="0">
-        <v>0.095309388973568734</v>
+        <v>0.045651810016909183</v>
       </c>
     </row>
     <row r="73">
@@ -4602,22 +4602,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="0">
-        <v>0.97764838038916435</v>
+        <v>0.48939392571429741</v>
       </c>
       <c r="C73" s="0">
-        <v>-0.042913053741019877</v>
+        <v>-0.021110581563946122</v>
       </c>
       <c r="D73" s="0">
-        <v>0.099571801432747992</v>
+        <v>0.047799592819775257</v>
       </c>
       <c r="E73" s="0">
-        <v>1.1823103503976395</v>
+        <v>0.58738137737678398</v>
       </c>
       <c r="F73" s="0">
-        <v>1.1898803294407197</v>
+        <v>0.59119587669949014</v>
       </c>
       <c r="G73" s="0">
-        <v>0.097661639540623416</v>
+        <v>0.046747055258153786</v>
       </c>
     </row>
     <row r="74">
@@ -4625,22 +4625,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="0">
-        <v>0.97699869191027977</v>
+        <v>0.48907966828104699</v>
       </c>
       <c r="C74" s="0">
-        <v>-0.043333297880643558</v>
+        <v>-0.021297714631810544</v>
       </c>
       <c r="D74" s="0">
-        <v>0.10191460195440911</v>
+        <v>0.048884368605046261</v>
       </c>
       <c r="E74" s="0">
-        <v>1.186749556182418</v>
+        <v>0.58944398538314458</v>
       </c>
       <c r="F74" s="0">
-        <v>1.194294760635761</v>
+        <v>0.59324094613627532</v>
       </c>
       <c r="G74" s="0">
-        <v>0.10011167360437363</v>
+        <v>0.047886149251784645</v>
       </c>
     </row>
     <row r="75">
@@ -4648,22 +4648,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="0">
-        <v>0.97633586187599264</v>
+        <v>0.48875972300798148</v>
       </c>
       <c r="C75" s="0">
-        <v>-0.043779889863320362</v>
+        <v>-0.021497512026289505</v>
       </c>
       <c r="D75" s="0">
-        <v>0.10436184524588836</v>
+        <v>0.050016149347301905</v>
       </c>
       <c r="E75" s="0">
-        <v>1.1913779931904007</v>
+        <v>0.59159179057474276</v>
       </c>
       <c r="F75" s="0">
-        <v>1.1989041718458151</v>
+        <v>0.59537407339085047</v>
       </c>
       <c r="G75" s="0">
-        <v>0.10266566924581574</v>
+        <v>0.04907181614298859</v>
       </c>
     </row>
     <row r="76">
@@ -4671,22 +4671,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="0">
-        <v>0.97565886857679174</v>
+        <v>0.48843360473284425</v>
       </c>
       <c r="C76" s="0">
-        <v>-0.044253486228503537</v>
+        <v>-0.021710244195497153</v>
       </c>
       <c r="D76" s="0">
-        <v>0.10691995558915406</v>
+        <v>0.05119774825323449</v>
       </c>
       <c r="E76" s="0">
-        <v>1.19620725251956</v>
+        <v>0.59382987325753978</v>
       </c>
       <c r="F76" s="0">
-        <v>1.2037201981445063</v>
+        <v>0.59760034240038173</v>
       </c>
       <c r="G76" s="0">
-        <v>0.10533026722246046</v>
+        <v>0.05030697512296075</v>
       </c>
     </row>
     <row r="77">
@@ -4694,22 +4694,22 @@
         <v>75</v>
       </c>
       <c r="B77" s="0">
-        <v>0.97496665636615276</v>
+        <v>0.48810081477207928</v>
       </c>
       <c r="C77" s="0">
-        <v>-0.044754810906014957</v>
+        <v>-0.02193621330321904</v>
       </c>
       <c r="D77" s="0">
-        <v>0.10959586233207044</v>
+        <v>0.052432191894370886</v>
       </c>
       <c r="E77" s="0">
-        <v>1.2012498292350762</v>
+        <v>0.59616369649210621</v>
       </c>
       <c r="F77" s="0">
-        <v>1.2087554001010572</v>
+        <v>0.59992522991607</v>
       </c>
       <c r="G77" s="0">
-        <v>0.10811261767572986</v>
+        <v>0.051594759749031653</v>
       </c>
     </row>
     <row r="78">
@@ -4717,22 +4717,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="0">
-        <v>0.97425813159945507</v>
+        <v>0.48776083903533113</v>
       </c>
       <c r="C78" s="0">
-        <v>-0.045284657916028592</v>
+        <v>-0.022175754259019884</v>
       </c>
       <c r="D78" s="0">
-        <v>0.11239705056421119</v>
+        <v>0.053722741022971213</v>
       </c>
       <c r="E78" s="0">
-        <v>1.2065192120285044</v>
+        <v>0.59859914287210747</v>
       </c>
       <c r="F78" s="0">
-        <v>1.2140233545076902</v>
+        <v>0.60235464263466643</v>
       </c>
       <c r="G78" s="0">
-        <v>0.1110204322105553</v>
+        <v>0.052938539389148949</v>
       </c>
     </row>
     <row r="79">
@@ -4740,22 +4740,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="0">
-        <v>0.97353215837112528</v>
+        <v>0.48741314606498265</v>
       </c>
       <c r="C79" s="0">
-        <v>-0.045843894449421628</v>
+        <v>-0.022429235922906143</v>
       </c>
       <c r="D79" s="0">
-        <v>0.1153316178188788</v>
+        <v>0.055072913769383988</v>
       </c>
       <c r="E79" s="0">
-        <v>1.2120299835902382</v>
+        <v>0.60114255554505314</v>
       </c>
       <c r="F79" s="0">
-        <v>1.2195387560511706</v>
+        <v>0.60489495866911547</v>
       </c>
       <c r="G79" s="0">
-        <v>0.11406204211027414</v>
+        <v>0.054341943084877401</v>
       </c>
     </row>
     <row r="80">
@@ -4763,22 +4763,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="0">
-        <v>0.97278755401877204</v>
+        <v>0.48705718498663919</v>
       </c>
       <c r="C80" s="0">
-        <v>-0.046433464350803685</v>
+        <v>-0.022697062492551108</v>
       </c>
       <c r="D80" s="0">
-        <v>0.11840833766380819</v>
+        <v>0.056486511551092834</v>
       </c>
       <c r="E80" s="0">
-        <v>1.2177979332193893</v>
+        <v>0.60380078405761672</v>
       </c>
       <c r="F80" s="0">
-        <v>1.2253175314796401</v>
+        <v>0.60755307395011637</v>
       </c>
       <c r="G80" s="0">
-        <v>0.11724646357256034</v>
+        <v>0.055808886172392658</v>
       </c>
     </row>
     <row r="81">
@@ -4786,22 +4786,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="0">
-        <v>0.97202308436084151</v>
+        <v>0.48669238335568227</v>
       </c>
       <c r="C81" s="0">
-        <v>-0.047054392030355038</v>
+        <v>-0.022979675082785166</v>
       </c>
       <c r="D81" s="0">
-        <v>0.12163673118523372</v>
+        <v>0.057967648075997004</v>
       </c>
       <c r="E81" s="0">
-        <v>1.2238401834480257</v>
+        <v>0.60658123570091493</v>
       </c>
       <c r="F81" s="0">
-        <v>1.2313769680743185</v>
+        <v>0.61033645424556526</v>
       </c>
       <c r="G81" s="0">
-        <v>0.12058347099783663</v>
+        <v>0.057343600054452222</v>
       </c>
     </row>
     <row r="82">
@@ -4809,22 +4809,22 @@
         <v>80</v>
       </c>
       <c r="B82" s="0">
-        <v>0.97123745863172173</v>
+        <v>0.48631814488406539</v>
       </c>
       <c r="C82" s="0">
-        <v>-0.047707786834788019</v>
+        <v>-0.023277553508882325</v>
       </c>
       <c r="D82" s="0">
-        <v>0.12502714753924857</v>
+        <v>0.059520781884415099</v>
       </c>
       <c r="E82" s="0">
-        <v>1.2301753327579035</v>
+        <v>0.60949193314135519</v>
       </c>
       <c r="F82" s="0">
-        <v>1.2377358585435398</v>
+        <v>0.61325319359752772</v>
       </c>
       <c r="G82" s="0">
-        <v>0.12408367953521998</v>
+        <v>0.058950665579790708</v>
       </c>
     </row>
     <row r="83">
@@ -4832,22 +4832,22 @@
         <v>81</v>
       </c>
       <c r="B83" s="0">
-        <v>0.97042932407516269</v>
+        <v>0.48593384703037645</v>
       </c>
       <c r="C83" s="0">
-        <v>-0.048394847912256962</v>
+        <v>-0.023591218287110666</v>
       </c>
       <c r="D83" s="0">
-        <v>0.12859085494678232</v>
+        <v>0.0611507529479101</v>
       </c>
       <c r="E83" s="0">
-        <v>1.2368236168277489</v>
+        <v>0.61254157925358999</v>
       </c>
       <c r="F83" s="0">
-        <v>1.2444146648244705</v>
+        <v>0.61631208011021676</v>
       </c>
       <c r="G83" s="0">
-        <v>0.12775863829874004</v>
+        <v>0.060635050561819087</v>
       </c>
     </row>
     <row r="84">
@@ -4855,22 +4855,22 @@
         <v>82</v>
       </c>
       <c r="B84" s="0">
-        <v>0.9695972601533116</v>
+        <v>0.48553883843483953</v>
       </c>
       <c r="C84" s="0">
-        <v>-0.049116869611048331</v>
+        <v>-0.023921232868136605</v>
       </c>
       <c r="D84" s="0">
-        <v>0.13234014375111952</v>
+        <v>0.062862823930714587</v>
       </c>
       <c r="E84" s="0">
-        <v>1.243807091180916</v>
+        <v>0.61573963022806244</v>
       </c>
       <c r="F84" s="0">
-        <v>1.2514357037192987</v>
+        <v>0.6195226701818709</v>
       </c>
       <c r="G84" s="0">
-        <v>0.13162093591566362</v>
+        <v>0.062402152058459462</v>
       </c>
     </row>
     <row r="85">
@@ -4878,22 +4878,22 @@
         <v>83</v>
       </c>
       <c r="B85" s="0">
-        <v>0.96873977232459863</v>
+        <v>0.48513243617935559</v>
       </c>
       <c r="C85" s="0">
-        <v>-0.049875247457379833</v>
+        <v>-0.024268206121182391</v>
       </c>
       <c r="D85" s="0">
-        <v>0.1362884434490223</v>
+        <v>0.064662726824429515</v>
       </c>
       <c r="E85" s="0">
-        <v>1.2511498386232884</v>
+        <v>0.61909637821227237</v>
       </c>
       <c r="F85" s="0">
-        <v>1.2588233578243326</v>
+        <v>0.62289537246420112</v>
       </c>
       <c r="G85" s="0">
-        <v>0.13568432036885711</v>
+        <v>0.06425784414258634</v>
       </c>
     </row>
     <row r="86">
@@ -4901,22 +4901,22 @@
         <v>84</v>
       </c>
       <c r="B86" s="0">
-        <v>0.96785528533894871</v>
+        <v>0.48471392285084708</v>
       </c>
       <c r="C86" s="0">
-        <v>-0.050671484763768954</v>
+        <v>-0.02463279508937392</v>
       </c>
       <c r="D86" s="0">
-        <v>0.14045045595953576</v>
+        <v>0.066556715792533749</v>
       </c>
       <c r="E86" s="0">
-        <v>1.2588782054899623</v>
+        <v>0.62262304496882626</v>
       </c>
       <c r="F86" s="0">
-        <v>1.2666043158534108</v>
+        <v>0.6264415430620186</v>
       </c>
       <c r="G86" s="0">
-        <v>0.13996383545802418</v>
+        <v>0.06620853202180306</v>
       </c>
     </row>
     <row r="87">
@@ -4924,22 +4924,22 @@
         <v>85</v>
       </c>
       <c r="B87" s="0">
-        <v>0.96694213599343559</v>
+        <v>0.48428254338407462</v>
       </c>
       <c r="C87" s="0">
-        <v>-0.051507199926259989</v>
+        <v>-0.025015708039536767</v>
       </c>
       <c r="D87" s="0">
-        <v>0.14484230782302696</v>
+        <v>0.068551627212888058</v>
       </c>
       <c r="E87" s="0">
-        <v>1.2670210714828398</v>
+        <v>0.6263318883033725</v>
       </c>
       <c r="F87" s="0">
-        <v>1.274807847237976</v>
+        <v>0.63017359376175974</v>
       </c>
       <c r="G87" s="0">
-        <v>0.14447597664517867</v>
+        <v>0.068261213522087194</v>
       </c>
     </row>
     <row r="88">
@@ -4947,22 +4947,22 @@
         <v>86</v>
       </c>
       <c r="B88" s="0">
-        <v>0.96599856528526107</v>
+        <v>0.48383750165765721</v>
       </c>
       <c r="C88" s="0">
-        <v>-0.052384134476486377</v>
+        <v>-0.02541770783281604</v>
       </c>
       <c r="D88" s="0">
-        <v>0.1494817245452206</v>
+        <v>0.070654948089848055</v>
       </c>
       <c r="E88" s="0">
-        <v>1.2756101588124151</v>
+        <v>0.63023632334217838</v>
       </c>
       <c r="F88" s="0">
-        <v>1.2834661168388843</v>
+        <v>0.63410511541167403</v>
       </c>
       <c r="G88" s="0">
-        <v>0.14923886958705232</v>
+        <v>0.070423549138378672</v>
       </c>
     </row>
     <row r="89">
@@ -4970,22 +4970,22 @@
         <v>87</v>
       </c>
       <c r="B89" s="0">
-        <v>0.96502270989188166</v>
+        <v>0.48337795681426127</v>
       </c>
       <c r="C89" s="0">
-        <v>-0.053304161963139342</v>
+        <v>-0.025839615646006685</v>
       </c>
       <c r="D89" s="0">
-        <v>0.15438823094052284</v>
+        <v>0.072874894230383902</v>
       </c>
       <c r="E89" s="0">
-        <v>1.2846803874981618</v>
+        <v>0.6343510611362162</v>
       </c>
       <c r="F89" s="0">
-        <v>1.2926145467727357</v>
+        <v>0.6382510189826548</v>
       </c>
       <c r="G89" s="0">
-        <v>0.15427247531537997</v>
+        <v>0.072703942084329648</v>
       </c>
     </row>
     <row r="90">
@@ -4993,22 +4993,22 @@
         <v>88</v>
       </c>
       <c r="B90" s="0">
-        <v>0.96401259289997499</v>
+        <v>0.48290301927273532</v>
       </c>
       <c r="C90" s="0">
-        <v>-0.054269297747189742</v>
+        <v>-0.026282315077391889</v>
       </c>
       <c r="D90" s="0">
-        <v>0.15958338211575518</v>
+        <v>0.075220499850440603</v>
       </c>
       <c r="E90" s="0">
-        <v>1.2942702850870209</v>
+        <v>0.63869226755335506</v>
       </c>
       <c r="F90" s="0">
-        <v>1.30229223379388</v>
+        <v>0.64262769733461422</v>
       </c>
       <c r="G90" s="0">
-        <v>0.15959882683634133</v>
+        <v>0.075111630053102077</v>
       </c>
     </row>
     <row r="91">
@@ -5016,22 +5016,22 @@
         <v>89</v>
       </c>
       <c r="B91" s="0">
-        <v>0.96296611369565333</v>
+        <v>0.48241174639632928</v>
       </c>
       <c r="C91" s="0">
-        <v>-0.055281709806219298</v>
+        <v>-0.026746756675314801</v>
       </c>
       <c r="D91" s="0">
-        <v>0.16509103070848041</v>
+        <v>0.077701720610907507</v>
       </c>
       <c r="E91" s="0">
-        <v>1.3044224607885415</v>
+        <v>0.64327774601482102</v>
       </c>
       <c r="F91" s="0">
-        <v>1.3125424324539319</v>
+        <v>0.64725321132181268</v>
       </c>
       <c r="G91" s="0">
-        <v>0.16524230292299663</v>
+        <v>0.077656790744066701</v>
       </c>
     </row>
     <row r="92">
@@ -5039,22 +5039,22 @@
         <v>90</v>
       </c>
       <c r="B92" s="0">
-        <v>0.96188103691770421</v>
+        <v>0.48190313777696409</v>
       </c>
       <c r="C92" s="0">
-        <v>-0.056343730655748249</v>
+        <v>-0.027233962932695966</v>
       </c>
       <c r="D92" s="0">
-        <v>0.17093763720396146</v>
+        <v>0.080329552492901885</v>
       </c>
       <c r="E92" s="0">
-        <v>1.3151841561892543</v>
+        <v>0.64812714836492213</v>
       </c>
       <c r="F92" s="0">
-        <v>1.3234131164772662</v>
+        <v>0.65214750462073912</v>
       </c>
       <c r="G92" s="0">
-        <v>0.17122994612181464</v>
+        <v>0.080350663632853467</v>
       </c>
     </row>
     <row r="93">
@@ -5062,22 +5062,22 @@
         <v>91</v>
       </c>
       <c r="B93" s="0">
-        <v>0.96075498036343621</v>
+        <v>0.48137613009075664</v>
       </c>
       <c r="C93" s="0">
-        <v>-0.05745787050972638</v>
+        <v>-0.027745033796368317</v>
       </c>
       <c r="D93" s="0">
-        <v>0.17715263166735656</v>
+        <v>0.083116169430061379</v>
       </c>
       <c r="E93" s="0">
-        <v>1.3266078874170484</v>
+        <v>0.65326221907107107</v>
       </c>
       <c r="F93" s="0">
-        <v>1.334957633565905</v>
+        <v>0.65733265259400819</v>
       </c>
       <c r="G93" s="0">
-        <v>0.17759183355449187</v>
+        <v>0.083205690985687392</v>
       </c>
     </row>
     <row r="94">
@@ -5085,22 +5085,22 @@
         <v>92</v>
       </c>
       <c r="B94" s="0">
-        <v>0.95958540172270723</v>
+        <v>0.48082959147452381</v>
       </c>
       <c r="C94" s="0">
-        <v>-0.058626831818622376</v>
+        <v>-0.028281152746525762</v>
       </c>
       <c r="D94" s="0">
-        <v>0.1837688371303248</v>
+        <v>0.086075083247761155</v>
       </c>
       <c r="E94" s="0">
-        <v>1.338752197035834</v>
+        <v>0.65870707908220205</v>
       </c>
       <c r="F94" s="0">
-        <v>1.3472354723420523</v>
+        <v>0.66283315166235579</v>
       </c>
       <c r="G94" s="0">
-        <v>0.18436151105973045</v>
+        <v>0.086235681770745976</v>
       </c>
     </row>
     <row r="95">
@@ -5108,22 +5108,22 @@
         <v>93</v>
       </c>
       <c r="B95" s="0">
-        <v>0.95836958399964345</v>
+        <v>0.48026231536674507</v>
       </c>
       <c r="C95" s="0">
-        <v>-0.059853525342205845</v>
+        <v>-0.0288435935089109</v>
       </c>
       <c r="D95" s="0">
-        <v>0.19082296727912512</v>
+        <v>0.089221330250624675</v>
       </c>
       <c r="E95" s="0">
-        <v>1.3516825382705726</v>
+        <v>0.66448855709098853</v>
       </c>
       <c r="F95" s="0">
-        <v>1.360313164566135</v>
+        <v>0.66867625710916967</v>
       </c>
       <c r="G95" s="0">
-        <v>0.1915765037060965</v>
+        <v>0.089456002935700982</v>
       </c>
     </row>
     <row r="96">
@@ -5131,22 +5131,22 @@
         <v>94</v>
       </c>
       <c r="B96" s="0">
-        <v>0.95710461946303238</v>
+        <v>0.47967301374923965</v>
       </c>
       <c r="C96" s="0">
-        <v>-0.061141087935480995</v>
+        <v>-0.029433727470724407</v>
       </c>
       <c r="D96" s="0">
-        <v>0.19835621415931218</v>
+        <v>0.092571689796322812</v>
       </c>
       <c r="E96" s="0">
-        <v>1.3654723196725123</v>
+        <v>0.67063657773164165</v>
       </c>
       <c r="F96" s="0">
-        <v>1.3742653514203651</v>
+        <v>0.67489237907321165</v>
       </c>
       <c r="G96" s="0">
-        <v>0.19927891887705854</v>
+        <v>0.092883803549260111</v>
       </c>
     </row>
     <row r="97">
@@ -5154,22 +5154,22 @@
         <v>95</v>
       </c>
       <c r="B97" s="0">
-        <v>0.95578739194503293</v>
+        <v>0.47906030971757768</v>
       </c>
       <c r="C97" s="0">
-        <v>-0.062492902250831796</v>
+        <v>-0.030053031880823328</v>
       </c>
       <c r="D97" s="0">
-        <v>0.20641494554875958</v>
+        <v>0.096144941456721575</v>
       </c>
       <c r="E97" s="0">
-        <v>1.3802041454122192</v>
+        <v>0.67718461851150491</v>
       </c>
       <c r="F97" s="0">
-        <v>1.3891760499114818</v>
+        <v>0.68151554880942522</v>
       </c>
       <c r="G97" s="0">
-        <v>0.20751616219933475</v>
+        <v>0.096538278608934658</v>
       </c>
     </row>
     <row r="98">
@@ -5177,22 +5177,22 @@
         <v>96</v>
       </c>
       <c r="B98" s="0">
-        <v>0.95441455728320068</v>
+        <v>0.4784227292986874</v>
       </c>
       <c r="C98" s="0">
-        <v>-0.063912618587772599</v>
+        <v>-0.030703098925763481</v>
       </c>
       <c r="D98" s="0">
-        <v>0.21505153673994454</v>
+        <v>0.099962168978914551</v>
       </c>
       <c r="E98" s="0">
-        <v>1.3959712955486821</v>
+        <v>0.68417025016927724</v>
       </c>
       <c r="F98" s="0">
-        <v>1.4051401648520028</v>
+        <v>0.68858397026737905</v>
       </c>
       <c r="G98" s="0">
-        <v>0.21634179185090868</v>
+        <v>0.10044098098250016</v>
       </c>
     </row>
     <row r="99">
@@ -5200,22 +5200,22 @@
         <v>97</v>
       </c>
       <c r="B99" s="0">
-        <v>0.95298252167230091</v>
+        <v>0.47775869242317148</v>
       </c>
       <c r="C99" s="0">
-        <v>-0.065404179154435971</v>
+        <v>-0.031385645785885361</v>
       </c>
       <c r="D99" s="0">
-        <v>0.22432536810419934</v>
+        <v>0.10404712132947978</v>
       </c>
       <c r="E99" s="0">
-        <v>1.4128795025748111</v>
+        <v>0.69163577887671901</v>
       </c>
       <c r="F99" s="0">
-        <v>1.4222653041565945</v>
+        <v>0.69614067585908446</v>
       </c>
       <c r="G99" s="0">
-        <v>0.22581654365089016</v>
+        <v>0.10461619209186708</v>
       </c>
     </row>
     <row r="100">
@@ -5223,22 +5223,22 @@
         <v>98</v>
       </c>
       <c r="B100" s="0">
-        <v>0.95148741765929301</v>
+        <v>0.47706650294713343</v>
       </c>
       <c r="C100" s="0">
-        <v>-0.066971845042855555</v>
+        <v>-0.032102525790231866</v>
       </c>
       <c r="D100" s="0">
-        <v>0.23430402852650561</v>
+        <v>0.1084266437864886</v>
       </c>
       <c r="E100" s="0">
-        <v>1.4310490962677636</v>
+        <v>0.69962901352806073</v>
       </c>
       <c r="F100" s="0">
-        <v>1.440673971354449</v>
+        <v>0.70423431024483441</v>
       </c>
       <c r="G100" s="0">
-        <v>0.23600956836364992</v>
+        <v>0.10909136472239822</v>
       </c>
     </row>
     <row r="101">
@@ -5246,22 +5246,22 @@
         <v>99</v>
       </c>
       <c r="B101" s="0">
-        <v>0.94992507747646815</v>
+        <v>0.47634433760363643</v>
       </c>
       <c r="C101" s="0">
-        <v>-0.068620226264101206</v>
+        <v>-0.032855740805933814</v>
       </c>
       <c r="D101" s="0">
-        <v>0.24506477635858959</v>
+        <v>0.11313119554352789</v>
       </c>
       <c r="E101" s="0">
-        <v>1.4506176097592789</v>
+        <v>0.70820418767026006</v>
       </c>
       <c r="F101" s="0">
-        <v>1.4605062306955234</v>
+        <v>0.71292007244694655</v>
       </c>
       <c r="G101" s="0">
-        <v>0.24699993463484749</v>
+        <v>0.11389765496446121</v>
       </c>
     </row>
     <row r="102">
@@ -5269,22 +5269,22 @@
         <v>100</v>
       </c>
       <c r="B102" s="0">
-        <v>0.94829100336293315</v>
+        <v>0.47559023374688258</v>
       </c>
       <c r="C102" s="0">
-        <v>-0.070354315240554868</v>
+        <v>-0.033647455017227622</v>
       </c>
       <c r="D102" s="0">
-        <v>0.25669632501826611</v>
+        <v>0.11819547489764819</v>
       </c>
       <c r="E102" s="0">
-        <v>1.4717429677514273</v>
+        <v>0.71742307394413385</v>
       </c>
       <c r="F102" s="0">
-        <v>1.4819229690463367</v>
+        <v>0.72226085514968141</v>
       </c>
       <c r="G102" s="0">
-        <v>0.25887846704098993</v>
+        <v>0.11907056506858178</v>
       </c>
     </row>
     <row r="103">
@@ -5292,22 +5292,22 @@
         <v>101</v>
       </c>
       <c r="B103" s="0">
-        <v>0.94658033447240864</v>
+        <v>0.47480207573238492</v>
       </c>
       <c r="C103" s="0">
-        <v>-0.072179524212365551</v>
+        <v>-0.034480010271957372</v>
       </c>
       <c r="D103" s="0">
-        <v>0.26930104131165938</v>
+        <v>0.12365917921551269</v>
       </c>
       <c r="E103" s="0">
-        <v>1.4946074157624618</v>
+        <v>0.72735633997211446</v>
       </c>
       <c r="F103" s="0">
-        <v>1.5051099178471719</v>
+        <v>0.73232863142326998</v>
       </c>
       <c r="G103" s="0">
-        <v>0.27175001049141595</v>
+        <v>0.12465072534458231</v>
       </c>
     </row>
     <row r="104">
@@ -5315,22 +5315,22 @@
         <v>102</v>
       </c>
       <c r="B104" s="0">
-        <v>0.94478780990415645</v>
+        <v>0.47397757975333094</v>
       </c>
       <c r="C104" s="0">
-        <v>-0.07410172708501199</v>
+        <v>-0.035355943199808913</v>
       </c>
       <c r="D104" s="0">
-        <v>0.2829976732246256</v>
+        <v>0.12956793508779785</v>
       </c>
       <c r="E104" s="0">
-        <v>1.5194224013139463</v>
+        <v>0.73808520949839762</v>
       </c>
       <c r="F104" s="0">
-        <v>1.5302826519927817</v>
+        <v>0.74320615441045379</v>
       </c>
       <c r="G104" s="0">
-        <v>0.28573624202510573</v>
+        <v>0.1306848517621399</v>
       </c>
     </row>
     <row r="105">
@@ -5338,22 +5338,22 @@
         <v>103</v>
       </c>
       <c r="B105" s="0">
-        <v>0.94290772732216355</v>
+        <v>0.47311427692638663</v>
       </c>
       <c r="C105" s="0">
-        <v>-0.07612730632685516</v>
+        <v>-0.036278004337354439</v>
       </c>
       <c r="D105" s="0">
-        <v>0.2979247636451306</v>
+        <v>0.13597444522429603</v>
       </c>
       <c r="E105" s="0">
-        <v>1.5464346901514239</v>
+        <v>0.74970351278329184</v>
       </c>
       <c r="F105" s="0">
-        <v>1.557692856897489</v>
+        <v>0.75498905630673152</v>
       </c>
       <c r="G105" s="0">
-        <v>0.30097919237058962</v>
+        <v>0.13722692748474771</v>
       </c>
     </row>
     <row r="106">
@@ -5361,22 +5361,22 @@
         <v>104</v>
       </c>
       <c r="B106" s="0">
-        <v>0.9409338965433135</v>
+        <v>0.47220949438863641</v>
       </c>
       <c r="C106" s="0">
-        <v>-0.078263205621951271</v>
+        <v>-0.037249179531044591</v>
       </c>
       <c r="D106" s="0">
-        <v>0.31424496222278075</v>
+        <v>0.14293991392713976</v>
       </c>
       <c r="E106" s="0">
-        <v>1.575934102063361</v>
+        <v>0.76232023799935844</v>
       </c>
       <c r="F106" s="0">
-        <v>1.5876362596674991</v>
+        <v>0.76778846154884462</v>
       </c>
       <c r="G106" s="0">
-        <v>0.31764569770130752</v>
+        <v>0.14433967246149512</v>
       </c>
     </row>
     <row r="107">
@@ -5384,22 +5384,22 @@
         <v>105</v>
       </c>
       <c r="B107" s="0">
-        <v>0.93885958737582353</v>
+        <v>0.47126033413031271</v>
       </c>
       <c r="C107" s="0">
-        <v>-0.080516989097036681</v>
+        <v>-0.038272713931619309</v>
       </c>
       <c r="D107" s="0">
-        <v>0.33215052693942238</v>
+        <v>0.15053583420742323</v>
       </c>
       <c r="E107" s="0">
-        <v>1.6082633955715988</v>
+        <v>0.77606273396963354</v>
       </c>
       <c r="F107" s="0">
-        <v>1.6204627696690352</v>
+        <v>0.7817342689097988</v>
       </c>
       <c r="G107" s="0">
-        <v>0.33593308477896933</v>
+        <v>0.1520963872941217</v>
       </c>
     </row>
     <row r="108">
@@ -5407,22 +5407,22 @@
         <v>106</v>
       </c>
       <c r="B108" s="0">
-        <v>0.93667747087154174</v>
+        <v>0.47026364924440206</v>
       </c>
       <c r="C108" s="0">
-        <v>-0.082896908075991538</v>
+        <v>-0.039352138943184435</v>
       </c>
       <c r="D108" s="0">
-        <v>0.35187042173875777</v>
+        <v>0.15884624948825951</v>
       </c>
       <c r="E108" s="0">
-        <v>1.6438310403787375</v>
+        <v>0.79108076899258262</v>
       </c>
       <c r="F108" s="0">
-        <v>1.6565895903068433</v>
+        <v>0.79697931332110483</v>
       </c>
       <c r="G108" s="0">
-        <v>0.35607651249558958</v>
+        <v>0.16058328872444308</v>
       </c>
     </row>
     <row r="109">
@@ -5430,22 +5430,22 @@
         <v>107</v>
       </c>
       <c r="B109" s="0">
-        <v>0.93437955301610365</v>
+        <v>0.46921601722276896</v>
       </c>
       <c r="C109" s="0">
-        <v>-0.08541197647452474</v>
+        <v>-0.040491302548963826</v>
       </c>
       <c r="D109" s="0">
-        <v>0.37367958538876855</v>
+        <v>0.16797064550444016</v>
       </c>
       <c r="E109" s="0">
-        <v>1.6831279253125899</v>
+        <v>0.80755172831761779</v>
       </c>
       <c r="F109" s="0">
-        <v>1.6965183831329884</v>
+        <v>0.81370469857873329</v>
       </c>
       <c r="G109" s="0">
-        <v>0.37835856928764272</v>
+        <v>0.16990249858811787</v>
       </c>
     </row>
     <row r="110">
@@ -5453,22 +5453,22 @@
         <v>108</v>
       </c>
       <c r="B110" s="0">
-        <v>0.93195709971487573</v>
+        <v>0.46811370986757711</v>
       </c>
       <c r="C110" s="0">
-        <v>-0.088072056137491084</v>
+        <v>-0.041694403505246988</v>
       </c>
       <c r="D110" s="0">
-        <v>0.39791119977611583</v>
+        <v>0.17802768991294016</v>
       </c>
       <c r="E110" s="0">
-        <v>1.7267495132111697</v>
+        <v>0.82568734592886883</v>
       </c>
       <c r="F110" s="0">
-        <v>1.7408580452219262</v>
+        <v>0.83212670893222696</v>
       </c>
       <c r="G110" s="0">
-        <v>0.40312199071476001</v>
+        <v>0.18017591272094347</v>
       </c>
     </row>
     <row r="111">
@@ -5476,22 +5476,22 @@
         <v>109</v>
       </c>
       <c r="B111" s="0">
-        <v>0.92940055173432579</v>
+        <v>0.46695265931455399</v>
       </c>
       <c r="C111" s="0">
-        <v>-0.090887953647687952</v>
+        <v>-0.042966029977560473</v>
       </c>
       <c r="D111" s="0">
-        <v>0.42497317297062581</v>
+        <v>0.18916012851422309</v>
       </c>
       <c r="E111" s="0">
-        <v>1.7754256649496671</v>
+        <v>0.84574253353651352</v>
       </c>
       <c r="F111" s="0">
-        <v>1.7903553968975683</v>
+        <v>0.85250588048651998</v>
       </c>
       <c r="G111" s="0">
-        <v>0.43078676725083132</v>
+        <v>0.19155027184779622</v>
       </c>
     </row>
     <row r="112">
@@ -5499,22 +5499,22 @@
         <v>110</v>
       </c>
       <c r="B112" s="0">
-        <v>0.92669942802105032</v>
+        <v>0.46572841957860822</v>
       </c>
       <c r="C112" s="0">
-        <v>-0.093871530406126585</v>
+        <v>-0.044311203291335588</v>
       </c>
       <c r="D112" s="0">
-        <v>0.45537065848921848</v>
+        <v>0.20154128449195627</v>
       </c>
       <c r="E112" s="0">
-        <v>1.8300614695902073</v>
+        <v>0.86802712176596242</v>
       </c>
       <c r="F112" s="0">
-        <v>1.845937232672882</v>
+        <v>0.87515907424465011</v>
       </c>
       <c r="G112" s="0">
-        <v>0.46187354853422752</v>
+        <v>0.20420390044087961</v>
       </c>
     </row>
     <row r="113">
@@ -5522,22 +5522,22 @@
         <v>111</v>
       </c>
       <c r="B113" s="0">
-        <v>0.92384221553531865</v>
+        <v>0.46443612292958431</v>
       </c>
       <c r="C113" s="0">
-        <v>-0.097035828109672387</v>
+        <v>-0.04573542758666542</v>
       </c>
       <c r="D113" s="0">
-        <v>0.48973740570359137</v>
+        <v>0.21538381839803733</v>
       </c>
       <c r="E113" s="0">
-        <v>1.8917942115669007</v>
+        <v>0.89292171664256703</v>
       </c>
       <c r="F113" s="0">
-        <v>1.908769050194945</v>
+        <v>0.90047579467102379</v>
       </c>
       <c r="G113" s="0">
-        <v>0.49703627386556615</v>
+        <v>0.21835580108005698</v>
       </c>
     </row>
     <row r="114">
@@ -5545,22 +5545,22 @@
         <v>112</v>
       </c>
       <c r="B114" s="0">
-        <v>0.92081624339184509</v>
+        <v>0.46307043028279532</v>
       </c>
       <c r="C114" s="0">
-        <v>-0.10039521214502804</v>
+        <v>-0.047244746307384129</v>
       </c>
       <c r="D114" s="0">
-        <v>0.52888034574502696</v>
+        <v>0.23095173906829855</v>
       </c>
       <c r="E114" s="0">
-        <v>1.9620745771959625</v>
+        <v>0.92089948618502349</v>
       </c>
       <c r="F114" s="0">
-        <v>1.9803388596375475</v>
+        <v>0.92894063200017218</v>
       </c>
       <c r="G114" s="0">
-        <v>0.53710865384073214</v>
+        <v>0.23427814093176697</v>
       </c>
     </row>
     <row r="115">
@@ -5568,22 +5568,22 @@
         <v>113</v>
       </c>
       <c r="B115" s="0">
-        <v>0.91760753868391609</v>
+        <v>0.46162547464090509</v>
       </c>
       <c r="C115" s="0">
-        <v>-0.10396553589383696</v>
+        <v>-0.048845806623799976</v>
       </c>
       <c r="D115" s="0">
-        <v>0.57384456626529123</v>
+        <v>0.24857719259587649</v>
       </c>
       <c r="E115" s="0">
-        <v>2.0427852880235582</v>
+        <v>0.95255668173722807</v>
       </c>
       <c r="F115" s="0">
-        <v>2.0625797669604249</v>
+        <v>0.96116473408722281</v>
       </c>
       <c r="G115" s="0">
-        <v>0.58317202892239317</v>
+        <v>0.25231373168984678</v>
       </c>
     </row>
     <row r="116">
@@ -5591,22 +5591,22 @@
         <v>114</v>
       </c>
       <c r="B116" s="0">
-        <v>0.91420066086066076</v>
+        <v>0.46009479644500012</v>
       </c>
       <c r="C116" s="0">
-        <v>-0.10776432952208559</v>
+        <v>-0.050545933092559371</v>
       </c>
       <c r="D116" s="0">
-        <v>0.62601070258537728</v>
+        <v>0.26868444968016531</v>
       </c>
       <c r="E116" s="0">
-        <v>2.1364193827849127</v>
+        <v>0.98865634836120442</v>
       </c>
       <c r="F116" s="0">
-        <v>2.1580544373791661</v>
+        <v>0.99793092826682794</v>
       </c>
       <c r="G116" s="0">
-        <v>0.63665728501307117</v>
+        <v>0.27290104541682664</v>
       </c>
     </row>
     <row r="117">
@@ -5614,22 +5614,22 @@
         <v>115</v>
       </c>
       <c r="B117" s="0">
-        <v>0.91057851090945907</v>
+        <v>0.45847126947617817</v>
       </c>
       <c r="C117" s="0">
-        <v>-0.1118110175327299</v>
+        <v>-0.052353212104419497</v>
       </c>
       <c r="D117" s="0">
-        <v>0.6872457958599415</v>
+        <v>0.29182504812781368</v>
       </c>
       <c r="E117" s="0">
-        <v>2.2463571276049485</v>
+        <v>1.0301925219324877</v>
       </c>
       <c r="F117" s="0">
-        <v>2.2702420323780088</v>
+        <v>1.0402600728469844</v>
       </c>
       <c r="G117" s="0">
-        <v>0.69950306952685914</v>
+        <v>0.29661093074043415</v>
       </c>
     </row>
     <row r="118">
@@ -5637,22 +5637,22 @@
         <v>116</v>
       </c>
       <c r="B118" s="0">
-        <v>0.90672211083843957</v>
+        <v>0.45674701568562703</v>
       </c>
       <c r="C118" s="0">
-        <v>-0.11612717022537851</v>
+        <v>-0.054276588971536421</v>
       </c>
       <c r="D118" s="0">
-        <v>0.76014623629604294</v>
+        <v>0.31873079373966934</v>
       </c>
       <c r="E118" s="0">
-        <v>2.3773132271222468</v>
+        <v>1.0784873031577378</v>
       </c>
       <c r="F118" s="0">
-        <v>2.4040023867902822</v>
+        <v>1.0895115254572942</v>
       </c>
       <c r="G118" s="0">
-        <v>0.77441121789049061</v>
+        <v>0.32420209941721434</v>
       </c>
     </row>
     <row r="119">
@@ -5660,22 +5660,22 @@
         <v>117</v>
       </c>
       <c r="B119" s="0">
-        <v>0.90261034802217144</v>
+        <v>0.45491330700956656</v>
       </c>
       <c r="C119" s="0">
-        <v>-0.12073679527161743</v>
+        <v>-0.056325979873274708</v>
       </c>
       <c r="D119" s="0">
-        <v>0.84844772062760254</v>
+        <v>0.35039645531556007</v>
       </c>
       <c r="E119" s="0">
-        <v>2.5360937244711197</v>
+        <v>1.1353427347630518</v>
       </c>
       <c r="F119" s="0">
-        <v>2.5663631065918615</v>
+        <v>1.1475405696378027</v>
       </c>
       <c r="G119" s="0">
-        <v>0.86527899152937526</v>
+        <v>0.3567078957619943</v>
       </c>
     </row>
     <row r="120">
@@ -5683,22 +5683,22 @@
         <v>118</v>
       </c>
       <c r="B120" s="0">
-        <v>0.89821967782141354</v>
+        <v>0.4529604518309735</v>
       </c>
       <c r="C120" s="0">
-        <v>-0.12566667693124939</v>
+        <v>-0.05851240133021033</v>
       </c>
       <c r="D120" s="0">
-        <v>0.95775783185045294</v>
+        <v>0.38821409401637197</v>
       </c>
       <c r="E120" s="0">
-        <v>2.7329527495078723</v>
+        <v>1.2032882203827788</v>
       </c>
       <c r="F120" s="0">
-        <v>2.7679334956723403</v>
+        <v>1.2169553121104741</v>
       </c>
       <c r="G120" s="0">
-        <v>0.97797396611768139</v>
+        <v>0.39557760385246704</v>
       </c>
     </row>
     <row r="121">
@@ -5706,22 +5706,22 @@
         <v>119</v>
       </c>
       <c r="B121" s="0">
-        <v>0.89352377645604864</v>
+        <v>0.45087766326408135</v>
       </c>
       <c r="C121" s="0">
-        <v>-0.13094677207103678</v>
+        <v>-0.060848120431236552</v>
       </c>
       <c r="D121" s="0">
-        <v>1.0969628586911822</v>
+        <v>0.43420213340038738</v>
       </c>
       <c r="E121" s="0">
-        <v>2.9842063596643125</v>
+        <v>1.2860037119549812</v>
       </c>
       <c r="F121" s="0">
-        <v>3.0256353850414004</v>
+        <v>1.3015569335094099</v>
       </c>
       <c r="G121" s="0">
-        <v>1.1218276742765108</v>
+        <v>0.44291811432186406</v>
       </c>
     </row>
     <row r="122">
@@ -5729,22 +5729,22 @@
         <v>120</v>
       </c>
       <c r="B122" s="0">
-        <v>0.88849313432215393</v>
+        <v>0.4486529058361744</v>
       </c>
       <c r="C122" s="0">
-        <v>-0.13661067419144135</v>
+        <v>-0.063346829726021764</v>
       </c>
       <c r="D122" s="0">
-        <v>1.2811940838952121</v>
+        <v>0.49142007840261509</v>
       </c>
       <c r="E122" s="0">
-        <v>3.3177622506051661</v>
+        <v>1.3890882620400058</v>
       </c>
       <c r="F122" s="0">
-        <v>3.3684974608218727</v>
+        <v>1.4071410072676645</v>
       </c>
       <c r="G122" s="0">
-        <v>1.3127988981558065</v>
+        <v>0.50193290277813052</v>
       </c>
     </row>
   </sheetData>
@@ -5758,7 +5758,7 @@
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="true"/>
     <col min="2" max="2" width="12.42578125" customWidth="true"/>
-    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5777,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="0">
-        <v>-471.49874015388281</v>
+        <v>-184.24407584919334</v>
       </c>
       <c r="C2" s="0">
-        <v>237.11108631285262</v>
+        <v>-165.67090501961354</v>
       </c>
     </row>
     <row r="3">
@@ -5788,10 +5788,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>-471.79612308508598</v>
+        <v>-187.35131148997857</v>
       </c>
       <c r="C3" s="0">
-        <v>256.19037794598165</v>
+        <v>-139.86141393724188</v>
       </c>
     </row>
     <row r="4">
@@ -5799,10 +5799,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="0">
-        <v>-472.53618154200086</v>
+        <v>-189.57025168633584</v>
       </c>
       <c r="C4" s="0">
-        <v>273.3384207509755</v>
+        <v>-120.04703190558448</v>
       </c>
     </row>
     <row r="5">
@@ -5810,10 +5810,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="0">
-        <v>-473.64064075795181</v>
+        <v>-191.57428994392166</v>
       </c>
       <c r="C5" s="0">
-        <v>289.25134977844982</v>
+        <v>-102.6882918430409</v>
       </c>
     </row>
     <row r="6">
@@ -5821,10 +5821,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="0">
-        <v>-475.0657398748175</v>
+        <v>-193.55753037463873</v>
       </c>
       <c r="C6" s="0">
-        <v>304.29846249645357</v>
+        <v>-86.726874873623245</v>
       </c>
     </row>
     <row r="7">
@@ -5832,10 +5832,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="0">
-        <v>-476.78400290494346</v>
+        <v>-195.6055464575565</v>
       </c>
       <c r="C7" s="0">
-        <v>318.70034195941423</v>
+        <v>-71.682246363539377</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="0">
-        <v>-478.7767992654849</v>
+        <v>-197.76391171866362</v>
       </c>
       <c r="C8" s="0">
-        <v>332.59919129511491</v>
+        <v>-57.292038210180465</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="0">
-        <v>-481.03076638380355</v>
+        <v>-200.0597189054036</v>
       </c>
       <c r="C9" s="0">
-        <v>346.09166149994093</v>
+        <v>-43.396829875016692</v>
       </c>
     </row>
     <row r="10">
@@ -5865,10 +5865,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="0">
-        <v>-483.53588883606051</v>
+        <v>-202.51026259058639</v>
       </c>
       <c r="C10" s="0">
-        <v>359.24600638966876</v>
+        <v>-29.892758308990437</v>
       </c>
     </row>
     <row r="11">
@@ -5876,10 +5876,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="0">
-        <v>-486.28438136343533</v>
+        <v>-205.12712679347311</v>
       </c>
       <c r="C11" s="0">
-        <v>372.11181479597946</v>
+        <v>-16.708795284121379</v>
       </c>
     </row>
     <row r="12">
@@ -5887,10 +5887,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="0">
-        <v>-489.2699988864232</v>
+        <v>-207.91832544857857</v>
       </c>
       <c r="C12" s="0">
-        <v>384.72588876023929</v>
+        <v>-3.7946406564469157</v>
       </c>
     </row>
     <row r="13">
@@ -5898,10 +5898,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="0">
-        <v>-492.4875895985187</v>
+        <v>-210.88951484609893</v>
       </c>
       <c r="C13" s="0">
-        <v>397.11597401322411</v>
+        <v>8.8862478881729317</v>
       </c>
     </row>
     <row r="14">
@@ -5909,10 +5909,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="0">
-        <v>-495.93279424692901</v>
+        <v>-214.04472337016483</v>
       </c>
       <c r="C14" s="0">
-        <v>409.30322434394981</v>
+        <v>21.360914099760009</v>
       </c>
     </row>
     <row r="15">
@@ -5920,10 +5920,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="0">
-        <v>-499.60183733909446</v>
+        <v>-217.38681252524731</v>
       </c>
       <c r="C15" s="0">
-        <v>421.30388453184247</v>
+        <v>33.649631884122414</v>
       </c>
     </row>
     <row r="16">
@@ -5931,10 +5931,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="0">
-        <v>-503.49137833074519</v>
+        <v>-220.9177800019865</v>
       </c>
       <c r="C16" s="0">
-        <v>433.13047221308676</v>
+        <v>45.767722097715648</v>
       </c>
     </row>
     <row r="17">
@@ -5942,10 +5942,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="0">
-        <v>-507.59840318956236</v>
+        <v>-224.63896563605732</v>
       </c>
       <c r="C17" s="0">
-        <v>444.79262791865284</v>
+        <v>57.7268014953479</v>
       </c>
     </row>
     <row r="18">
@@ -5953,10 +5953,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="0">
-        <v>-511.92014386931487</v>
+        <v>-228.55119538869297</v>
       </c>
       <c r="C18" s="0">
-        <v>456.29773919763159</v>
+        <v>69.535664821373075</v>
       </c>
     </row>
     <row r="19">
@@ -5964,10 +5964,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="0">
-        <v>-516.45401752606074</v>
+        <v>-232.65488448667415</v>
       </c>
       <c r="C19" s="0">
-        <v>467.65140720209729</v>
+        <v>81.200922378627695</v>
       </c>
     </row>
     <row r="20">
@@ -5975,10 +5975,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="0">
-        <v>-521.19757998147907</v>
+        <v>-236.95011289979709</v>
       </c>
       <c r="C20" s="0">
-        <v>478.85780108512654</v>
+        <v>92.727470186451342</v>
       </c>
     </row>
     <row r="21">
@@ -5986,10 +5986,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="0">
-        <v>-526.14848965112606</v>
+        <v>-241.43668162714772</v>
       </c>
       <c r="C21" s="0">
-        <v>489.91993101424112</v>
+        <v>104.11884282217773</v>
       </c>
     </row>
     <row r="22">
@@ -5997,10 +5997,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="0">
-        <v>-531.30447928105878</v>
+        <v>-246.11415538521331</v>
       </c>
       <c r="C22" s="0">
-        <v>500.83986116439371</v>
+        <v>115.37748235557604</v>
       </c>
     </row>
     <row r="23">
@@ -6008,10 +6008,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="0">
-        <v>-536.66333359306259</v>
+        <v>-250.981895479495</v>
       </c>
       <c r="C23" s="0">
-        <v>511.61887778809012</v>
+        <v>126.50494617882327</v>
       </c>
     </row>
     <row r="24">
@@ -6019,10 +6019,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="0">
-        <v>-542.22287145788926</v>
+        <v>-256.03908546996883</v>
       </c>
       <c r="C24" s="0">
-        <v>522.25762321227012</v>
+        <v>137.50206961672313</v>
       </c>
     </row>
     <row r="25">
@@ -6030,10 +6030,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="0">
-        <v>-547.98093157856931</v>
+        <v>-261.28475146722605</v>
       </c>
       <c r="C25" s="0">
-        <v>532.75620367755471</v>
+        <v>148.36909458680913</v>
       </c>
     </row>
     <row r="26">
@@ -6041,10 +6041,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="0">
-        <v>-553.93536092336581</v>
+        <v>-266.71777837313533</v>
       </c>
       <c r="C26" s="0">
-        <v>543.11427687459434</v>
+        <v>159.10577243662561</v>
       </c>
     </row>
     <row r="27">
@@ -6052,10 +6052,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="0">
-        <v>-560.08400533349732</v>
+        <v>-272.33692302092288</v>
       </c>
       <c r="C27" s="0">
-        <v>553.33112356221943</v>
+        <v>169.7114469067908</v>
       </c>
     </row>
     <row r="28">
@@ -6063,10 +6063,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="0">
-        <v>-566.42470186628236</v>
+        <v>-278.14082491803936</v>
       </c>
       <c r="C28" s="0">
-        <v>563.40570658888669</v>
+        <v>180.18512163249358</v>
       </c>
     </row>
     <row r="29">
@@ -6074,10 +6074,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="0">
-        <v>-572.9552725345618</v>
+        <v>-284.12801511653413</v>
       </c>
       <c r="C29" s="0">
-        <v>573.33671985983347</v>
+        <v>190.52551549692083</v>
       </c>
     </row>
     <row r="30">
@@ -6085,10 +6085,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="0">
-        <v>-579.67351917819428</v>
+        <v>-290.29692360734106</v>
       </c>
       <c r="C30" s="0">
-        <v>583.1226292149139</v>
+        <v>200.73110835281</v>
       </c>
     </row>
     <row r="31">
@@ -6096,10 +6096,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="0">
-        <v>-586.57721926003319</v>
+        <v>-296.64588554065995</v>
       </c>
       <c r="C31" s="0">
-        <v>592.76170674925686</v>
+        <v>210.80017904239657</v>
       </c>
     </row>
     <row r="32">
@@ -6107,10 +6107,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="0">
-        <v>-593.66412242198533</v>
+        <v>-303.17314650537873</v>
       </c>
       <c r="C32" s="0">
-        <v>602.252059781252</v>
+        <v>220.7308372107027</v>
       </c>
     </row>
     <row r="33">
@@ -6118,10 +6118,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="0">
-        <v>-600.93194766999091</v>
+        <v>-309.87686704875119</v>
       </c>
       <c r="C33" s="0">
-        <v>611.59165542200083</v>
+        <v>230.52105008003787</v>
       </c>
     </row>
     <row r="34">
@@ -6129,10 +6129,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="0">
-        <v>-608.37838108256483</v>
+        <v>-316.75512657831877</v>
       </c>
       <c r="C34" s="0">
-        <v>620.77834150740341</v>
+        <v>240.1686651054448</v>
       </c>
     </row>
     <row r="35">
@@ -6140,10 +6140,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="0">
-        <v>-616.00107395769646</v>
+        <v>-323.80592675821589</v>
       </c>
       <c r="C35" s="0">
-        <v>629.80986450401554</v>
+        <v>249.67142924082049</v>
       </c>
     </row>
     <row r="36">
@@ -6151,10 +6151,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="0">
-        <v>-623.79764132880791</v>
+        <v>-331.0271944892632</v>
       </c>
       <c r="C36" s="0">
-        <v>638.68388488242044</v>
+        <v>259.02700539876742</v>
       </c>
     </row>
     <row r="37">
@@ -6162,10 +6162,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="0">
-        <v>-631.76566079304757</v>
+        <v>-338.41678454425312</v>
       </c>
       <c r="C37" s="0">
-        <v>647.39799035913404</v>
+        <v>268.23298657293987</v>
       </c>
     </row>
     <row r="38">
@@ -6173,10 +6173,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="0">
-        <v>-639.90267160525025</v>
+        <v>-345.97248191609219</v>
       </c>
       <c r="C38" s="0">
-        <v>655.9497073345558</v>
+        <v>277.28690800211922</v>
       </c>
     </row>
     <row r="39">
@@ -6184,10 +6184,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="0">
-        <v>-648.20617399895491</v>
+        <v>-353.69200392535515</v>
       </c>
       <c r="C39" s="0">
-        <v>664.33651079558922</v>
+        <v>286.18625768441046</v>
       </c>
     </row>
     <row r="40">
@@ -6195,10 +6195,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="0">
-        <v>-656.673628702369</v>
+        <v>-361.57300212525138</v>
       </c>
       <c r="C40" s="0">
-        <v>672.55583290427671</v>
+        <v>294.92848549371746</v>
       </c>
     </row>
     <row r="41">
@@ -6206,10 +6206,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="0">
-        <v>-665.30245662244238</v>
+        <v>-369.613064034964</v>
       </c>
       <c r="C41" s="0">
-        <v>680.60507045552151</v>
+        <v>303.51101110556016</v>
       </c>
     </row>
     <row r="42">
@@ -6217,10 +6217,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="0">
-        <v>-674.09003867450974</v>
+        <v>-377.80971472672007</v>
       </c>
       <c r="C42" s="0">
-        <v>688.48159135578328</v>
+        <v>311.93123090303169</v>
       </c>
     </row>
     <row r="43">
@@ -6228,10 +6228,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="0">
-        <v>-683.03371573846255</v>
+        <v>-386.16041828742687</v>
       </c>
       <c r="C43" s="0">
-        <v>696.18274024916218</v>
+        <v>320.18652400430324</v>
       </c>
     </row>
     <row r="44">
@@ -6239,10 +6239,10 @@
         <v>42</v>
       </c>
       <c r="B44" s="0">
-        <v>-692.13078872530832</v>
+        <v>-394.66257917198061</v>
       </c>
       <c r="C44" s="0">
-        <v>703.70584339629238</v>
+        <v>328.27425752912978</v>
       </c>
     </row>
     <row r="45">
@@ -6250,10 +6250,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="0">
-        <v>-701.37851874033504</v>
+        <v>-403.31354346242875</v>
       </c>
       <c r="C45" s="0">
-        <v>711.04821289409233</v>
+        <v>336.1917912022447</v>
       </c>
     </row>
     <row r="46">
@@ -6261,10 +6261,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="0">
-        <v>-710.77412733107485</v>
+        <v>-412.11060004436769</v>
       </c>
       <c r="C46" s="0">
-        <v>718.2071503099852</v>
+        <v>343.936481375303</v>
       </c>
     </row>
     <row r="47">
@@ -6272,10 +6272,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="0">
-        <v>-720.31479680987729</v>
+        <v>-421.05098171019142</v>
       </c>
       <c r="C47" s="0">
-        <v>725.17994979207083</v>
+        <v>351.50568453573624</v>
       </c>
     </row>
     <row r="48">
@@ -6283,10 +6283,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="0">
-        <v>-729.99767064224898</v>
+        <v>-430.13186619676913</v>
       </c>
       <c r="C48" s="0">
-        <v>731.96390070657481</v>
+        <v>358.89676035969728</v>
       </c>
     </row>
     <row r="49">
@@ -6294,10 +6294,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="0">
-        <v>-739.81985389324802</v>
+        <v>-439.35037716380197</v>
       </c>
       <c r="C49" s="0">
-        <v>738.55628984522036</v>
+        <v>366.10707435696656</v>
       </c>
     </row>
     <row r="50">
@@ -6305,10 +6305,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="0">
-        <v>-749.77841372512489</v>
+        <v>-448.70358511762083</v>
       </c>
       <c r="C50" s="0">
-        <v>744.95440323780963</v>
+        <v>373.13400014780888</v>
       </c>
     </row>
     <row r="51">
@@ -6316,10 +6316,10 @@
         <v>49</v>
       </c>
       <c r="B51" s="0">
-        <v>-759.87037994020261</v>
+        <v>-458.18850828442015</v>
       </c>
       <c r="C51" s="0">
-        <v>751.15552759894638</v>
+        <v>379.97492140515885</v>
       </c>
     </row>
     <row r="52">
@@ -6327,10 +6327,10 @@
         <v>50</v>
       </c>
       <c r="B52" s="0">
-        <v>-770.09274556358923</v>
+        <v>-467.80211343542766</v>
       </c>
       <c r="C52" s="0">
-        <v>757.15695143230494</v>
+        <v>386.62723348975345</v>
       </c>
     </row>
     <row r="53">
@@ -6338,10 +6338,10 @@
         <v>51</v>
       </c>
       <c r="B53" s="0">
-        <v>-780.44246746085821</v>
+        <v>-477.54131666622033</v>
       </c>
       <c r="C53" s="0">
-        <v>762.9559658110104</v>
+        <v>393.08834480102246</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>52</v>
       </c>
       <c r="B54" s="0">
-        <v>-790.91646698624265</v>
+        <v>-487.40298413108354</v>
       </c>
       <c r="C54" s="0">
-        <v>768.54986484842687</v>
+        <v>399.35567786221941</v>
       </c>
     </row>
     <row r="55">
@@ -6360,10 +6360,10 @@
         <v>53</v>
       </c>
       <c r="B55" s="0">
-        <v>-801.51163065721914</v>
+        <v>-497.38393273300943</v>
       </c>
       <c r="C55" s="0">
-        <v>773.93594586976474</v>
+        <v>405.42667015463627</v>
       </c>
     </row>
     <row r="56">
@@ -6371,10 +6371,10 @@
         <v>54</v>
       </c>
       <c r="B56" s="0">
-        <v>-812.22481085163065</v>
+        <v>-507.48093076890757</v>
       </c>
       <c r="C56" s="0">
-        <v>779.11150929142411</v>
+        <v>411.29877471240377</v>
       </c>
     </row>
     <row r="57">
@@ -6382,10 +6382,10 @@
         <v>55</v>
       </c>
       <c r="B57" s="0">
-        <v>-823.05282652366748</v>
+        <v>-517.69069852920848</v>
       </c>
       <c r="C57" s="0">
-        <v>784.0738582117616</v>
+        <v>416.96946048644759</v>
       </c>
     </row>
     <row r="58">
@@ -6393,10 +6393,10 @@
         <v>56</v>
       </c>
       <c r="B58" s="0">
-        <v>-833.99246393517501</v>
+        <v>-528.00990885032456</v>
       </c>
       <c r="C58" s="0">
-        <v>788.82029771388977</v>
+        <v>422.43621248353162</v>
       </c>
     </row>
     <row r="59">
@@ -6404,10 +6404,10 @@
         <v>57</v>
       </c>
       <c r="B59" s="0">
-        <v>-845.0404773988073</v>
+        <v>-538.43518761778955</v>
       </c>
       <c r="C59" s="0">
-        <v>793.34813387821873</v>
+        <v>427.69653168380012</v>
       </c>
     </row>
     <row r="60">
@@ -6415,10 +6415,10 @@
         <v>58</v>
       </c>
       <c r="B60" s="0">
-        <v>-856.19359002957663</v>
+        <v>-548.96311421720191</v>
       </c>
       <c r="C60" s="0">
-        <v>797.65467249961841</v>
+        <v>432.7479347379612</v>
       </c>
     </row>
     <row r="61">
@@ -6426,10 +6426,10 @@
         <v>59</v>
       </c>
       <c r="B61" s="0">
-        <v>-867.448494501298</v>
+        <v>-559.59022192974669</v>
       </c>
       <c r="C61" s="0">
-        <v>801.73721750123627</v>
+        <v>437.58795344306617</v>
       </c>
     </row>
     <row r="62">
@@ -6437,10 +6437,10 @@
         <v>60</v>
       </c>
       <c r="B62" s="0">
-        <v>-878.80185380434261</v>
+        <v>-570.3129982680066</v>
       </c>
       <c r="C62" s="0">
-        <v>805.59306903419361</v>
+        <v>442.21413399368748</v>
       </c>
     </row>
     <row r="63">
@@ -6448,10 +6448,10 @@
         <v>61</v>
       </c>
       <c r="B63" s="0">
-        <v>-890.25030200095603</v>
+        <v>-581.12788524729285</v>
       </c>
       <c r="C63" s="0">
-        <v>809.21952124944392</v>
+        <v>446.62403600320931</v>
       </c>
     </row>
     <row r="64">
@@ -6459,10 +6459,10 @@
         <v>62</v>
       </c>
       <c r="B64" s="0">
-        <v>-901.7904449742</v>
+        <v>-592.03127958707091</v>
       </c>
       <c r="C64" s="0">
-        <v>812.61385972505911</v>
+        <v>450.81523128786552</v>
       </c>
     </row>
     <row r="65">
@@ -6470,10 +6470,10 @@
         <v>63</v>
       </c>
       <c r="B65" s="0">
-        <v>-913.41886116628916</v>
+        <v>-603.01953283585124</v>
       </c>
       <c r="C65" s="0">
-        <v>815.77335852897704</v>
+        <v>454.78530240395554</v>
       </c>
     </row>
     <row r="66">
@@ -6481,10 +6481,10 @@
         <v>64</v>
       </c>
       <c r="B66" s="0">
-        <v>-925.1321023017781</v>
+        <v>-614.08895141243772</v>
       </c>
       <c r="C66" s="0">
-        <v>818.69527689382039</v>
+        <v>458.53184092649684</v>
       </c>
     </row>
     <row r="67">
@@ -6492,10 +6492,10 @@
         <v>65</v>
       </c>
       <c r="B67" s="0">
-        <v>-936.92669409060977</v>
+        <v>-625.23579655516448</v>
       </c>
       <c r="C67" s="0">
-        <v>821.3768554766599</v>
+        <v>462.05244545518218</v>
       </c>
     </row>
     <row r="68">
@@ -6503,10 +6503,10 @@
         <v>66</v>
       </c>
       <c r="B68" s="0">
-        <v>-948.79913690556418</v>
+        <v>-636.45628416977763</v>
       </c>
       <c r="C68" s="0">
-        <v>823.81531217254451</v>
+        <v>465.34471933102975</v>
       </c>
     </row>
     <row r="69">
@@ -6514,10 +6514,10 @@
         <v>67</v>
       </c>
       <c r="B69" s="0">
-        <v>-960.74590642803037</v>
+        <v>-647.74658456520797</v>
       </c>
       <c r="C69" s="0">
-        <v>826.0078374461167</v>
+        <v>468.40626804438836</v>
       </c>
     </row>
     <row r="70">
@@ -6525,10 +6525,10 @@
         <v>68</v>
       </c>
       <c r="B70" s="0">
-        <v>-972.76345425532008</v>
+        <v>-659.10282206537715</v>
       </c>
       <c r="C70" s="0">
-        <v>827.95158914065587</v>
+        <v>471.23469631204989</v>
       </c>
     </row>
     <row r="71">
@@ -6536,10 +6536,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="0">
-        <v>-984.84820846191383</v>
+        <v>-670.52107448339757</v>
       </c>
       <c r="C71" s="0">
-        <v>829.6436867183296</v>
+        <v>473.82760479795905</v>
       </c>
     </row>
     <row r="72">
@@ -6547,10 +6547,10 @@
         <v>70</v>
       </c>
       <c r="B72" s="0">
-        <v>-996.99657410603709</v>
+        <v>-681.99737244272387</v>
       </c>
       <c r="C72" s="0">
-        <v>831.08120487919791</v>
+        <v>476.1825864484174</v>
       </c>
     </row>
     <row r="73">
@@ -6558,10 +6558,10 @@
         <v>71</v>
       </c>
       <c r="B73" s="0">
-        <v>-1009.2049336718071</v>
+        <v>-693.52769852803067</v>
       </c>
       <c r="C73" s="0">
-        <v>832.26116649939536</v>
+        <v>478.29722240871871</v>
       </c>
     </row>
     <row r="74">
@@ -6569,10 +6569,10 @@
         <v>72</v>
       </c>
       <c r="B74" s="0">
-        <v>-1021.4696474358416</v>
+        <v>-705.10798624606832</v>
       </c>
       <c r="C74" s="0">
-        <v>833.18053482099037</v>
+        <v>480.16907748362854</v>
       </c>
     </row>
     <row r="75">
@@ -6580,10 +6580,10 @@
         <v>73</v>
       </c>
       <c r="B75" s="0">
-        <v>-1033.7870537456047</v>
+        <v>-716.73411877412616</v>
       </c>
       <c r="C75" s="0">
-        <v>833.83620481682919</v>
+        <v>481.79569509906753</v>
       </c>
     </row>
     <row r="76">
@@ -6591,10 +6591,10 @@
         <v>74</v>
       </c>
       <c r="B76" s="0">
-        <v>-1046.1534691948928</v>
+        <v>-728.40192747094966</v>
       </c>
       <c r="C76" s="0">
-        <v>834.22499364329235</v>
+        <v>483.17459171668366</v>
       </c>
     </row>
     <row r="77">
@@ -6602,10 +6602,10 @@
         <v>75</v>
       </c>
       <c r="B77" s="0">
-        <v>-1058.5651886796422</v>
+        <v>-740.10719012107154</v>
       </c>
       <c r="C77" s="0">
-        <v>834.34363008192577</v>
+        <v>484.30325064639777</v>
       </c>
     </row>
     <row r="78">
@@ -6613,10 +6613,10 @@
         <v>76</v>
       </c>
       <c r="B78" s="0">
-        <v>-1071.0184853146188</v>
+        <v>-751.84562887985089</v>
       </c>
       <c r="C78" s="0">
-        <v>834.18874285713127</v>
+        <v>485.17911519465582</v>
       </c>
     </row>
     <row r="79">
@@ -6624,10 +6624,10 @@
         <v>77</v>
       </c>
       <c r="B79" s="0">
-        <v>-1083.5096101884453</v>
+        <v>-763.61290788170004</v>
       </c>
       <c r="C79" s="0">
-        <v>833.75684770126259</v>
+        <v>485.79958107756988</v>
       </c>
     </row>
     <row r="80">
@@ -6635,10 +6635,10 @@
         <v>78</v>
       </c>
       <c r="B80" s="0">
-        <v>-1096.0347919307587</v>
+        <v>-775.40463046848345</v>
       </c>
       <c r="C80" s="0">
-        <v>833.04433302001996</v>
+        <v>486.16198801832047</v>
       </c>
     </row>
     <row r="81">
@@ -6646,10 +6646,10 @@
         <v>79</v>
       </c>
       <c r="B81" s="0">
-        <v>-1108.5902360609207</v>
+        <v>-787.21633598888047</v>
       </c>
       <c r="C81" s="0">
-        <v>832.04744398968239</v>
+        <v>486.26361043693436</v>
       </c>
     </row>
     <row r="82">
@@ -6657,10 +6657,10 @@
         <v>80</v>
       </c>
       <c r="B82" s="0">
-        <v>-1121.1721240824886</v>
+        <v>-799.04349611206737</v>
       </c>
       <c r="C82" s="0">
-        <v>830.76226489279759</v>
+        <v>486.1016471274653</v>
       </c>
     </row>
     <row r="83">
@@ -6668,10 +6668,10 @@
         <v>81</v>
       </c>
       <c r="B83" s="0">
-        <v>-1133.7766122814701</v>
+        <v>-810.88151059036511</v>
       </c>
       <c r="C83" s="0">
-        <v>829.18469946974017</v>
+        <v>485.67320980241789</v>
       </c>
     </row>
     <row r="84">
@@ -6679,10 +6679,10 @@
         <v>82</v>
       </c>
       <c r="B84" s="0">
-        <v>-1146.3998301789006</v>
+        <v>-822.72570239548361</v>
       </c>
       <c r="C84" s="0">
-        <v>827.31044902938595</v>
+        <v>484.97531036662173</v>
       </c>
     </row>
     <row r="85">
@@ -6690,10 +6690,10 @@
         <v>83</v>
       </c>
       <c r="B85" s="0">
-        <v>-1159.0378785793664</v>
+        <v>-834.57131214060644</v>
       </c>
       <c r="C85" s="0">
-        <v>825.13498802178288</v>
+        <v>484.00484676203553</v>
       </c>
     </row>
     <row r="86">
@@ -6701,10 +6701,10 @@
         <v>84</v>
       </c>
       <c r="B86" s="0">
-        <v>-1171.6868271462677</v>
+        <v>-846.41349168684883</v>
       </c>
       <c r="C86" s="0">
-        <v>822.6535367280751</v>
+        <v>482.75858720082647</v>
       </c>
     </row>
     <row r="87">
@@ -6712,10 +6712,10 @@
         <v>85</v>
       </c>
       <c r="B87" s="0">
-        <v>-1184.3427114215763</v>
+        <v>-858.2472968152149</v>
       </c>
       <c r="C87" s="0">
-        <v>819.86103066640703</v>
+        <v>481.23315257547716</v>
       </c>
     </row>
     <row r="88">
@@ -6723,10 +6723,10 @@
         <v>86</v>
       </c>
       <c r="B88" s="0">
-        <v>-1197.0015291919374</v>
+        <v>-870.06767882530528</v>
       </c>
       <c r="C88" s="0">
-        <v>816.75208624519951</v>
+        <v>479.42499680107199</v>
       </c>
     </row>
     <row r="89">
@@ -6734,10 +6734,10 @@
         <v>87</v>
       </c>
       <c r="B89" s="0">
-        <v>-1209.6592360836317</v>
+        <v>-881.86947489779027</v>
       </c>
       <c r="C89" s="0">
-        <v>813.32096211464489</v>
+        <v>477.33038480497686</v>
       </c>
     </row>
     <row r="90">
@@ -6745,10 +6745,10 @@
         <v>88</v>
       </c>
       <c r="B90" s="0">
-        <v>-1222.3117402451837</v>
+        <v>-893.64739702874783</v>
       </c>
       <c r="C90" s="0">
-        <v>809.56151557062469</v>
+        <v>474.94536783165</v>
       </c>
     </row>
     <row r="91">
@@ -6756,10 +6756,10 @@
         <v>89</v>
       </c>
       <c r="B91" s="0">
-        <v>-1234.9548959472431</v>
+        <v>-905.39601930874142</v>
       </c>
       <c r="C91" s="0">
-        <v>805.4671532485736</v>
+        <v>472.2657556735723</v>
       </c>
     </row>
     <row r="92">
@@ -6767,10 +6767,10 @@
         <v>90</v>
       </c>
       <c r="B92" s="0">
-        <v>-1247.5844958933558</v>
+        <v>-917.10976327743742</v>
       </c>
       <c r="C92" s="0">
-        <v>801.03077520344743</v>
+        <v>469.2870853712123</v>
       </c>
     </row>
     <row r="93">
@@ -6778,10 +6778,10 @@
         <v>91</v>
       </c>
       <c r="B93" s="0">
-        <v>-1260.1962619904866</v>
+        <v>-928.78288103261559</v>
       </c>
       <c r="C93" s="0">
-        <v>796.24471129986682</v>
+        <v>466.00458584287298</v>
       </c>
     </row>
     <row r="94">
@@ -6789,10 +6789,10 @@
         <v>92</v>
       </c>
       <c r="B94" s="0">
-        <v>-1272.7858342723855</v>
+        <v>-940.40943570946536</v>
       </c>
       <c r="C94" s="0">
-        <v>791.10064862570732</v>
+        <v>462.41313780590485</v>
       </c>
     </row>
     <row r="95">
@@ -6800,10 +6800,10 @@
         <v>93</v>
       </c>
       <c r="B95" s="0">
-        <v>-1285.3487575988561</v>
+        <v>-951.98327886835841</v>
       </c>
       <c r="C95" s="0">
-        <v>785.58954838306886</v>
+        <v>458.50722822986972</v>
       </c>
     </row>
     <row r="96">
@@ -6811,10 +6811,10 @@
         <v>94</v>
       </c>
       <c r="B96" s="0">
-        <v>-1297.8804656656948</v>
+        <v>-963.49802423332062</v>
       </c>
       <c r="C96" s="0">
-        <v>779.70155038945052</v>
+        <v>454.28089841432501</v>
       </c>
     </row>
     <row r="97">
@@ -6822,10 +6822,10 @@
         <v>95</v>
       </c>
       <c r="B97" s="0">
-        <v>-1310.3762617479829</v>
+        <v>-974.94701710429911</v>
       </c>
       <c r="C97" s="0">
-        <v>773.42586292198985</v>
+        <v>449.72768460199717</v>
       </c>
     </row>
     <row r="98">
@@ -6833,10 +6833,10 @@
         <v>96</v>
       </c>
       <c r="B98" s="0">
-        <v>-1322.8312954562571</v>
+        <v>-986.32329861708342</v>
       </c>
       <c r="C98" s="0">
-        <v>766.75063513620921</v>
+        <v>444.84054981312346</v>
       </c>
     </row>
     <row r="99">
@@ -6844,10 +6844,10 @@
         <v>97</v>
       </c>
       <c r="B99" s="0">
-        <v>-1335.240534600983</v>
+        <v>-997.61956383753602</v>
       </c>
       <c r="C99" s="0">
-        <v>759.66280865769795</v>
+        <v>439.61180530659704</v>
       </c>
     </row>
     <row r="100">
@@ -6855,10 +6855,10 @@
         <v>98</v>
       </c>
       <c r="B100" s="0">
-        <v>-1347.5987310222852</v>
+        <v>-1008.8281124390254</v>
       </c>
       <c r="C100" s="0">
-        <v>752.14794414014148</v>
+        <v>434.03301972268832</v>
       </c>
     </row>
     <row r="101">
@@ -6866,10 +6866,10 @@
         <v>99</v>
       </c>
       <c r="B101" s="0">
-        <v>-1359.9003789305746</v>
+        <v>-1019.9407904096911</v>
       </c>
       <c r="C101" s="0">
-        <v>744.1900175511596</v>
+        <v>428.09491351936953</v>
       </c>
     </row>
     <row r="102">
@@ -6877,10 +6877,10 @@
         <v>100</v>
       </c>
       <c r="B102" s="0">
-        <v>-1372.1396638939368</v>
+        <v>-1030.9489208465611</v>
       </c>
       <c r="C102" s="0">
-        <v>735.77117961342492</v>
+        <v>421.78723575149581</v>
       </c>
     </row>
     <row r="103">
@@ -6888,10 +6888,10 @@
         <v>101</v>
       </c>
       <c r="B103" s="0">
-        <v>-1384.3104000639141</v>
+        <v>-1041.843221390475</v>
       </c>
       <c r="C103" s="0">
-        <v>726.87147008831221</v>
+        <v>415.09861952117279</v>
       </c>
     </row>
     <row r="104">
@@ -6899,10 +6899,10 @@
         <v>102</v>
       </c>
       <c r="B104" s="0">
-        <v>-1396.4059525015575</v>
+        <v>-1052.6137051969695</v>
       </c>
       <c r="C104" s="0">
-        <v>717.46847629679723</v>
+        <v>408.01641149590182</v>
       </c>
     </row>
     <row r="105">
@@ -6910,10 +6910,10 @@
         <v>103</v>
       </c>
       <c r="B105" s="0">
-        <v>-1408.419140476914</v>
+        <v>-1063.249561471057</v>
       </c>
       <c r="C105" s="0">
-        <v>707.5369222202637</v>
+        <v>400.52646967610855</v>
       </c>
     </row>
     <row r="106">
@@ -6921,10 +6921,10 @@
         <v>104</v>
       </c>
       <c r="B106" s="0">
-        <v>-1420.3421162603672</v>
+        <v>-1073.7390104378603</v>
       </c>
       <c r="C106" s="0">
-        <v>697.04817041371416</v>
+        <v>392.61292199335259</v>
       </c>
     </row>
     <row r="107">
@@ -6932,10 +6932,10 @@
         <v>105</v>
       </c>
       <c r="B107" s="0">
-        <v>-1432.166212045267</v>
+        <v>-1084.0691260661784</v>
       </c>
       <c r="C107" s="0">
-        <v>685.9696133596351</v>
+        <v>384.25787619016256</v>
       </c>
     </row>
     <row r="108">
@@ -6943,10 +6943,10 @@
         <v>106</v>
       </c>
       <c r="B108" s="0">
-        <v>-1443.8817450001711</v>
+        <v>-1094.2256177437159</v>
       </c>
       <c r="C108" s="0">
-        <v>674.26392314480177</v>
+        <v>375.44106856321838</v>
       </c>
     </row>
     <row r="109">
@@ -6954,10 +6954,10 @@
         <v>107</v>
       </c>
       <c r="B109" s="0">
-        <v>-1455.4777666821585</v>
+        <v>-1104.1925591824133</v>
       </c>
       <c r="C109" s="0">
-        <v>661.88811747604132</v>
+        <v>366.13943523846478</v>
       </c>
     </row>
     <row r="110">
@@ -6965,10 +6965,10 @@
         <v>108</v>
       </c>
       <c r="B110" s="0">
-        <v>-1466.9417375833079</v>
+        <v>-1113.9520487488046</v>
       </c>
       <c r="C110" s="0">
-        <v>648.79238455609561</v>
+        <v>356.32658423550367</v>
       </c>
     </row>
     <row r="111">
@@ -6976,10 +6976,10 @@
         <v>109</v>
       </c>
       <c r="B111" s="0">
-        <v>-1478.259099528429</v>
+        <v>-1123.4837796182815</v>
       </c>
       <c r="C111" s="0">
-        <v>634.91858684325018</v>
+        <v>345.97213898210629</v>
       </c>
     </row>
     <row r="112">
@@ -6987,10 +6987,10 @@
         <v>110</v>
       </c>
       <c r="B112" s="0">
-        <v>-1489.4127065237681</v>
+        <v>-1132.7644897882924</v>
       </c>
       <c r="C112" s="0">
-        <v>620.19833039169259</v>
+        <v>335.0409130964847</v>
       </c>
     </row>
     <row r="113">
@@ -6998,10 +6998,10 @@
         <v>111</v>
       </c>
       <c r="B113" s="0">
-        <v>-1500.3820560159791</v>
+        <v>-1141.7672496916261</v>
       </c>
       <c r="C113" s="0">
-        <v>604.55043598252632</v>
+        <v>323.49186048993948</v>
       </c>
     </row>
     <row r="114">
@@ -7009,10 +7009,10 @@
         <v>112</v>
       </c>
       <c r="B114" s="0">
-        <v>-1511.1422331274</v>
+        <v>-1150.4605267084255</v>
       </c>
       <c r="C114" s="0">
-        <v>587.8775698195459</v>
+        <v>311.27672144789995</v>
       </c>
     </row>
     <row r="115">
@@ -7020,10 +7020,10 @@
         <v>113</v>
       </c>
       <c r="B115" s="0">
-        <v>-1521.662432760834</v>
+        <v>-1158.8069375724169</v>
       </c>
       <c r="C115" s="0">
-        <v>570.06166617854376</v>
+        <v>298.33824982653516</v>
       </c>
     </row>
     <row r="116">
@@ -7031,10 +7031,10 @@
         <v>114</v>
       </c>
       <c r="B116" s="0">
-        <v>-1531.9038446143789</v>
+        <v>-1166.7615550972334</v>
       </c>
       <c r="C116" s="0">
-        <v>550.95756731222525</v>
+        <v>284.60785116086788</v>
       </c>
     </row>
     <row r="117">
@@ -7042,10 +7042,10 @@
         <v>115</v>
       </c>
       <c r="B117" s="0">
-        <v>-1541.81654731615</v>
+        <v>-1174.2695633911462</v>
       </c>
       <c r="C117" s="0">
-        <v>530.38395076102506</v>
+        <v>270.00237269782093</v>
       </c>
     </row>
     <row r="118">
@@ -7053,10 +7053,10 @@
         <v>116</v>
       </c>
       <c r="B118" s="0">
-        <v>-1551.3348057701803</v>
+        <v>-1181.2629345995829</v>
       </c>
       <c r="C118" s="0">
-        <v>508.10997774541249</v>
+        <v>254.41963908201626</v>
       </c>
     </row>
     <row r="119">
@@ -7064,10 +7064,10 @@
         <v>117</v>
       </c>
       <c r="B119" s="0">
-        <v>-1560.369683661876</v>
+        <v>-1187.6555891616929</v>
       </c>
       <c r="C119" s="0">
-        <v>483.83489466430433</v>
+        <v>237.73207342405419</v>
       </c>
     </row>
     <row r="120">
@@ -7075,10 +7075,10 @@
         <v>118</v>
       </c>
       <c r="B120" s="0">
-        <v>-1568.7969016599568</v>
+        <v>-1193.3361167912949</v>
       </c>
       <c r="C120" s="0">
-        <v>457.15540397832081</v>
+        <v>219.77728511130607</v>
       </c>
     </row>
     <row r="121">
@@ -7086,10 +7086,10 @@
         <v>119</v>
       </c>
       <c r="B121" s="0">
-        <v>-1576.4357142518825</v>
+        <v>-1198.1563950903708</v>
       </c>
       <c r="C121" s="0">
-        <v>427.51037360015204</v>
+        <v>200.34363269527364</v>
       </c>
     </row>
     <row r="122">
@@ -7097,10 +7097,10 @@
         <v>120</v>
       </c>
       <c r="B122" s="0">
-        <v>-1583.0093475395622</v>
+        <v>-1201.9129224009687</v>
       </c>
       <c r="C122" s="0">
-        <v>394.07988244665546</v>
+        <v>179.14699526004745</v>
       </c>
     </row>
   </sheetData>
